--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.712</v>
+        <v>0.708</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>590.9299999999999</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.552</v>
+        <v>0.527</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>2723.16</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.528</v>
+        <v>0.51</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>1074.11</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.476</v>
+        <v>0.472</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>12965.18</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.428</v>
+        <v>0.422</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>106366.17</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>1241.31</v>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.34</v>
+        <v>0.347</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>52717.24</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.307</v>
+        <v>0.316</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>1165.85</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.296</v>
+        <v>0.289</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>2992.18</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.246</v>
+        <v>0.252</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>238.15</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.198</v>
+        <v>0.203</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>1399.1</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.145</v>
+        <v>0.155</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>399.81</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>2198.74</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.318</v>
+        <v>1.284</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>754.02</v>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.387</v>
+        <v>0.373</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>1187.51</v>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.286</v>
+        <v>0.287</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>13692.85</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.702</v>
+        <v>0.698</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>627.4299999999999</v>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.388</v>
+        <v>0.395</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>706.29</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.393</v>
+        <v>1.376</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.124</v>
+        <v>1.109</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.613</v>
+        <v>0.603</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.538</v>
+        <v>0.55</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.416</v>
+        <v>0.414</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>23983.85</v>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>36459.35</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.307</v>
+        <v>0.305</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.277</v>
+        <v>0.272</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>17599.83</v>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.265</v>
+        <v>0.259</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.637</v>
+        <v>2.621</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.666</v>
+        <v>1.683</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.869</v>
+        <v>0.859</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.787</v>
+        <v>0.805</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.676</v>
+        <v>0.696</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.628</v>
+        <v>0.631</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.519</v>
+        <v>0.534</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2247,39 +2247,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>IFP</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Interfor Corporation</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.708</v>
+        <v>0.931</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>590.9299999999999</v>
+        <v>372.96</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>WDO</t>
+          <t>IFP</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd.</t>
+          <t>Interfor Corporation</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -2303,18 +2303,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.527</v>
+        <v>0.715</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>2723.16</v>
+        <v>590.9299999999999</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
+          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>WDO</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation</t>
+          <t>Wesdome Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2348,20 +2348,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.51</v>
+        <v>0.539</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1074.11</v>
+        <v>2723.16</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.472</v>
+        <v>0.51</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>12965.18</v>
+        <v>1074.11</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.422</v>
+        <v>0.474</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>106366.17</v>
+        <v>12965.18</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,33 +2452,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.375</v>
+        <v>0.422</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>1241.31</v>
+        <v>106366.17</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc.</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.347</v>
+        <v>0.375</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>52717.24</v>
+        <v>1241.31</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CFP</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Canfor Corporation</t>
+          <t>Cenovus Energy Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.316</v>
+        <v>0.345</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>1165.85</v>
+        <v>52717.24</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
+          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2575,39 +2575,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>CFP</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Canfor Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.289</v>
+        <v>0.321</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>2992.18</v>
+        <v>1165.85</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2616,39 +2616,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.275</v>
+        <v>0.287</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>690.71</v>
+        <v>2992.18</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.252</v>
+        <v>0.275</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>238.15</v>
+        <v>690.71</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -2717,20 +2717,20 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.203</v>
+        <v>0.258</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>1399.1</v>
+        <v>238.15</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>WFG</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>West Fraser Timber Co. Ltd.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.171</v>
+        <v>0.247</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>430.47</v>
+        <v>5201.6</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>West Fraser Timber Co</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -2780,33 +2780,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.155</v>
+        <v>0.203</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>399.81</v>
+        <v>1399.1</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2821,74 +2821,74 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.131</v>
+        <v>0.171</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>2198.74</v>
+        <v>430.47</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="106" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Eupraxia Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.284</v>
+        <v>0.152</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>754.02</v>
+        <v>399.81</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2896,46 +2896,46 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>LGD</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>1.067</v>
+        <v>0.129</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>521.72</v>
+        <v>2198.74</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="106" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2944,33 +2944,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>HMMC</t>
+          <t>MATR</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp.</t>
+          <t>Mattr Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.373</v>
+        <v>1.342</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>1187.51</v>
+        <v>754.02</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,190 +2985,246 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>LGD</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Liberty Gold Corp.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.287</v>
+        <v>1.072</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>13692.85</v>
+        <v>521.72</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B27" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>HMMC</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Hemlo Mining Corp.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.698</v>
+        <v>0.37</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>627.4299999999999</v>
+        <v>1187.51</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C28" s="130" t="inlineStr">
-        <is>
-          <t>SGY</t>
-        </is>
-      </c>
-      <c r="D28" s="131" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="132" t="inlineStr">
+      <c r="B28" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C28" s="115" t="inlineStr">
+        <is>
+          <t>WCP</t>
+        </is>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>Whitecap Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="117" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F28" s="132" t="inlineStr">
+      <c r="F28" s="117" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G28" s="133" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H28" s="134" t="n">
-        <v>706.29</v>
-      </c>
-      <c r="I28" s="135" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+      <c r="G28" s="118" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="H28" s="119" t="n">
+        <v>13692.85</v>
+      </c>
+      <c r="I28" s="120" t="inlineStr">
+        <is>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="8" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="136" t="n"/>
-      <c r="C29" s="137" t="n"/>
-      <c r="D29" s="138" t="n"/>
-      <c r="E29" s="139" t="n"/>
-      <c r="F29" s="139" t="n"/>
-      <c r="G29" s="140" t="n"/>
-      <c r="H29" s="141" t="n"/>
-      <c r="I29" s="142" t="n"/>
+      <c r="B29" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>TOT</t>
+        </is>
+      </c>
+      <c r="D29" s="122" t="inlineStr">
+        <is>
+          <t>Total Energy Services Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F29" s="123" t="inlineStr">
+        <is>
+          <t>Energy Equipment and Services</t>
+        </is>
+      </c>
+      <c r="G29" s="118" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="H29" s="124" t="n">
+        <v>627.4299999999999</v>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+        </is>
+      </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C30" s="144" t="n"/>
-      <c r="D30" s="144" t="n"/>
-      <c r="E30" s="144" t="n"/>
-      <c r="F30" s="144" t="n"/>
-      <c r="G30" s="144" t="n"/>
-      <c r="H30" s="144" t="n"/>
-      <c r="I30" s="144" t="n"/>
+      <c r="B30" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C30" s="130" t="inlineStr">
+        <is>
+          <t>SGY</t>
+        </is>
+      </c>
+      <c r="D30" s="131" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="132" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F30" s="132" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G30" s="133" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="H30" s="134" t="n">
+        <v>706.29</v>
+      </c>
+      <c r="I30" s="135" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+        </is>
+      </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="28" customHeight="1">
+    <row r="31" ht="8" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C31" s="146" t="n"/>
-      <c r="D31" s="146" t="n"/>
-      <c r="E31" s="146" t="n"/>
-      <c r="F31" s="146" t="n"/>
-      <c r="G31" s="146" t="n"/>
-      <c r="H31" s="146" t="n"/>
-      <c r="I31" s="146" t="n"/>
+      <c r="B31" s="136" t="n"/>
+      <c r="C31" s="137" t="n"/>
+      <c r="D31" s="138" t="n"/>
+      <c r="E31" s="139" t="n"/>
+      <c r="F31" s="139" t="n"/>
+      <c r="G31" s="140" t="n"/>
+      <c r="H31" s="141" t="n"/>
+      <c r="I31" s="142" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="91" t="n"/>
-      <c r="I32" s="53" t="n"/>
+      <c r="B32" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C32" s="144" t="n"/>
+      <c r="D32" s="144" t="n"/>
+      <c r="E32" s="144" t="n"/>
+      <c r="F32" s="144" t="n"/>
+      <c r="G32" s="144" t="n"/>
+      <c r="H32" s="144" t="n"/>
+      <c r="I32" s="144" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="20.4" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="89" t="n"/>
-      <c r="H33" s="93" t="n"/>
-      <c r="I33" s="54" t="n"/>
+      <c r="B33" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C33" s="146" t="n"/>
+      <c r="D33" s="146" t="n"/>
+      <c r="E33" s="146" t="n"/>
+      <c r="F33" s="146" t="n"/>
+      <c r="G33" s="146" t="n"/>
+      <c r="H33" s="146" t="n"/>
+      <c r="I33" s="146" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -3383,12 +3439,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G28">
+  <conditionalFormatting sqref="G8:G30">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4369,7 +4425,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4502,7 +4558,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.376</v>
+        <v>1.37</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4543,7 +4599,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.109</v>
+        <v>1.115</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4584,7 +4640,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.603</v>
+        <v>0.626</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4625,7 +4681,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.55</v>
+        <v>0.545</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4666,7 +4722,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.513</v>
+        <v>0.517</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4707,7 +4763,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>23983.85</v>
@@ -4748,7 +4804,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.408</v>
+        <v>0.412</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>36459.35</v>
@@ -4789,7 +4845,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4830,7 +4886,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.305</v>
+        <v>0.307</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4871,7 +4927,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.272</v>
+        <v>0.275</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -4912,7 +4968,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>17599.83</v>
@@ -4953,7 +5009,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -4994,7 +5050,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.621</v>
+        <v>2.596</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5035,7 +5091,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.683</v>
+        <v>1.664</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5076,7 +5132,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.859</v>
+        <v>0.864</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5117,7 +5173,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.805</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5158,7 +5214,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.696</v>
+        <v>0.709</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5199,7 +5255,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5240,7 +5296,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.631</v>
+        <v>0.642</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5281,7 +5337,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.534</v>
+        <v>0.536</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5322,7 +5378,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2247,39 +2247,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>IFP</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Interfor Corporation</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.931</v>
+        <v>0.698</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>372.96</v>
+        <v>590.9299999999999</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>IFP</t>
+          <t>WDO</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Interfor Corporation</t>
+          <t>Wesdome Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -2303,18 +2303,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.715</v>
+        <v>0.526</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>590.9299999999999</v>
+        <v>2723.16</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
+          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WDO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd.</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2348,20 +2348,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.539</v>
+        <v>0.485</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>2723.16</v>
+        <v>1074.11</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.51</v>
+        <v>0.477</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>1074.11</v>
+        <v>12965.18</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.474</v>
+        <v>0.418</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>12965.18</v>
+        <v>106366.17</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,33 +2452,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.422</v>
+        <v>0.375</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>106366.17</v>
+        <v>1241.31</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>Cenovus Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.375</v>
+        <v>0.345</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>1241.31</v>
+        <v>52717.24</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>CFP</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc.</t>
+          <t>Canfor Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.345</v>
+        <v>0.311</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>52717.24</v>
+        <v>1165.85</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
+          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2575,39 +2575,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>CFP</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Canfor Corporation</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.321</v>
+        <v>0.297</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>1165.85</v>
+        <v>2992.18</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2616,39 +2616,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.287</v>
+        <v>0.275</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>2992.18</v>
+        <v>690.71</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.275</v>
+        <v>0.262</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>690.71</v>
+        <v>238.15</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -2717,20 +2717,20 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.258</v>
+        <v>0.195</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>238.15</v>
+        <v>1399.1</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>WFG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>West Fraser Timber Co. Ltd.</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.247</v>
+        <v>0.171</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>5201.6</v>
+        <v>430.47</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>West Fraser Timber Co</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -2780,33 +2780,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Eupraxia Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.203</v>
+        <v>0.153</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>1399.1</v>
+        <v>399.81</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2821,74 +2821,74 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.171</v>
+        <v>0.12</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>430.47</v>
+        <v>2198.74</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="106" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>MATR</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc.</t>
+          <t>Mattr Corp.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.152</v>
+        <v>1.328</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>399.81</v>
+        <v>754.02</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2896,46 +2896,46 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B24" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>LGD</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Liberty Gold Corp.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.129</v>
+        <v>1.113</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>2198.74</v>
+        <v>521.72</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="106" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2944,33 +2944,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>HMMC</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Hemlo Mining Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>1.342</v>
+        <v>0.347</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>754.02</v>
+        <v>1187.51</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,246 +2985,190 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>LGD</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>1.072</v>
+        <v>0.275</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>521.72</v>
+        <v>13692.85</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B27" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>HMMC</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.37</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>1187.51</v>
+        <v>627.4299999999999</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C28" s="115" t="inlineStr">
-        <is>
-          <t>WCP</t>
-        </is>
-      </c>
-      <c r="D28" s="116" t="inlineStr">
-        <is>
-          <t>Whitecap Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="117" t="inlineStr">
+      <c r="B28" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C28" s="130" t="inlineStr">
+        <is>
+          <t>SGY</t>
+        </is>
+      </c>
+      <c r="D28" s="131" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="132" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F28" s="117" t="inlineStr">
+      <c r="F28" s="132" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G28" s="118" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="H28" s="119" t="n">
-        <v>13692.85</v>
-      </c>
-      <c r="I28" s="120" t="inlineStr">
-        <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+      <c r="G28" s="133" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H28" s="134" t="n">
+        <v>706.29</v>
+      </c>
+      <c r="I28" s="135" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="8" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C29" s="121" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="D29" s="122" t="inlineStr">
-        <is>
-          <t>Total Energy Services Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F29" s="123" t="inlineStr">
-        <is>
-          <t>Energy Equipment and Services</t>
-        </is>
-      </c>
-      <c r="G29" s="118" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="H29" s="124" t="n">
-        <v>627.4299999999999</v>
-      </c>
-      <c r="I29" s="125" t="inlineStr">
-        <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
-        </is>
-      </c>
+      <c r="B29" s="136" t="n"/>
+      <c r="C29" s="137" t="n"/>
+      <c r="D29" s="138" t="n"/>
+      <c r="E29" s="139" t="n"/>
+      <c r="F29" s="139" t="n"/>
+      <c r="G29" s="140" t="n"/>
+      <c r="H29" s="141" t="n"/>
+      <c r="I29" s="142" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C30" s="130" t="inlineStr">
-        <is>
-          <t>SGY</t>
-        </is>
-      </c>
-      <c r="D30" s="131" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="132" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F30" s="132" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G30" s="133" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="H30" s="134" t="n">
-        <v>706.29</v>
-      </c>
-      <c r="I30" s="135" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
-        </is>
-      </c>
+      <c r="B30" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C30" s="144" t="n"/>
+      <c r="D30" s="144" t="n"/>
+      <c r="E30" s="144" t="n"/>
+      <c r="F30" s="144" t="n"/>
+      <c r="G30" s="144" t="n"/>
+      <c r="H30" s="144" t="n"/>
+      <c r="I30" s="144" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="8" customHeight="1">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="136" t="n"/>
-      <c r="C31" s="137" t="n"/>
-      <c r="D31" s="138" t="n"/>
-      <c r="E31" s="139" t="n"/>
-      <c r="F31" s="139" t="n"/>
-      <c r="G31" s="140" t="n"/>
-      <c r="H31" s="141" t="n"/>
-      <c r="I31" s="142" t="n"/>
+      <c r="B31" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C31" s="146" t="n"/>
+      <c r="D31" s="146" t="n"/>
+      <c r="E31" s="146" t="n"/>
+      <c r="F31" s="146" t="n"/>
+      <c r="G31" s="146" t="n"/>
+      <c r="H31" s="146" t="n"/>
+      <c r="I31" s="146" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C32" s="144" t="n"/>
-      <c r="D32" s="144" t="n"/>
-      <c r="E32" s="144" t="n"/>
-      <c r="F32" s="144" t="n"/>
-      <c r="G32" s="144" t="n"/>
-      <c r="H32" s="144" t="n"/>
-      <c r="I32" s="144" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C33" s="146" t="n"/>
-      <c r="D33" s="146" t="n"/>
-      <c r="E33" s="146" t="n"/>
-      <c r="F33" s="146" t="n"/>
-      <c r="G33" s="146" t="n"/>
-      <c r="H33" s="146" t="n"/>
-      <c r="I33" s="146" t="n"/>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="89" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -3439,12 +3383,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G30">
+  <conditionalFormatting sqref="G8:G28">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4425,7 +4369,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4558,7 +4502,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.37</v>
+        <v>1.373</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4599,7 +4543,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.115</v>
+        <v>1.122</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4640,7 +4584,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.626</v>
+        <v>0.601</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4681,7 +4625,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4722,7 +4666,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.517</v>
+        <v>0.513</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4735,7 +4679,7 @@
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4744,39 +4688,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.417</v>
+        <v>0.416</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>23983.85</v>
+        <v>36459.35</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4785,33 +4729,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.412</v>
+        <v>0.405</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>36459.35</v>
+        <v>23983.85</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -4845,7 +4789,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4886,7 +4830,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.307</v>
+        <v>0.31</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4927,7 +4871,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -5009,7 +4953,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -5050,7 +4994,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.596</v>
+        <v>2.579</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5091,7 +5035,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.664</v>
+        <v>1.654</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5132,7 +5076,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.864</v>
+        <v>0.862</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5173,7 +5117,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5214,7 +5158,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.709</v>
+        <v>0.702</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5255,7 +5199,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.697</v>
+        <v>0.711</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5296,7 +5240,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.642</v>
+        <v>0.644</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5337,7 +5281,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.536</v>
+        <v>0.533</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5378,7 +5322,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.48</v>
+        <v>0.494</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -895,6 +895,9 @@
     <xf numFmtId="0" fontId="34" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -945,9 +948,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46304.71976872718</v>
+        <v>46307.83654378022</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46304.71976872718</v>
+        <v>46307.83654378022</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.824</v>
+        <v>1.071</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>498.51</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.756</v>
+        <v>0.652</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>443.56</v>
@@ -2320,7 +2320,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2329,39 +2329,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>743.0700000000001</v>
+        <v>925.72</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>925.72</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2411,39 +2411,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Aurora Cannabis Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.316</v>
+        <v>0.207</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>304.87</v>
+        <v>3837.96</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Aurora Cannabis Inc together with its subsidiaries engages in the production distribution and sale of cannabis products in Canada and internationally</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -2471,14 +2471,14 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.263</v>
+        <v>0.195</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>1545.36</v>
+        <v>80962.39</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2493,33 +2493,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>TXG</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.177</v>
+        <v>0.162</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>3837.96</v>
+        <v>4675.63</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>KITS</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>Kits Eyecare Ltd.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.167</v>
+        <v>0.106</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>80962.39</v>
+        <v>394.83</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.11</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>6196.82</v>
@@ -2607,7 +2607,7 @@
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2616,121 +2616,121 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>TXG</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Computer Modelling Group Ltd.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.08</v>
+        <v>0.054</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>4675.63</v>
+        <v>226.17</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>KITS</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd.</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.075</v>
+        <v>0.477</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>394.83</v>
+        <v>492.8</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd.</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.034</v>
+        <v>0.475</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>226.17</v>
+        <v>777.7</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="88" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="127" t="inlineStr">
         <is>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.519</v>
+        <v>0.412</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>209743.55</v>
+        <v>732.01</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="127" t="inlineStr">
         <is>
@@ -2780,39 +2780,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.491</v>
+        <v>0.4</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>777.7</v>
+        <v>209743.55</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2821,39 +2821,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.442</v>
+        <v>0.354</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>732.01</v>
+        <v>1326.96</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2862,39 +2862,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>Ero Copper Corp.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.4</v>
+        <v>0.327</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>492.8</v>
+        <v>3867.19</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>Ero Copper Corp engages in the exploration development and production of mining projects in Brazil</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="88" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2903,33 +2903,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.338</v>
+        <v>0.244</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>1326.96</v>
+        <v>745.59</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -2963,14 +2963,14 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.298</v>
+        <v>0.234</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>6794.59</v>
+        <v>3333.46</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,39 +2985,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.294</v>
+        <v>0.182</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>745.59</v>
+        <v>997.76</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3026,39 +3026,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>WJX</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Wajax Corporation</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.288</v>
+        <v>0.152</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>3333.46</v>
+        <v>598.17</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Wajax Corporation provides industrial products and services in Canada</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3067,33 +3067,33 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>FTT</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Ero Copper Corp.</t>
+          <t>Finning International Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.212</v>
+        <v>0.149</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>3867.19</v>
+        <v>9996.17</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Ero Copper Corp engages in the exploration development and production of mining projects in Brazil</t>
+          <t>Finning International Inc sells services and rents heavy equipment engines and related products in Canada Chile the United Kingdom Argentina and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Tecsys Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
@@ -3127,14 +3127,14 @@
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.179</v>
+        <v>0.137</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>399.91</v>
+        <v>6794.59</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Tecsys Inc engages in the development marketing and sale of enterprise-wide supply chain management software and related services in Canada the United States Europe and internationally</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
@@ -3149,39 +3149,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>FTT</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Finning International Inc.</t>
+          <t>Tecsys Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.176</v>
+        <v>0.078</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>9996.17</v>
+        <v>399.91</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Finning International Inc sells services and rents heavy equipment engines and related products in Canada Chile the United Kingdom Argentina and internationally</t>
+          <t>Tecsys Inc engages in the development marketing and sale of enterprise-wide supply chain management software and related services in Canada the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3190,33 +3190,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.133</v>
+        <v>0.057</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>997.76</v>
+        <v>1823.99</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -3224,81 +3224,81 @@
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>WJX</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Wajax Corporation</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.107</v>
+        <v>0.293</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>598.17</v>
+        <v>1633.9</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Wajax Corporation provides industrial products and services in Canada</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="52" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="128" t="inlineStr">
+      <c r="B33" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C33" s="129" t="inlineStr">
-        <is>
-          <t>ORE</t>
-        </is>
-      </c>
-      <c r="D33" s="130" t="inlineStr">
-        <is>
-          <t>Orezone Gold Corporation</t>
-        </is>
-      </c>
-      <c r="E33" s="131" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F33" s="131" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G33" s="132" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H33" s="133" t="n">
-        <v>1633.9</v>
-      </c>
-      <c r="I33" s="134" t="inlineStr">
-        <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+      <c r="C33" s="130" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="D33" s="131" t="inlineStr">
+        <is>
+          <t>Aurora Cannabis Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="132" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F33" s="132" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G33" s="133" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H33" s="134" t="n">
+        <v>304.87</v>
+      </c>
+      <c r="I33" s="135" t="inlineStr">
+        <is>
+          <t>Aurora Cannabis Inc together with its subsidiaries engages in the production distribution and sale of cannabis products in Canada and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -3306,48 +3306,48 @@
     </row>
     <row r="34" ht="8" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="135" t="n"/>
-      <c r="C34" s="136" t="n"/>
-      <c r="D34" s="137" t="n"/>
-      <c r="E34" s="138" t="n"/>
-      <c r="F34" s="138" t="n"/>
-      <c r="G34" s="139" t="n"/>
-      <c r="H34" s="140" t="n"/>
-      <c r="I34" s="141" t="n"/>
+      <c r="B34" s="136" t="n"/>
+      <c r="C34" s="137" t="n"/>
+      <c r="D34" s="138" t="n"/>
+      <c r="E34" s="139" t="n"/>
+      <c r="F34" s="139" t="n"/>
+      <c r="G34" s="140" t="n"/>
+      <c r="H34" s="141" t="n"/>
+      <c r="I34" s="142" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="142" t="inlineStr">
+      <c r="B35" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C35" s="143" t="n"/>
-      <c r="D35" s="143" t="n"/>
-      <c r="E35" s="143" t="n"/>
-      <c r="F35" s="143" t="n"/>
-      <c r="G35" s="143" t="n"/>
-      <c r="H35" s="143" t="n"/>
-      <c r="I35" s="143" t="n"/>
+      <c r="C35" s="144" t="n"/>
+      <c r="D35" s="144" t="n"/>
+      <c r="E35" s="144" t="n"/>
+      <c r="F35" s="144" t="n"/>
+      <c r="G35" s="144" t="n"/>
+      <c r="H35" s="144" t="n"/>
+      <c r="I35" s="144" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="144" t="inlineStr">
+      <c r="B36" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C36" s="145" t="n"/>
-      <c r="D36" s="145" t="n"/>
-      <c r="E36" s="145" t="n"/>
-      <c r="F36" s="145" t="n"/>
-      <c r="G36" s="145" t="n"/>
-      <c r="H36" s="145" t="n"/>
-      <c r="I36" s="145" t="n"/>
+      <c r="C36" s="146" t="n"/>
+      <c r="D36" s="146" t="n"/>
+      <c r="E36" s="146" t="n"/>
+      <c r="F36" s="146" t="n"/>
+      <c r="G36" s="146" t="n"/>
+      <c r="H36" s="146" t="n"/>
+      <c r="I36" s="146" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46304.71976872718</v>
+        <v>46307.83654378022</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4623,39 +4623,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Datadog Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.196</v>
+        <v>1.327</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>48504.52</v>
+        <v>98620.67</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -4664,33 +4664,33 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.06</v>
+        <v>1.164</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>123883.6</v>
+        <v>48504.52</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.843</v>
+        <v>0.819</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>122343.55</v>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.786</v>
+        <v>0.745</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>109006.53</v>
@@ -4778,7 +4778,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4787,33 +4787,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.699</v>
+        <v>0.665</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>14054.04</v>
+        <v>17950.14</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.603</v>
+        <v>0.537</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>26429.32</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.554</v>
+        <v>0.464</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>459224.48</v>
@@ -4901,7 +4901,7 @@
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Arista Networks Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -4925,24 +4925,24 @@
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>21029.38</v>
+        <v>265705.98</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Arista Networks Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
@@ -4970,61 +4970,61 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.422</v>
+        <v>0.117</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>265705.98</v>
+        <v>98476.7</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>Lumentum Holdings Inc manufactures and sells optical and photonic products in the Americas the Asia-Pacific Europe the Middle East and Africa</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B17" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.284</v>
+        <v>2.909</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>98476.7</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc manufactures and sells optical and photonic products in the Americas the Asia-Pacific Europe the Middle East and Africa</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="127" t="inlineStr">
         <is>
@@ -5033,39 +5033,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Hewlett Packard Enterprise Company</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>3.335</v>
+        <v>1.73</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>95407.55</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -5074,12 +5074,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company</t>
+          <t>Palo Alto Networks Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -5089,24 +5089,24 @@
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>1.951</v>
+        <v>1.419</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>95407.55</v>
+        <v>333603.3</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+          <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="88" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="127" t="inlineStr">
         <is>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc.</t>
+          <t>NetApp Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
@@ -5130,24 +5130,24 @@
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>1.563</v>
+        <v>1.319</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>333603.3</v>
+        <v>46186.75</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
+          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="52" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="127" t="inlineStr">
         <is>
@@ -5156,12 +5156,12 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc.</t>
+          <t>Everpure Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -5171,18 +5171,18 @@
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Semiconductors and Semiconductor Equipment</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.473</v>
+        <v>1.291</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>1040152.7</v>
+        <v>49676.52</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc operates as a semiconductor company internationally</t>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
@@ -5197,39 +5197,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>1.43</v>
+        <v>1.042</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>49676.52</v>
+        <v>123883.6</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="88" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -5238,39 +5238,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>NetApp Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.405</v>
+        <v>0.764</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>46186.75</v>
+        <v>45576.53</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -5279,33 +5279,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.841</v>
+        <v>0.406</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>45576.53</v>
+        <v>21029.38</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.395</v>
+        <v>0.293</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>3913396.13</v>
@@ -5352,42 +5352,42 @@
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings Inc.</t>
+          <t>Johnson Controls International plc</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>1.714</v>
+        <v>0.136</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>277784.63</v>
+        <v>93531.92999999999</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings Inc provides cybersecurity solutions in the United States and internationally</t>
+          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5395,19 +5395,19 @@
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="146" t="inlineStr">
+      <c r="B27" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Fortinet Inc.</t>
+          <t>CrowdStrike Holdings Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
@@ -5421,55 +5421,55 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>1.462</v>
+        <v>1.516</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>138773.13</v>
+        <v>277784.63</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+          <t>CrowdStrike Holdings Inc provides cybersecurity solutions in the United States and internationally</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="146" t="inlineStr">
+      <c r="B28" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Illumina Inc.</t>
+          <t>Fortinet Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>1.154</v>
+        <v>1.342</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>39661.06</v>
+        <v>138773.13</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Illumina Inc provides sequencing- and array-based solutions for genetic and genomic analysis in the Americas Europe Greater China the Asia Pacific the Middle East and Africa</t>
+          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
@@ -5477,40 +5477,40 @@
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="128" t="inlineStr">
+      <c r="B29" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C29" s="129" t="inlineStr">
-        <is>
-          <t>RVTY</t>
-        </is>
-      </c>
-      <c r="D29" s="130" t="inlineStr">
-        <is>
-          <t>Revvity Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="131" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F29" s="131" t="inlineStr">
-        <is>
-          <t>Life Sciences Tools and Services</t>
-        </is>
-      </c>
-      <c r="G29" s="132" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="H29" s="133" t="n">
-        <v>16701.36</v>
-      </c>
-      <c r="I29" s="134" t="inlineStr">
-        <is>
-          <t>Revvity Inc provides health sciences solutions technologies and services</t>
+      <c r="C29" s="130" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D29" s="131" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="132" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F29" s="132" t="inlineStr">
+        <is>
+          <t>Semiconductors and Semiconductor Equipment</t>
+        </is>
+      </c>
+      <c r="G29" s="133" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="H29" s="134" t="n">
+        <v>1040152.7</v>
+      </c>
+      <c r="I29" s="135" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices Inc operates as a semiconductor company internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5518,48 +5518,48 @@
     </row>
     <row r="30" ht="8" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="135" t="n"/>
-      <c r="C30" s="136" t="n"/>
-      <c r="D30" s="137" t="n"/>
-      <c r="E30" s="138" t="n"/>
-      <c r="F30" s="138" t="n"/>
-      <c r="G30" s="139" t="n"/>
-      <c r="H30" s="140" t="n"/>
-      <c r="I30" s="141" t="n"/>
+      <c r="B30" s="136" t="n"/>
+      <c r="C30" s="137" t="n"/>
+      <c r="D30" s="138" t="n"/>
+      <c r="E30" s="139" t="n"/>
+      <c r="F30" s="139" t="n"/>
+      <c r="G30" s="140" t="n"/>
+      <c r="H30" s="141" t="n"/>
+      <c r="I30" s="142" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="142" t="inlineStr">
+      <c r="B31" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C31" s="143" t="n"/>
-      <c r="D31" s="143" t="n"/>
-      <c r="E31" s="143" t="n"/>
-      <c r="F31" s="143" t="n"/>
-      <c r="G31" s="143" t="n"/>
-      <c r="H31" s="143" t="n"/>
-      <c r="I31" s="143" t="n"/>
+      <c r="C31" s="144" t="n"/>
+      <c r="D31" s="144" t="n"/>
+      <c r="E31" s="144" t="n"/>
+      <c r="F31" s="144" t="n"/>
+      <c r="G31" s="144" t="n"/>
+      <c r="H31" s="144" t="n"/>
+      <c r="I31" s="144" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="144" t="inlineStr">
+      <c r="B32" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C32" s="145" t="n"/>
-      <c r="D32" s="145" t="n"/>
-      <c r="E32" s="145" t="n"/>
-      <c r="F32" s="145" t="n"/>
-      <c r="G32" s="145" t="n"/>
-      <c r="H32" s="145" t="n"/>
-      <c r="I32" s="145" t="n"/>
+      <c r="C32" s="146" t="n"/>
+      <c r="D32" s="146" t="n"/>
+      <c r="E32" s="146" t="n"/>
+      <c r="F32" s="146" t="n"/>
+      <c r="G32" s="146" t="n"/>
+      <c r="H32" s="146" t="n"/>
+      <c r="I32" s="146" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46307.83654378022</v>
+        <v>46308.74562633393</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46307.83654378022</v>
+        <v>46308.74562633393</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.071</v>
+        <v>1.131</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>498.51</v>
@@ -2279,7 +2279,7 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>FTG</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -2303,18 +2303,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.652</v>
+        <v>0.749</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>443.56</v>
+        <v>600.1</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2329,39 +2329,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>FTG</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Firan Technology Group Corporation</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.4</v>
+        <v>0.526</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>925.72</v>
+        <v>443.56</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,39 +2370,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.36</v>
+        <v>0.448</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>925.72</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2411,33 +2411,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.207</v>
+        <v>0.379</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>3837.96</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.195</v>
+        <v>0.237</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>80962.39</v>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>TXG</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.162</v>
+        <v>0.226</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>4675.63</v>
+        <v>3837.96</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="106" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>KITS</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.106</v>
+        <v>0.187</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>394.83</v>
+        <v>99672.56</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.002</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>6196.82</v>
@@ -2607,42 +2607,42 @@
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="88" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B17" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd.</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.054</v>
+        <v>0.539</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>226.17</v>
+        <v>777.7</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.477</v>
+        <v>0.463</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>492.8</v>
@@ -2689,7 +2689,7 @@
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -2698,33 +2698,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.475</v>
+        <v>0.454</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>777.7</v>
+        <v>209743.55</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.412</v>
+        <v>0.397</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>732.01</v>
@@ -2780,39 +2780,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.4</v>
+        <v>0.354</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>209743.55</v>
+        <v>1326.96</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="88" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2821,33 +2821,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.354</v>
+        <v>0.251</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>1326.96</v>
+        <v>3333.46</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Ero Copper Corp.</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -2881,14 +2881,14 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.327</v>
+        <v>0.225</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>3867.19</v>
+        <v>1633.9</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Ero Copper Corp engages in the exploration development and production of mining projects in Brazil</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2903,33 +2903,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>WJX</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Wajax Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.244</v>
+        <v>0.171</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>745.59</v>
+        <v>598.17</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Wajax Corporation provides industrial products and services in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -2963,20 +2963,20 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.234</v>
+        <v>0.164</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>3333.46</v>
+        <v>6794.59</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2985,33 +2985,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>TXG</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.182</v>
+        <v>0.158</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>997.76</v>
+        <v>4675.63</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3026,33 +3026,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>WJX</t>
+          <t>KITS</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Wajax Corporation</t>
+          <t>Kits Eyecare Ltd.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.152</v>
+        <v>0.094</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>598.17</v>
+        <v>394.83</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Wajax Corporation provides industrial products and services in Canada</t>
+          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
@@ -3067,39 +3067,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>FTT</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Finning International Inc.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.149</v>
+        <v>0.06</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>9996.17</v>
+        <v>1823.99</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Finning International Inc sells services and rents heavy equipment engines and related products in Canada Chile the United Kingdom Argentina and internationally</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Computer Modelling Group Ltd.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
@@ -3127,55 +3127,55 @@
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.137</v>
+        <v>0.049</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>6794.59</v>
+        <v>226.17</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B30" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Tecsys Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.078</v>
+        <v>0.247</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>399.91</v>
+        <v>745.59</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Tecsys Inc engages in the development marketing and sale of enterprise-wide supply chain management software and related services in Canada the United States Europe and internationally</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -3183,171 +3183,115 @@
     </row>
     <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C31" s="121" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D31" s="122" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F31" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G31" s="118" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="H31" s="124" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I31" s="125" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+      <c r="B31" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C31" s="130" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="D31" s="131" t="inlineStr">
+        <is>
+          <t>Aurora Cannabis Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="132" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F31" s="132" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G31" s="133" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="H31" s="134" t="n">
+        <v>304.87</v>
+      </c>
+      <c r="I31" s="135" t="inlineStr">
+        <is>
+          <t>Aurora Cannabis Inc together with its subsidiaries engages in the production distribution and sale of cannabis products in Canada and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="8" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C32" s="115" t="inlineStr">
-        <is>
-          <t>ORE</t>
-        </is>
-      </c>
-      <c r="D32" s="116" t="inlineStr">
-        <is>
-          <t>Orezone Gold Corporation</t>
-        </is>
-      </c>
-      <c r="E32" s="117" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F32" s="117" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G32" s="118" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="H32" s="119" t="n">
-        <v>1633.9</v>
-      </c>
-      <c r="I32" s="120" t="inlineStr">
-        <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
-        </is>
-      </c>
+      <c r="B32" s="136" t="n"/>
+      <c r="C32" s="137" t="n"/>
+      <c r="D32" s="138" t="n"/>
+      <c r="E32" s="139" t="n"/>
+      <c r="F32" s="139" t="n"/>
+      <c r="G32" s="140" t="n"/>
+      <c r="H32" s="141" t="n"/>
+      <c r="I32" s="142" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C33" s="130" t="inlineStr">
-        <is>
-          <t>ACB</t>
-        </is>
-      </c>
-      <c r="D33" s="131" t="inlineStr">
-        <is>
-          <t>Aurora Cannabis Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="132" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F33" s="132" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G33" s="133" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H33" s="134" t="n">
-        <v>304.87</v>
-      </c>
-      <c r="I33" s="135" t="inlineStr">
-        <is>
-          <t>Aurora Cannabis Inc together with its subsidiaries engages in the production distribution and sale of cannabis products in Canada and internationally</t>
-        </is>
-      </c>
+      <c r="B33" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C33" s="144" t="n"/>
+      <c r="D33" s="144" t="n"/>
+      <c r="E33" s="144" t="n"/>
+      <c r="F33" s="144" t="n"/>
+      <c r="G33" s="144" t="n"/>
+      <c r="H33" s="144" t="n"/>
+      <c r="I33" s="144" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="8" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="136" t="n"/>
-      <c r="C34" s="137" t="n"/>
-      <c r="D34" s="138" t="n"/>
-      <c r="E34" s="139" t="n"/>
-      <c r="F34" s="139" t="n"/>
-      <c r="G34" s="140" t="n"/>
-      <c r="H34" s="141" t="n"/>
-      <c r="I34" s="142" t="n"/>
+      <c r="B34" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C34" s="146" t="n"/>
+      <c r="D34" s="146" t="n"/>
+      <c r="E34" s="146" t="n"/>
+      <c r="F34" s="146" t="n"/>
+      <c r="G34" s="146" t="n"/>
+      <c r="H34" s="146" t="n"/>
+      <c r="I34" s="146" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C35" s="144" t="n"/>
-      <c r="D35" s="144" t="n"/>
-      <c r="E35" s="144" t="n"/>
-      <c r="F35" s="144" t="n"/>
-      <c r="G35" s="144" t="n"/>
-      <c r="H35" s="144" t="n"/>
-      <c r="I35" s="144" t="n"/>
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="89" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="54" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="28" customHeight="1">
+    <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C36" s="146" t="n"/>
-      <c r="D36" s="146" t="n"/>
-      <c r="E36" s="146" t="n"/>
-      <c r="F36" s="146" t="n"/>
-      <c r="G36" s="146" t="n"/>
-      <c r="H36" s="146" t="n"/>
-      <c r="I36" s="146" t="n"/>
+      <c r="B36" s="48" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="89" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
@@ -3524,11 +3468,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G33">
+  <conditionalFormatting sqref="G8:G31">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4509,7 +4453,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46307.83654378022</v>
+        <v>46308.74562633393</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4623,33 +4567,33 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Datadog Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.327</v>
+        <v>2.971</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>98620.67</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
@@ -4664,39 +4608,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Datadog Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.164</v>
+        <v>1.314</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>48504.52</v>
+        <v>98620.67</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="88" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4705,39 +4649,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.819</v>
+        <v>1.121</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>122343.55</v>
+        <v>48504.52</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4746,12 +4690,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -4765,14 +4709,14 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.745</v>
+        <v>0.897</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>109006.53</v>
+        <v>122343.55</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -4787,33 +4731,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.665</v>
+        <v>0.804</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>17950.14</v>
+        <v>109006.53</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4828,12 +4772,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>F5 Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4843,18 +4787,18 @@
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.537</v>
+        <v>0.648</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>26429.32</v>
+        <v>17950.14</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4888,7 +4832,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.464</v>
+        <v>0.459</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>459224.48</v>
@@ -4901,7 +4845,7 @@
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4910,33 +4854,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Arista Networks Inc.</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.31</v>
+        <v>0.232</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>265705.98</v>
+        <v>30639.57</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -4951,33 +4895,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.117</v>
+        <v>0.163</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>98476.7</v>
+        <v>677009.86</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc manufactures and sells optical and photonic products in the Americas the Asia-Pacific Europe the Middle East and Africa</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -4985,19 +4929,19 @@
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -5007,18 +4951,18 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>2.909</v>
+        <v>0.114</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>74971.71000000001</v>
+        <v>108638.32</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -5052,7 +4996,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>95407.55</v>
@@ -5074,12 +5018,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc.</t>
+          <t>Everpure Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -5089,18 +5033,18 @@
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>1.419</v>
+        <v>1.289</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>333603.3</v>
+        <v>49676.52</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5134,7 +5078,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>1.319</v>
+        <v>1.28</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>46186.75</v>
@@ -5156,33 +5100,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.291</v>
+        <v>1.109</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>49676.52</v>
+        <v>123883.6</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
@@ -5197,39 +5141,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>1.042</v>
+        <v>0.825</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>123883.6</v>
+        <v>45576.53</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -5238,39 +5182,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.764</v>
+        <v>0.405</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>45576.53</v>
+        <v>21029.38</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -5279,12 +5223,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -5298,20 +5242,20 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.406</v>
+        <v>0.306</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>21029.38</v>
+        <v>3913396.13</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -5320,12 +5264,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Arista Networks Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5335,231 +5279,175 @@
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.293</v>
+        <v>0.264</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>3913396.13</v>
+        <v>265705.98</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="88" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B26" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc</t>
+          <t>Fortinet Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.136</v>
+        <v>1.329</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>93531.92999999999</v>
+        <v>138773.13</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="128" t="inlineStr">
+      <c r="B27" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C27" s="121" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="D27" s="122" t="inlineStr">
-        <is>
-          <t>CrowdStrike Holdings Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="123" t="inlineStr">
+      <c r="C27" s="130" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D27" s="131" t="inlineStr">
+        <is>
+          <t>F5 Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="132" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F27" s="123" t="inlineStr">
+      <c r="F27" s="132" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G27" s="118" t="n">
-        <v>1.516</v>
-      </c>
-      <c r="H27" s="124" t="n">
-        <v>277784.63</v>
-      </c>
-      <c r="I27" s="125" t="inlineStr">
-        <is>
-          <t>CrowdStrike Holdings Inc provides cybersecurity solutions in the United States and internationally</t>
+      <c r="G27" s="133" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="H27" s="134" t="n">
+        <v>26429.32</v>
+      </c>
+      <c r="I27" s="135" t="inlineStr">
+        <is>
+          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="8" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C28" s="115" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="D28" s="116" t="inlineStr">
-        <is>
-          <t>Fortinet Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="117" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F28" s="117" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G28" s="118" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="H28" s="119" t="n">
-        <v>138773.13</v>
-      </c>
-      <c r="I28" s="120" t="inlineStr">
-        <is>
-          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
-        </is>
-      </c>
+      <c r="B28" s="136" t="n"/>
+      <c r="C28" s="137" t="n"/>
+      <c r="D28" s="138" t="n"/>
+      <c r="E28" s="139" t="n"/>
+      <c r="F28" s="139" t="n"/>
+      <c r="G28" s="140" t="n"/>
+      <c r="H28" s="141" t="n"/>
+      <c r="I28" s="142" t="n"/>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C29" s="130" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="D29" s="131" t="inlineStr">
-        <is>
-          <t>Advanced Micro Devices Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="132" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F29" s="132" t="inlineStr">
-        <is>
-          <t>Semiconductors and Semiconductor Equipment</t>
-        </is>
-      </c>
-      <c r="G29" s="133" t="n">
-        <v>1.136</v>
-      </c>
-      <c r="H29" s="134" t="n">
-        <v>1040152.7</v>
-      </c>
-      <c r="I29" s="135" t="inlineStr">
-        <is>
-          <t>Advanced Micro Devices Inc operates as a semiconductor company internationally</t>
-        </is>
-      </c>
+      <c r="B29" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C29" s="144" t="n"/>
+      <c r="D29" s="144" t="n"/>
+      <c r="E29" s="144" t="n"/>
+      <c r="F29" s="144" t="n"/>
+      <c r="G29" s="144" t="n"/>
+      <c r="H29" s="144" t="n"/>
+      <c r="I29" s="144" t="n"/>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="8" customHeight="1">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="136" t="n"/>
-      <c r="C30" s="137" t="n"/>
-      <c r="D30" s="138" t="n"/>
-      <c r="E30" s="139" t="n"/>
-      <c r="F30" s="139" t="n"/>
-      <c r="G30" s="140" t="n"/>
-      <c r="H30" s="141" t="n"/>
-      <c r="I30" s="142" t="n"/>
+      <c r="B30" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C30" s="146" t="n"/>
+      <c r="D30" s="146" t="n"/>
+      <c r="E30" s="146" t="n"/>
+      <c r="F30" s="146" t="n"/>
+      <c r="G30" s="146" t="n"/>
+      <c r="H30" s="146" t="n"/>
+      <c r="I30" s="146" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="34" customHeight="1">
+    <row r="31">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C31" s="144" t="n"/>
-      <c r="D31" s="144" t="n"/>
-      <c r="E31" s="144" t="n"/>
-      <c r="F31" s="144" t="n"/>
-      <c r="G31" s="144" t="n"/>
-      <c r="H31" s="144" t="n"/>
-      <c r="I31" s="144" t="n"/>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="89" t="n"/>
+      <c r="H31" s="93" t="n"/>
+      <c r="I31" s="54" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C32" s="146" t="n"/>
-      <c r="D32" s="146" t="n"/>
-      <c r="E32" s="146" t="n"/>
-      <c r="F32" s="146" t="n"/>
-      <c r="G32" s="146" t="n"/>
-      <c r="H32" s="146" t="n"/>
-      <c r="I32" s="146" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
@@ -5787,12 +5675,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G29">
+  <conditionalFormatting sqref="G8:G27">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -369,17 +369,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0392B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFCEFE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
       </patternFill>
     </fill>
   </fills>
@@ -562,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -895,10 +895,60 @@
     <xf numFmtId="0" fontId="34" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -910,44 +960,12 @@
     <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2071,7 +2089,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46308.74562633393</v>
+        <v>46309.65282256808</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2151,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46308.74562633393</v>
+        <v>46309.65282256808</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2238,7 +2256,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2247,12 +2265,12 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
@@ -2262,18 +2280,18 @@
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.131</v>
+        <v>0.716</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>498.51</v>
+        <v>884.7</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
@@ -2307,7 +2325,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.749</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>600.1</v>
@@ -2329,33 +2347,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>FTG</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.526</v>
+        <v>0.573</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>443.56</v>
+        <v>925.72</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2370,39 +2388,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>FTG</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Firan Technology Group Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.448</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>925.72</v>
+        <v>443.56</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2411,39 +2429,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.379</v>
+        <v>0.432</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>743.0700000000001</v>
+        <v>15597.29</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,12 +2470,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -2471,20 +2489,20 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.237</v>
+        <v>0.304</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>80962.39</v>
+        <v>336.54</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2493,12 +2511,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2512,14 +2530,14 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.226</v>
+        <v>0.298</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>3837.96</v>
+        <v>80962.39</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -2553,7 +2571,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.187</v>
+        <v>0.282</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>99672.56</v>
@@ -2566,7 +2584,7 @@
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2575,33 +2593,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>BLCO</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Bausch + Lomb Corporation</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>-0.002</v>
+        <v>0.279</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>6196.82</v>
+        <v>3333.46</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Bausch + Lomb Corporation operates as an eye health company in the United States Puerto Rico China France Japan Germany the United Kingdom Canada Russia Spain Italy Mexico Poland and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2609,81 +2627,81 @@
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.539</v>
+        <v>0.248</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>777.7</v>
+        <v>3837.96</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="106" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.463</v>
+        <v>0.246</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>492.8</v>
+        <v>398.33</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2691,101 +2709,101 @@
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.454</v>
+        <v>0.216</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>209743.55</v>
+        <v>382.43</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.397</v>
+        <v>0.105</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>732.01</v>
+        <v>4283.74</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -2795,24 +2813,24 @@
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.354</v>
+        <v>0.1</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>1326.96</v>
+        <v>1823.99</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2821,39 +2839,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.251</v>
+        <v>1.146</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>3333.46</v>
+        <v>498.51</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2862,39 +2880,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.225</v>
+        <v>0.518</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>1633.9</v>
+        <v>777.7</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2903,39 +2921,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>WJX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Wajax Corporation</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.171</v>
+        <v>0.44</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>598.17</v>
+        <v>492.8</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Wajax Corporation provides industrial products and services in Canada</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2944,33 +2962,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.164</v>
+        <v>0.401</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>6794.59</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,39 +3003,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>TXG</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.158</v>
+        <v>0.399</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>4675.63</v>
+        <v>732.01</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="88" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3026,39 +3044,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>KITS</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.094</v>
+        <v>0.377</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>394.83</v>
+        <v>209743.55</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3067,12 +3085,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>NWC</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>The North West Company Inc.</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3082,24 +3100,24 @@
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>1823.99</v>
+        <v>1326.96</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3108,74 +3126,74 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.049</v>
+        <v>0.247</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>226.17</v>
+        <v>745.59</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B30" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.247</v>
+        <v>0.159</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>745.59</v>
+        <v>6794.59</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -3183,128 +3201,212 @@
     </row>
     <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C31" s="130" t="inlineStr">
-        <is>
-          <t>ACB</t>
-        </is>
-      </c>
-      <c r="D31" s="131" t="inlineStr">
-        <is>
-          <t>Aurora Cannabis Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="132" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F31" s="132" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G31" s="133" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="H31" s="134" t="n">
-        <v>304.87</v>
-      </c>
-      <c r="I31" s="135" t="inlineStr">
-        <is>
-          <t>Aurora Cannabis Inc together with its subsidiaries engages in the production distribution and sale of cannabis products in Canada and internationally</t>
+      <c r="B31" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C31" s="121" t="inlineStr">
+        <is>
+          <t>TXG</t>
+        </is>
+      </c>
+      <c r="D31" s="122" t="inlineStr">
+        <is>
+          <t>Torex Gold Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F31" s="123" t="inlineStr">
+        <is>
+          <t>Metals and Mining</t>
+        </is>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H31" s="124" t="n">
+        <v>4675.63</v>
+      </c>
+      <c r="I31" s="125" t="inlineStr">
+        <is>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="8" customHeight="1">
+    <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="136" t="n"/>
-      <c r="C32" s="137" t="n"/>
-      <c r="D32" s="138" t="n"/>
-      <c r="E32" s="139" t="n"/>
-      <c r="F32" s="139" t="n"/>
-      <c r="G32" s="140" t="n"/>
-      <c r="H32" s="141" t="n"/>
-      <c r="I32" s="142" t="n"/>
+      <c r="B32" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C32" s="115" t="inlineStr">
+        <is>
+          <t>KITS</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>Kits Eyecare Ltd.</t>
+        </is>
+      </c>
+      <c r="E32" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F32" s="117" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G32" s="118" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H32" s="119" t="n">
+        <v>394.83</v>
+      </c>
+      <c r="I32" s="120" t="inlineStr">
+        <is>
+          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
+        </is>
+      </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="88" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C33" s="144" t="n"/>
-      <c r="D33" s="144" t="n"/>
-      <c r="E33" s="144" t="n"/>
-      <c r="F33" s="144" t="n"/>
-      <c r="G33" s="144" t="n"/>
-      <c r="H33" s="144" t="n"/>
-      <c r="I33" s="144" t="n"/>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>CMG</t>
+        </is>
+      </c>
+      <c r="D33" s="122" t="inlineStr">
+        <is>
+          <t>Computer Modelling Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G33" s="118" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H33" s="124" t="n">
+        <v>226.17</v>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
+        </is>
+      </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="34" ht="88" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C34" s="146" t="n"/>
-      <c r="D34" s="146" t="n"/>
-      <c r="E34" s="146" t="n"/>
-      <c r="F34" s="146" t="n"/>
-      <c r="G34" s="146" t="n"/>
-      <c r="H34" s="146" t="n"/>
-      <c r="I34" s="146" t="n"/>
+      <c r="B34" s="128" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C34" s="129" t="inlineStr">
+        <is>
+          <t>BLCO</t>
+        </is>
+      </c>
+      <c r="D34" s="130" t="inlineStr">
+        <is>
+          <t>Bausch + Lomb Corporation</t>
+        </is>
+      </c>
+      <c r="E34" s="131" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F34" s="131" t="inlineStr">
+        <is>
+          <t>Health Care Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G34" s="132" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="H34" s="133" t="n">
+        <v>6196.82</v>
+      </c>
+      <c r="I34" s="134" t="inlineStr">
+        <is>
+          <t>Bausch + Lomb Corporation operates as an eye health company in the United States Puerto Rico China France Japan Germany the United Kingdom Canada Russia Spain Italy Mexico Poland and internationally</t>
+        </is>
+      </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="30.6" customHeight="1">
+    <row r="35" ht="8" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="89" t="n"/>
-      <c r="H35" s="93" t="n"/>
-      <c r="I35" s="54" t="n"/>
+      <c r="B35" s="135" t="n"/>
+      <c r="C35" s="136" t="n"/>
+      <c r="D35" s="137" t="n"/>
+      <c r="E35" s="138" t="n"/>
+      <c r="F35" s="138" t="n"/>
+      <c r="G35" s="139" t="n"/>
+      <c r="H35" s="140" t="n"/>
+      <c r="I35" s="141" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="40.8" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="40" t="n"/>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="89" t="n"/>
-      <c r="H36" s="91" t="n"/>
-      <c r="I36" s="53" t="n"/>
+      <c r="B36" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C36" s="143" t="n"/>
+      <c r="D36" s="143" t="n"/>
+      <c r="E36" s="143" t="n"/>
+      <c r="F36" s="143" t="n"/>
+      <c r="G36" s="143" t="n"/>
+      <c r="H36" s="143" t="n"/>
+      <c r="I36" s="143" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="89" t="n"/>
-      <c r="H37" s="93" t="n"/>
-      <c r="I37" s="54" t="n"/>
+      <c r="B37" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C37" s="145" t="n"/>
+      <c r="D37" s="145" t="n"/>
+      <c r="E37" s="145" t="n"/>
+      <c r="F37" s="145" t="n"/>
+      <c r="G37" s="145" t="n"/>
+      <c r="H37" s="145" t="n"/>
+      <c r="I37" s="145" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -3468,11 +3570,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G31">
+  <conditionalFormatting sqref="G8:G34">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4453,7 +4555,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46308.74562633393</v>
+        <v>46309.65282256808</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4586,7 +4688,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>2.971</v>
+        <v>3.067</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>74971.71000000001</v>
@@ -4627,7 +4729,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.314</v>
+        <v>1.147</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>98620.67</v>
@@ -4668,7 +4770,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>1.121</v>
+        <v>1.085</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>48504.52</v>
@@ -4681,7 +4783,7 @@
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4690,12 +4792,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -4709,14 +4811,14 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.897</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>122343.55</v>
+        <v>109006.53</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -4731,33 +4833,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.804</v>
+        <v>0.777</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>109006.53</v>
+        <v>45576.53</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4791,7 +4893,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.648</v>
+        <v>0.615</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>17950.14</v>
@@ -4832,7 +4934,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.459</v>
+        <v>0.397</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>459224.48</v>
@@ -4854,12 +4956,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -4869,24 +4971,24 @@
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.232</v>
+        <v>0.37</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>30639.57</v>
+        <v>480788.44</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4895,39 +4997,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.163</v>
+        <v>0.244</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>677009.86</v>
+        <v>682021.24</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -4936,156 +5038,156 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.114</v>
+        <v>0.217</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>108638.32</v>
+        <v>677009.86</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>1.68</v>
+        <v>0.197</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>95407.55</v>
+        <v>30639.57</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>1.289</v>
+        <v>0.176</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>49676.52</v>
+        <v>21455.05</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="88" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>NetApp Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>1.28</v>
+        <v>0.126</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>46186.75</v>
+        <v>108638.32</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
@@ -5119,7 +5221,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.109</v>
+        <v>1.245</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>123883.6</v>
@@ -5132,7 +5234,7 @@
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -5141,39 +5243,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>NetApp Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.825</v>
+        <v>1.175</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>45576.53</v>
+        <v>46186.75</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -5182,12 +5284,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Everpure Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -5197,24 +5299,24 @@
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.405</v>
+        <v>1.173</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>21029.38</v>
+        <v>49676.52</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="88" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -5223,39 +5325,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.306</v>
+        <v>1.054</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>3913396.13</v>
+        <v>122343.55</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="88" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -5264,12 +5366,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Arista Networks Inc.</t>
+          <t>F5 Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5279,18 +5381,18 @@
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.264</v>
+        <v>0.474</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>265705.98</v>
+        <v>26429.32</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -5298,19 +5400,19 @@
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Fortinet Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
@@ -5324,14 +5426,14 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>1.329</v>
+        <v>0.386</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>138773.13</v>
+        <v>21029.38</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5339,141 +5441,253 @@
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C27" s="130" t="inlineStr">
-        <is>
-          <t>FFIV</t>
-        </is>
-      </c>
-      <c r="D27" s="131" t="inlineStr">
-        <is>
-          <t>F5 Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="132" t="inlineStr">
+      <c r="B27" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C27" s="121" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D27" s="122" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F27" s="132" t="inlineStr">
+      <c r="F27" s="123" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G27" s="133" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="H27" s="134" t="n">
-        <v>26429.32</v>
-      </c>
-      <c r="I27" s="135" t="inlineStr">
-        <is>
-          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
+      <c r="G27" s="118" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="H27" s="124" t="n">
+        <v>3913396.13</v>
+      </c>
+      <c r="I27" s="125" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="8" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="136" t="n"/>
-      <c r="C28" s="137" t="n"/>
-      <c r="D28" s="138" t="n"/>
-      <c r="E28" s="139" t="n"/>
-      <c r="F28" s="139" t="n"/>
-      <c r="G28" s="140" t="n"/>
-      <c r="H28" s="141" t="n"/>
-      <c r="I28" s="142" t="n"/>
+      <c r="B28" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C28" s="115" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>Arista Networks Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F28" s="117" t="inlineStr">
+        <is>
+          <t>Communications Equipment</t>
+        </is>
+      </c>
+      <c r="G28" s="118" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="H28" s="119" t="n">
+        <v>265705.98</v>
+      </c>
+      <c r="I28" s="120" t="inlineStr">
+        <is>
+          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+        </is>
+      </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C29" s="144" t="n"/>
-      <c r="D29" s="144" t="n"/>
-      <c r="E29" s="144" t="n"/>
-      <c r="F29" s="144" t="n"/>
-      <c r="G29" s="144" t="n"/>
-      <c r="H29" s="144" t="n"/>
-      <c r="I29" s="144" t="n"/>
+      <c r="B29" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D29" s="122" t="inlineStr">
+        <is>
+          <t>Accenture plc</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F29" s="123" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="G29" s="118" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="H29" s="124" t="n">
+        <v>116683.09</v>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="28" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C30" s="146" t="n"/>
-      <c r="D30" s="146" t="n"/>
-      <c r="E30" s="146" t="n"/>
-      <c r="F30" s="146" t="n"/>
-      <c r="G30" s="146" t="n"/>
-      <c r="H30" s="146" t="n"/>
-      <c r="I30" s="146" t="n"/>
+      <c r="B30" s="146" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C30" s="115" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Company</t>
+        </is>
+      </c>
+      <c r="E30" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F30" s="117" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G30" s="118" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="H30" s="119" t="n">
+        <v>95407.55</v>
+      </c>
+      <c r="I30" s="120" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+        </is>
+      </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="89" t="n"/>
-      <c r="H31" s="93" t="n"/>
-      <c r="I31" s="54" t="n"/>
+      <c r="B31" s="147" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C31" s="148" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D31" s="149" t="inlineStr">
+        <is>
+          <t>Fortinet Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="150" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F31" s="150" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G31" s="132" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="H31" s="151" t="n">
+        <v>138773.13</v>
+      </c>
+      <c r="I31" s="152" t="inlineStr">
+        <is>
+          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+        </is>
+      </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="8" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="91" t="n"/>
-      <c r="I32" s="53" t="n"/>
+      <c r="B32" s="135" t="n"/>
+      <c r="C32" s="136" t="n"/>
+      <c r="D32" s="137" t="n"/>
+      <c r="E32" s="138" t="n"/>
+      <c r="F32" s="138" t="n"/>
+      <c r="G32" s="139" t="n"/>
+      <c r="H32" s="140" t="n"/>
+      <c r="I32" s="141" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="20.4" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="89" t="n"/>
-      <c r="H33" s="93" t="n"/>
-      <c r="I33" s="54" t="n"/>
+      <c r="B33" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C33" s="143" t="n"/>
+      <c r="D33" s="143" t="n"/>
+      <c r="E33" s="143" t="n"/>
+      <c r="F33" s="143" t="n"/>
+      <c r="G33" s="143" t="n"/>
+      <c r="H33" s="143" t="n"/>
+      <c r="I33" s="143" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="40" t="n"/>
-      <c r="F34" s="40" t="n"/>
-      <c r="G34" s="89" t="n"/>
-      <c r="H34" s="91" t="n"/>
-      <c r="I34" s="53" t="n"/>
+      <c r="B34" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C34" s="145" t="n"/>
+      <c r="D34" s="145" t="n"/>
+      <c r="E34" s="145" t="n"/>
+      <c r="F34" s="145" t="n"/>
+      <c r="G34" s="145" t="n"/>
+      <c r="H34" s="145" t="n"/>
+      <c r="I34" s="145" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
@@ -5675,12 +5889,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G27">
+  <conditionalFormatting sqref="G8:G31">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -369,6 +369,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCEFE0"/>
       </patternFill>
     </fill>
@@ -377,13 +382,8 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0392B"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -558,6 +558,30 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -895,7 +919,57 @@
     <xf numFmtId="0" fontId="34" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -907,65 +981,13 @@
     <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2089,7 +2111,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46309.65282256808</v>
+        <v>46310.64329707867</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2151,7 +2173,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46309.65282256808</v>
+        <v>46310.64329707867</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2256,7 +2278,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2265,39 +2287,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.716</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>884.7</v>
+        <v>600.1</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2306,39 +2328,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.413</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>600.1</v>
+        <v>15597.29</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2347,39 +2369,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.573</v>
+        <v>0.288</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>925.72</v>
+        <v>382.43</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="106" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2388,33 +2410,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>FTG</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>443.56</v>
+        <v>99672.56</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2429,12 +2451,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2448,14 +2470,14 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.432</v>
+        <v>0.268</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>15597.29</v>
+        <v>336.54</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -2470,39 +2492,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.304</v>
+        <v>0.23</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>336.54</v>
+        <v>43014.26</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="106" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2511,12 +2533,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2526,24 +2548,24 @@
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.298</v>
+        <v>0.226</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>80962.39</v>
+        <v>398.33</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="106" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2552,74 +2574,74 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.282</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>99672.56</v>
+        <v>4283.74</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B16" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.279</v>
+        <v>1.178</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>3333.46</v>
+        <v>498.51</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2627,60 +2649,60 @@
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B17" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>FTG</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Firan Technology Group Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.248</v>
+        <v>0.581</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>3837.96</v>
+        <v>443.56</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="106" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -2690,100 +2712,100 @@
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.246</v>
+        <v>0.448</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>398.33</v>
+        <v>925.72</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.216</v>
+        <v>0.365</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>382.43</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="88" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.105</v>
+        <v>0.331</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>4283.74</v>
+        <v>209743.55</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
@@ -2791,40 +2813,40 @@
     </row>
     <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B21" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>NWC</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>The North West Company Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.1</v>
+        <v>0.311</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>1823.99</v>
+        <v>3333.46</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2839,12 +2861,12 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
@@ -2858,20 +2880,20 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>1.146</v>
+        <v>0.307</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>498.51</v>
+        <v>80962.39</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2880,33 +2902,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.518</v>
+        <v>0.247</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>777.7</v>
+        <v>745.59</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2921,39 +2943,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.44</v>
+        <v>0.235</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>492.8</v>
+        <v>3837.96</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2962,33 +2984,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.401</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>6794.59</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -3003,39 +3025,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>TXG</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.399</v>
+        <v>0.107</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>732.01</v>
+        <v>4675.63</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="88" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3044,33 +3066,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.377</v>
+        <v>0.105</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>209743.55</v>
+        <v>1823.99</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
@@ -3085,328 +3107,188 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>Computer Modelling Group Ltd.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.34</v>
+        <v>0.047</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>1326.96</v>
+        <v>226.17</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C29" s="121" t="inlineStr">
-        <is>
-          <t>SEC</t>
-        </is>
-      </c>
-      <c r="D29" s="122" t="inlineStr">
-        <is>
-          <t>Senvest Capital Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F29" s="123" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G29" s="118" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="H29" s="124" t="n">
-        <v>745.59</v>
-      </c>
-      <c r="I29" s="125" t="inlineStr">
-        <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+      <c r="B29" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C29" s="129" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="D29" s="130" t="inlineStr">
+        <is>
+          <t>Wall Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E29" s="131" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F29" s="131" t="inlineStr">
+        <is>
+          <t>Real Estate Management and Development</t>
+        </is>
+      </c>
+      <c r="G29" s="132" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H29" s="133" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="I29" s="134" t="inlineStr">
+        <is>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="8" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C30" s="115" t="inlineStr">
-        <is>
-          <t>DSG</t>
-        </is>
-      </c>
-      <c r="D30" s="116" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="117" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F30" s="117" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G30" s="118" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="H30" s="119" t="n">
-        <v>6794.59</v>
-      </c>
-      <c r="I30" s="120" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
-        </is>
-      </c>
+      <c r="B30" s="135" t="n"/>
+      <c r="C30" s="136" t="n"/>
+      <c r="D30" s="137" t="n"/>
+      <c r="E30" s="138" t="n"/>
+      <c r="F30" s="138" t="n"/>
+      <c r="G30" s="139" t="n"/>
+      <c r="H30" s="140" t="n"/>
+      <c r="I30" s="141" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C31" s="121" t="inlineStr">
-        <is>
-          <t>TXG</t>
-        </is>
-      </c>
-      <c r="D31" s="122" t="inlineStr">
-        <is>
-          <t>Torex Gold Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="123" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F31" s="123" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G31" s="118" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="H31" s="124" t="n">
-        <v>4675.63</v>
-      </c>
-      <c r="I31" s="125" t="inlineStr">
-        <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
-        </is>
-      </c>
+      <c r="B31" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C31" s="143" t="n"/>
+      <c r="D31" s="143" t="n"/>
+      <c r="E31" s="143" t="n"/>
+      <c r="F31" s="143" t="n"/>
+      <c r="G31" s="143" t="n"/>
+      <c r="H31" s="143" t="n"/>
+      <c r="I31" s="143" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C32" s="115" t="inlineStr">
-        <is>
-          <t>KITS</t>
-        </is>
-      </c>
-      <c r="D32" s="116" t="inlineStr">
-        <is>
-          <t>Kits Eyecare Ltd.</t>
-        </is>
-      </c>
-      <c r="E32" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F32" s="117" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G32" s="118" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="H32" s="119" t="n">
-        <v>394.83</v>
-      </c>
-      <c r="I32" s="120" t="inlineStr">
-        <is>
-          <t>Kits Eyecare Ltd operates a digital eyecare platform in the United States and Canada</t>
-        </is>
-      </c>
+      <c r="B32" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C32" s="145" t="n"/>
+      <c r="D32" s="145" t="n"/>
+      <c r="E32" s="145" t="n"/>
+      <c r="F32" s="145" t="n"/>
+      <c r="G32" s="145" t="n"/>
+      <c r="H32" s="145" t="n"/>
+      <c r="I32" s="145" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="88" customHeight="1">
+    <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C33" s="121" t="inlineStr">
-        <is>
-          <t>CMG</t>
-        </is>
-      </c>
-      <c r="D33" s="122" t="inlineStr">
-        <is>
-          <t>Computer Modelling Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E33" s="123" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F33" s="123" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G33" s="118" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="H33" s="124" t="n">
-        <v>226.17</v>
-      </c>
-      <c r="I33" s="125" t="inlineStr">
-        <is>
-          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
-        </is>
-      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="89" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="88" customHeight="1">
+    <row r="34" ht="30.6" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="128" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C34" s="129" t="inlineStr">
-        <is>
-          <t>BLCO</t>
-        </is>
-      </c>
-      <c r="D34" s="130" t="inlineStr">
-        <is>
-          <t>Bausch + Lomb Corporation</t>
-        </is>
-      </c>
-      <c r="E34" s="131" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F34" s="131" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G34" s="132" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="H34" s="133" t="n">
-        <v>6196.82</v>
-      </c>
-      <c r="I34" s="134" t="inlineStr">
-        <is>
-          <t>Bausch + Lomb Corporation operates as an eye health company in the United States Puerto Rico China France Japan Germany the United Kingdom Canada Russia Spain Italy Mexico Poland and internationally</t>
-        </is>
-      </c>
+      <c r="B34" s="48" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="40" t="n"/>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="89" t="n"/>
+      <c r="H34" s="91" t="n"/>
+      <c r="I34" s="53" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="8" customHeight="1">
+    <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="135" t="n"/>
-      <c r="C35" s="136" t="n"/>
-      <c r="D35" s="137" t="n"/>
-      <c r="E35" s="138" t="n"/>
-      <c r="F35" s="138" t="n"/>
-      <c r="G35" s="139" t="n"/>
-      <c r="H35" s="140" t="n"/>
-      <c r="I35" s="141" t="n"/>
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="89" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="54" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C36" s="143" t="n"/>
-      <c r="D36" s="143" t="n"/>
-      <c r="E36" s="143" t="n"/>
-      <c r="F36" s="143" t="n"/>
-      <c r="G36" s="143" t="n"/>
-      <c r="H36" s="143" t="n"/>
-      <c r="I36" s="143" t="n"/>
+      <c r="B36" s="48" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="89" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C37" s="145" t="n"/>
-      <c r="D37" s="145" t="n"/>
-      <c r="E37" s="145" t="n"/>
-      <c r="F37" s="145" t="n"/>
-      <c r="G37" s="145" t="n"/>
-      <c r="H37" s="145" t="n"/>
-      <c r="I37" s="145" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="89" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -3570,11 +3452,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G34">
+  <conditionalFormatting sqref="G8:G29">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4555,7 +4437,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46309.65282256808</v>
+        <v>46310.64329707867</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4688,7 +4570,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>3.067</v>
+        <v>3.412</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>74971.71000000001</v>
@@ -4710,33 +4592,33 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Datadog Inc.</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.147</v>
+        <v>1.065</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>98620.67</v>
+        <v>48504.52</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -4751,33 +4633,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Datadog Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>1.085</v>
+        <v>1.027</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>48504.52</v>
+        <v>98620.67</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4792,33 +4674,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.9</v>
+        <v>0.852</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>109006.53</v>
+        <v>45576.53</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -4833,33 +4715,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.777</v>
+        <v>0.58</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>45576.53</v>
+        <v>17950.14</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4874,33 +4756,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.615</v>
+        <v>0.428</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>17950.14</v>
+        <v>480788.44</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4915,39 +4797,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.397</v>
+        <v>0.376</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>459224.48</v>
+        <v>26039.81</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States the United Kingdom and internationally</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4956,39 +4838,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.37</v>
+        <v>0.322</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>480788.44</v>
+        <v>11772.74</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4997,33 +4879,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.244</v>
+        <v>0.31</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>682021.24</v>
+        <v>241617.28</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -5038,39 +4920,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.217</v>
+        <v>0.302</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>677009.86</v>
+        <v>33430.82</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -5079,33 +4961,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.197</v>
+        <v>0.278</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>30639.57</v>
+        <v>682021.24</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5139,7 +5021,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.176</v>
+        <v>0.233</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>21455.05</v>
@@ -5152,7 +5034,7 @@
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="106" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -5161,12 +5043,12 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
@@ -5176,18 +5058,18 @@
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.126</v>
+        <v>0.231</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>108638.32</v>
+        <v>48910.32</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
@@ -5195,81 +5077,81 @@
     </row>
     <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.245</v>
+        <v>0.231</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>123883.6</v>
+        <v>30639.57</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="88" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>NetApp Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>1.175</v>
+        <v>0.23</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>46186.75</v>
+        <v>404759.18</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5277,81 +5159,81 @@
     </row>
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.173</v>
+        <v>0.203</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>49676.52</v>
+        <v>677009.86</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="88" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>1.054</v>
+        <v>0.194</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>122343.55</v>
+        <v>498865.76</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5359,60 +5241,60 @@
     </row>
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B25" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>F5 Inc.</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.474</v>
+        <v>0.186</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>26429.32</v>
+        <v>183538.16</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B26" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
@@ -5422,18 +5304,18 @@
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.386</v>
+        <v>0.185</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>21029.38</v>
+        <v>116683.09</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5441,422 +5323,786 @@
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B27" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.276</v>
+        <v>0.175</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>3913396.13</v>
+        <v>151241.83</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B28" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Arista Networks Inc.</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.196</v>
+        <v>0.168</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>265705.98</v>
+        <v>47993.25</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>eBay Inc together with its subsidiaries operates marketplace platforms that connect buyers and sellers in the United States the United Kingdom China Germany and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B29" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.119</v>
+        <v>0.159</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>116683.09</v>
+        <v>108638.32</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="88" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B30" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>1.445</v>
+        <v>0.148</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>95407.55</v>
+        <v>111058.59</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="147" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C31" s="148" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="D31" s="149" t="inlineStr">
-        <is>
-          <t>Fortinet Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="150" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F31" s="150" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G31" s="132" t="n">
-        <v>1.268</v>
-      </c>
-      <c r="H31" s="151" t="n">
-        <v>138773.13</v>
-      </c>
-      <c r="I31" s="152" t="inlineStr">
-        <is>
-          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+      <c r="B31" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C31" s="121" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D31" s="122" t="inlineStr">
+        <is>
+          <t>Pfizer Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F31" s="123" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="H31" s="124" t="n">
+        <v>159089.29</v>
+      </c>
+      <c r="I31" s="125" t="inlineStr">
+        <is>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="8" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="135" t="n"/>
-      <c r="C32" s="136" t="n"/>
-      <c r="D32" s="137" t="n"/>
-      <c r="E32" s="138" t="n"/>
-      <c r="F32" s="138" t="n"/>
-      <c r="G32" s="139" t="n"/>
-      <c r="H32" s="140" t="n"/>
-      <c r="I32" s="141" t="n"/>
+      <c r="B32" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C32" s="115" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E32" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F32" s="117" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="G32" s="118" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="H32" s="119" t="n">
+        <v>25579.38</v>
+      </c>
+      <c r="I32" s="120" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+        </is>
+      </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C33" s="143" t="n"/>
-      <c r="D33" s="143" t="n"/>
-      <c r="E33" s="143" t="n"/>
-      <c r="F33" s="143" t="n"/>
-      <c r="G33" s="143" t="n"/>
-      <c r="H33" s="143" t="n"/>
-      <c r="I33" s="143" t="n"/>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D33" s="122" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G33" s="118" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="H33" s="124" t="n">
+        <v>123883.6</v>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+        </is>
+      </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="28" customHeight="1">
+    <row r="34" ht="88" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C34" s="145" t="n"/>
-      <c r="D34" s="145" t="n"/>
-      <c r="E34" s="145" t="n"/>
-      <c r="F34" s="145" t="n"/>
-      <c r="G34" s="145" t="n"/>
-      <c r="H34" s="145" t="n"/>
-      <c r="I34" s="145" t="n"/>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C34" s="115" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="D34" s="116" t="inlineStr">
+        <is>
+          <t>NetApp Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F34" s="117" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G34" s="118" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="H34" s="119" t="n">
+        <v>46186.75</v>
+      </c>
+      <c r="I34" s="120" t="inlineStr">
+        <is>
+          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="20.4" customHeight="1">
+    <row r="35" ht="88" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="89" t="n"/>
-      <c r="H35" s="93" t="n"/>
-      <c r="I35" s="54" t="n"/>
+      <c r="B35" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C35" s="121" t="inlineStr">
+        <is>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="D35" s="122" t="inlineStr">
+        <is>
+          <t>Valero Energy Corporation</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F35" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G35" s="118" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="H35" s="124" t="n">
+        <v>122343.55</v>
+      </c>
+      <c r="I35" s="125" t="inlineStr">
+        <is>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+        </is>
+      </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="30.6" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="40" t="n"/>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="89" t="n"/>
-      <c r="H36" s="91" t="n"/>
-      <c r="I36" s="53" t="n"/>
+      <c r="B36" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C36" s="115" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="E36" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F36" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G36" s="118" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="H36" s="119" t="n">
+        <v>109006.53</v>
+      </c>
+      <c r="I36" s="120" t="inlineStr">
+        <is>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+        </is>
+      </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="30.6" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="89" t="n"/>
-      <c r="H37" s="93" t="n"/>
-      <c r="I37" s="54" t="n"/>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C37" s="121" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D37" s="122" t="inlineStr">
+        <is>
+          <t>F5 Inc.</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F37" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G37" s="118" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H37" s="124" t="n">
+        <v>26429.32</v>
+      </c>
+      <c r="I37" s="125" t="inlineStr">
+        <is>
+          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
+        </is>
+      </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="20.4" customHeight="1">
+    <row r="38" ht="52" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="40" t="n"/>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="89" t="n"/>
-      <c r="H38" s="91" t="n"/>
-      <c r="I38" s="53" t="n"/>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C38" s="115" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="E38" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F38" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G38" s="118" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="H38" s="119" t="n">
+        <v>21029.38</v>
+      </c>
+      <c r="I38" s="120" t="inlineStr">
+        <is>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="88" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="89" t="n"/>
-      <c r="H39" s="93" t="n"/>
-      <c r="I39" s="54" t="n"/>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D39" s="122" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F39" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G39" s="118" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="H39" s="124" t="n">
+        <v>459224.48</v>
+      </c>
+      <c r="I39" s="125" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States the United Kingdom and internationally</t>
+        </is>
+      </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="40" t="n"/>
-      <c r="F40" s="40" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="91" t="n"/>
-      <c r="I40" s="53" t="n"/>
+      <c r="B40" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D40" s="116" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E40" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F40" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G40" s="118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H40" s="119" t="n">
+        <v>3913396.13</v>
+      </c>
+      <c r="I40" s="120" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+        </is>
+      </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="30.6" customHeight="1">
+    <row r="41" ht="88" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="54" t="n"/>
+      <c r="B41" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C41" s="121" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D41" s="122" t="inlineStr">
+        <is>
+          <t>Arista Networks Inc.</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F41" s="123" t="inlineStr">
+        <is>
+          <t>Communications Equipment</t>
+        </is>
+      </c>
+      <c r="G41" s="118" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="H41" s="124" t="n">
+        <v>265705.98</v>
+      </c>
+      <c r="I41" s="125" t="inlineStr">
+        <is>
+          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+        </is>
+      </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="52" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="94" t="n"/>
-      <c r="H42" s="105" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="146" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D42" s="116" t="inlineStr">
+        <is>
+          <t>Fortinet Inc.</t>
+        </is>
+      </c>
+      <c r="E42" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F42" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G42" s="118" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="H42" s="119" t="n">
+        <v>138773.13</v>
+      </c>
+      <c r="I42" s="120" t="inlineStr">
+        <is>
+          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+        </is>
+      </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="88" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="146" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C43" s="121" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D43" s="122" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Company</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F43" s="123" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="H43" s="124" t="n">
+        <v>95407.55</v>
+      </c>
+      <c r="I43" s="125" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+        </is>
+      </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C44" s="147" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D44" s="148" t="inlineStr">
+        <is>
+          <t>Everpure Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="149" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F44" s="149" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G44" s="132" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="H44" s="150" t="n">
+        <v>49676.52</v>
+      </c>
+      <c r="I44" s="151" t="inlineStr">
+        <is>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="8" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="152" t="n"/>
+      <c r="C45" s="152" t="n"/>
+      <c r="D45" s="152" t="n"/>
+      <c r="E45" s="152" t="n"/>
+      <c r="F45" s="152" t="n"/>
+      <c r="G45" s="152" t="n"/>
+      <c r="H45" s="152" t="n"/>
+      <c r="I45" s="152" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C46" s="143" t="n"/>
+      <c r="D46" s="143" t="n"/>
+      <c r="E46" s="143" t="n"/>
+      <c r="F46" s="143" t="n"/>
+      <c r="G46" s="143" t="n"/>
+      <c r="H46" s="143" t="n"/>
+      <c r="I46" s="143" t="n"/>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="28" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C47" s="145" t="n"/>
+      <c r="D47" s="145" t="n"/>
+      <c r="E47" s="145" t="n"/>
+      <c r="F47" s="145" t="n"/>
+      <c r="G47" s="145" t="n"/>
+      <c r="H47" s="145" t="n"/>
+      <c r="I47" s="145" t="n"/>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
@@ -5890,11 +6136,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G31">
+  <conditionalFormatting sqref="G8:G44">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
@@ -586,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -922,22 +922,22 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -971,21 +971,6 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2111,7 +2096,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46310.64329707867</v>
+        <v>46311.62926232007</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2173,7 +2158,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46310.64329707867</v>
+        <v>46311.62926232007</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2306,7 +2291,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>600.1</v>
@@ -2347,7 +2332,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.413</v>
+        <v>0.443</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>15597.29</v>
@@ -2369,39 +2354,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.288</v>
+        <v>0.392</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>382.43</v>
+        <v>1545.36</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="106" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2410,12 +2395,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -2429,20 +2414,20 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.274</v>
+        <v>0.297</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>99672.56</v>
+        <v>336.54</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="106" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2451,12 +2436,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2470,20 +2455,20 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.268</v>
+        <v>0.294</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>336.54</v>
+        <v>99672.56</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2492,33 +2477,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.23</v>
+        <v>0.263</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>43014.26</v>
+        <v>382.43</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2552,7 +2537,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.226</v>
+        <v>0.241</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>398.33</v>
@@ -2593,7 +2578,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.15</v>
+        <v>0.153</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>4283.74</v>
@@ -2634,7 +2619,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>1.178</v>
+        <v>1.174</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>498.51</v>
@@ -2675,7 +2660,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.581</v>
+        <v>0.624</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>443.56</v>
@@ -2716,7 +2701,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>925.72</v>
@@ -2757,7 +2742,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.365</v>
+        <v>0.384</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>743.0700000000001</v>
@@ -2798,7 +2783,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.331</v>
+        <v>0.347</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>209743.55</v>
@@ -2811,7 +2796,7 @@
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="52" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="127" t="inlineStr">
         <is>
@@ -2820,39 +2805,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.311</v>
+        <v>0.307</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>3333.46</v>
+        <v>80962.39</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2861,39 +2846,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.307</v>
+        <v>0.269</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>80962.39</v>
+        <v>3333.46</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2902,33 +2887,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.247</v>
+        <v>0.266</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>745.59</v>
+        <v>3837.96</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2943,33 +2928,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.235</v>
+        <v>0.172</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>3837.96</v>
+        <v>6794.59</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2984,33 +2969,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>TXG</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.2</v>
+        <v>0.156</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>6794.59</v>
+        <v>4675.63</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -3018,212 +3003,128 @@
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C26" s="115" t="inlineStr">
-        <is>
-          <t>TXG</t>
-        </is>
-      </c>
-      <c r="D26" s="116" t="inlineStr">
-        <is>
-          <t>Torex Gold Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E26" s="117" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F26" s="117" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G26" s="118" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="H26" s="119" t="n">
-        <v>4675.63</v>
-      </c>
-      <c r="I26" s="120" t="inlineStr">
-        <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+      <c r="B26" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C26" s="129" t="inlineStr">
+        <is>
+          <t>WFC</t>
+        </is>
+      </c>
+      <c r="D26" s="130" t="inlineStr">
+        <is>
+          <t>Wall Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E26" s="131" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F26" s="131" t="inlineStr">
+        <is>
+          <t>Real Estate Management and Development</t>
+        </is>
+      </c>
+      <c r="G26" s="132" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="H26" s="133" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="I26" s="134" t="inlineStr">
+        <is>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="8" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C27" s="121" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D27" s="122" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F27" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G27" s="118" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H27" s="124" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I27" s="125" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
-        </is>
-      </c>
+      <c r="B27" s="135" t="n"/>
+      <c r="C27" s="136" t="n"/>
+      <c r="D27" s="137" t="n"/>
+      <c r="E27" s="138" t="n"/>
+      <c r="F27" s="138" t="n"/>
+      <c r="G27" s="139" t="n"/>
+      <c r="H27" s="140" t="n"/>
+      <c r="I27" s="141" t="n"/>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C28" s="115" t="inlineStr">
-        <is>
-          <t>CMG</t>
-        </is>
-      </c>
-      <c r="D28" s="116" t="inlineStr">
-        <is>
-          <t>Computer Modelling Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E28" s="117" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F28" s="117" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G28" s="118" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="H28" s="119" t="n">
-        <v>226.17</v>
-      </c>
-      <c r="I28" s="120" t="inlineStr">
-        <is>
-          <t>Computer Modelling Group Ltd a software and consulting technology company engages in the development and licensing of reservoir simulation and seismic interpretation software and related services</t>
-        </is>
-      </c>
+      <c r="B28" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C28" s="143" t="n"/>
+      <c r="D28" s="143" t="n"/>
+      <c r="E28" s="143" t="n"/>
+      <c r="F28" s="143" t="n"/>
+      <c r="G28" s="143" t="n"/>
+      <c r="H28" s="143" t="n"/>
+      <c r="I28" s="143" t="n"/>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C29" s="129" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
-      </c>
-      <c r="D29" s="130" t="inlineStr">
-        <is>
-          <t>Wall Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E29" s="131" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F29" s="131" t="inlineStr">
-        <is>
-          <t>Real Estate Management and Development</t>
-        </is>
-      </c>
-      <c r="G29" s="132" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H29" s="133" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="I29" s="134" t="inlineStr">
-        <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
-        </is>
-      </c>
+      <c r="B29" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C29" s="145" t="n"/>
+      <c r="D29" s="145" t="n"/>
+      <c r="E29" s="145" t="n"/>
+      <c r="F29" s="145" t="n"/>
+      <c r="G29" s="145" t="n"/>
+      <c r="H29" s="145" t="n"/>
+      <c r="I29" s="145" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="8" customHeight="1">
+    <row r="30" ht="30.6" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="135" t="n"/>
-      <c r="C30" s="136" t="n"/>
-      <c r="D30" s="137" t="n"/>
-      <c r="E30" s="138" t="n"/>
-      <c r="F30" s="138" t="n"/>
-      <c r="G30" s="139" t="n"/>
-      <c r="H30" s="140" t="n"/>
-      <c r="I30" s="141" t="n"/>
+      <c r="B30" s="48" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="89" t="n"/>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="53" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="34" customHeight="1">
+    <row r="31" ht="30.6" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C31" s="143" t="n"/>
-      <c r="D31" s="143" t="n"/>
-      <c r="E31" s="143" t="n"/>
-      <c r="F31" s="143" t="n"/>
-      <c r="G31" s="143" t="n"/>
-      <c r="H31" s="143" t="n"/>
-      <c r="I31" s="143" t="n"/>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="89" t="n"/>
+      <c r="H31" s="93" t="n"/>
+      <c r="I31" s="54" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="28" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C32" s="145" t="n"/>
-      <c r="D32" s="145" t="n"/>
-      <c r="E32" s="145" t="n"/>
-      <c r="F32" s="145" t="n"/>
-      <c r="G32" s="145" t="n"/>
-      <c r="H32" s="145" t="n"/>
-      <c r="I32" s="145" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
@@ -3452,11 +3353,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B28:I28"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G29">
+  <conditionalFormatting sqref="G8:G26">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4437,7 +4338,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46310.64329707867</v>
+        <v>46311.62926232007</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4542,7 +4443,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -4551,39 +4452,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>3.412</v>
+        <v>0.575</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>17950.14</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -4592,12 +4493,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -4607,18 +4508,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.065</v>
+        <v>0.424</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>48504.52</v>
+        <v>480788.44</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -4633,39 +4534,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Datadog Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>1.027</v>
+        <v>0.385</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>98620.67</v>
+        <v>33875.2</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Datadog Inc operates an observability and security platform for cloud applications in the United States and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4674,12 +4575,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -4689,18 +4590,18 @@
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.852</v>
+        <v>0.385</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>45576.53</v>
+        <v>26039.81</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -4715,33 +4616,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.58</v>
+        <v>0.339</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>17950.14</v>
+        <v>24969.64</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4756,33 +4657,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.428</v>
+        <v>0.334</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>480788.44</v>
+        <v>61019.13</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4797,39 +4698,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.376</v>
+        <v>0.319</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>26039.81</v>
+        <v>11772.74</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4838,39 +4739,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.322</v>
+        <v>0.312</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>11772.74</v>
+        <v>241617.28</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4879,33 +4780,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.31</v>
+        <v>0.291</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>241617.28</v>
+        <v>682021.24</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -4939,7 +4840,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.302</v>
+        <v>0.285</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>33430.82</v>
@@ -4952,7 +4853,7 @@
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -4961,39 +4862,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.278</v>
+        <v>0.262</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>682021.24</v>
+        <v>28342.5</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5002,33 +4903,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.233</v>
+        <v>0.253</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>21455.05</v>
+        <v>156513.85</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5062,7 +4963,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.231</v>
+        <v>0.24</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>48910.32</v>
@@ -5075,7 +4976,7 @@
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5084,39 +4985,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.231</v>
+        <v>0.239</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>30639.57</v>
+        <v>21455.05</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5125,39 +5026,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.23</v>
+        <v>0.235</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>404759.18</v>
+        <v>30639.57</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="126" t="inlineStr">
         <is>
@@ -5166,12 +5067,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -5185,20 +5086,20 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.203</v>
+        <v>0.232</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>677009.86</v>
+        <v>404759.18</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5207,33 +5108,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.194</v>
+        <v>0.212</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>498865.76</v>
+        <v>54537.32</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5248,33 +5149,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.186</v>
+        <v>0.209</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>183538.16</v>
+        <v>677009.86</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -5289,33 +5190,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.185</v>
+        <v>0.202</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>116683.09</v>
+        <v>498865.76</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5330,33 +5231,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.175</v>
+        <v>0.186</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>151241.83</v>
+        <v>116683.09</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5371,33 +5272,33 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.168</v>
+        <v>0.181</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>47993.25</v>
+        <v>151241.83</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>eBay Inc together with its subsidiaries operates marketplace platforms that connect buyers and sellers in the United States the United Kingdom China Germany and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
@@ -5431,7 +5332,7 @@
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.159</v>
+        <v>0.171</v>
       </c>
       <c r="H29" s="124" t="n">
         <v>108638.32</v>
@@ -5453,12 +5354,12 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
@@ -5468,18 +5369,18 @@
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.148</v>
+        <v>0.168</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>111058.59</v>
+        <v>183538.16</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -5494,12 +5395,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5509,18 +5410,18 @@
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.119</v>
+        <v>0.144</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>159089.29</v>
+        <v>111058.59</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -5535,33 +5436,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.103</v>
+        <v>0.114</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>25579.38</v>
+        <v>159089.29</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5569,46 +5470,46 @@
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B33" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>1.232</v>
+        <v>0.096</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>123883.6</v>
+        <v>25579.38</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="88" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="127" t="inlineStr">
         <is>
@@ -5617,39 +5518,39 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>NetApp Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>1.029</v>
+        <v>1.24</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>46186.75</v>
+        <v>123883.6</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="52" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="127" t="inlineStr">
         <is>
@@ -5658,39 +5559,39 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.986</v>
+        <v>0.992</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>122343.55</v>
+        <v>48504.52</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row r="36" ht="88" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="127" t="inlineStr">
         <is>
@@ -5699,12 +5600,12 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
@@ -5718,20 +5619,20 @@
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.903</v>
+        <v>0.979</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>109006.53</v>
+        <v>122343.55</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="70" customHeight="1">
+    <row r="37" ht="88" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="127" t="inlineStr">
         <is>
@@ -5740,12 +5641,12 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>F5 Inc.</t>
+          <t>NetApp Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
@@ -5755,24 +5656,24 @@
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.43</v>
+        <v>0.945</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>26429.32</v>
+        <v>46186.75</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>F5 Inc provides multicloud application security and delivery solutions in the United States Europe the Middle East Africa and the Asia Pacific region</t>
+          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="127" t="inlineStr">
         <is>
@@ -5781,39 +5682,39 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.374</v>
+        <v>0.894</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>21029.38</v>
+        <v>109006.53</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="88" customHeight="1">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
       <c r="B39" s="127" t="inlineStr">
         <is>
@@ -5822,39 +5723,39 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.354</v>
+        <v>0.848</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>459224.48</v>
+        <v>45576.53</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States the United Kingdom and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="70" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="127" t="inlineStr">
         <is>
@@ -5863,12 +5764,12 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
@@ -5882,14 +5783,14 @@
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.29</v>
+        <v>0.373</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>3913396.13</v>
+        <v>21029.38</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
@@ -5904,12 +5805,12 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Arista Networks Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
@@ -5919,18 +5820,18 @@
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.091</v>
+        <v>0.299</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>265705.98</v>
+        <v>459224.48</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Arista Networks Inc engages in the development marketing and sale of data-driven client to cloud networking solutions for AI data center campus and routing environments in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>Palantir Technologies Inc builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -5945,39 +5846,39 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Fortinet Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>1.175</v>
+        <v>2.935</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>138773.13</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Fortinet Inc provides cybersecurity and convergence of networking and security solutions worldwide</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="88" customHeight="1">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="146" t="inlineStr">
         <is>
@@ -5986,12 +5887,12 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company</t>
+          <t>Everpure Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
@@ -6005,14 +5906,14 @@
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>1.122</v>
+        <v>0.866</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>95407.55</v>
+        <v>49676.52</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company together with its subsidiaries develops intelligent solutions in the United States the Americas Europe the Middle East Africa the Asia Pacific Japan and internationally</t>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
@@ -6025,35 +5926,35 @@
           <t>STRK</t>
         </is>
       </c>
-      <c r="C44" s="147" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="D44" s="148" t="inlineStr">
-        <is>
-          <t>Everpure Inc.</t>
-        </is>
-      </c>
-      <c r="E44" s="149" t="inlineStr">
+      <c r="C44" s="129" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D44" s="130" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E44" s="131" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F44" s="149" t="inlineStr">
-        <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+      <c r="F44" s="131" t="inlineStr">
+        <is>
+          <t>Software</t>
         </is>
       </c>
       <c r="G44" s="132" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="H44" s="150" t="n">
-        <v>49676.52</v>
-      </c>
-      <c r="I44" s="151" t="inlineStr">
-        <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+        <v>0.278</v>
+      </c>
+      <c r="H44" s="133" t="n">
+        <v>3913396.13</v>
+      </c>
+      <c r="I44" s="134" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6061,14 +5962,14 @@
     </row>
     <row r="45" ht="8" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="152" t="n"/>
-      <c r="C45" s="152" t="n"/>
-      <c r="D45" s="152" t="n"/>
-      <c r="E45" s="152" t="n"/>
-      <c r="F45" s="152" t="n"/>
-      <c r="G45" s="152" t="n"/>
-      <c r="H45" s="152" t="n"/>
-      <c r="I45" s="152" t="n"/>
+      <c r="B45" s="147" t="n"/>
+      <c r="C45" s="147" t="n"/>
+      <c r="D45" s="147" t="n"/>
+      <c r="E45" s="147" t="n"/>
+      <c r="F45" s="147" t="n"/>
+      <c r="G45" s="147" t="n"/>
+      <c r="H45" s="147" t="n"/>
+      <c r="I45" s="147" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -383,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -557,30 +557,6 @@
       <bottom style="thin">
         <color rgb="FFC67A29"/>
       </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2"/>
-      </left>
-      <right style="medium">
-        <color theme="2"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2"/>
-      </left>
-      <right style="medium">
-        <color theme="2"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -2096,7 +2072,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46311.62926232007</v>
+        <v>46314.72081556527</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2158,7 +2134,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46311.62926232007</v>
+        <v>46314.72081556527</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2263,7 +2239,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2272,39 +2248,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.666</v>
+        <v>0.657</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>600.1</v>
+        <v>884.7</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2313,39 +2289,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.443</v>
+        <v>0.513</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>15597.29</v>
+        <v>600.1</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="88" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2354,12 +2330,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2373,14 +2349,14 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.392</v>
+        <v>0.44</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1545.36</v>
+        <v>804.05</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2395,12 +2371,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -2414,20 +2390,20 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.297</v>
+        <v>0.411</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>336.54</v>
+        <v>15597.29</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="106" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2436,12 +2412,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2455,20 +2431,20 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.294</v>
+        <v>0.41</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>99672.56</v>
+        <v>1545.36</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2477,39 +2453,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.263</v>
+        <v>0.306</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>382.43</v>
+        <v>336.54</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="106" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2518,12 +2494,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2533,24 +2509,24 @@
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.241</v>
+        <v>0.297</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>398.33</v>
+        <v>373.79</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2559,53 +2535,53 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>POU</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>Paramount Resources Ltd.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.153</v>
+        <v>0.288</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>4283.74</v>
+        <v>3216.97</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>Paramount Resources Ltd an energy company explores for and develops conventional and unconventional petroleum and natural gas reserves and resources in Canada</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="106" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B16" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
@@ -2619,14 +2595,14 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>1.174</v>
+        <v>0.274</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>498.51</v>
+        <v>99672.56</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2634,40 +2610,40 @@
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B17" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>FTG</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.624</v>
+        <v>0.268</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>443.56</v>
+        <v>4428.98</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
@@ -2675,19 +2651,19 @@
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -2701,14 +2677,14 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.446</v>
+        <v>0.239</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>925.72</v>
+        <v>2245.27</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2716,81 +2692,81 @@
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.384</v>
+        <v>0.205</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>35208.26</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="88" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.347</v>
+        <v>0.174</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>209743.55</v>
+        <v>389.1</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
@@ -2798,128 +2774,128 @@
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.307</v>
+        <v>0.165</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>80962.39</v>
+        <v>4283.74</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="106" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.269</v>
+        <v>0.16</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>3333.46</v>
+        <v>398.33</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="88" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.266</v>
+        <v>0.143</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>3837.96</v>
+        <v>382.43</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2928,33 +2904,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.172</v>
+        <v>1.038</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>6794.59</v>
+        <v>498.51</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2969,227 +2945,451 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>TXG</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.156</v>
+        <v>0.541</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>4675.63</v>
+        <v>925.72</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C26" s="129" t="inlineStr">
-        <is>
-          <t>WFC</t>
-        </is>
-      </c>
-      <c r="D26" s="130" t="inlineStr">
-        <is>
-          <t>Wall Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E26" s="131" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F26" s="131" t="inlineStr">
-        <is>
-          <t>Real Estate Management and Development</t>
-        </is>
-      </c>
-      <c r="G26" s="132" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="H26" s="133" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="I26" s="134" t="inlineStr">
-        <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C26" s="115" t="inlineStr">
+        <is>
+          <t>ALC</t>
+        </is>
+      </c>
+      <c r="D26" s="116" t="inlineStr">
+        <is>
+          <t>Algoma Central Corporation</t>
+        </is>
+      </c>
+      <c r="E26" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F26" s="117" t="inlineStr">
+        <is>
+          <t>Marine Transportation</t>
+        </is>
+      </c>
+      <c r="G26" s="118" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="H26" s="119" t="n">
+        <v>743.0700000000001</v>
+      </c>
+      <c r="I26" s="120" t="inlineStr">
+        <is>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="8" customHeight="1">
+    <row r="27" ht="88" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="135" t="n"/>
-      <c r="C27" s="136" t="n"/>
-      <c r="D27" s="137" t="n"/>
-      <c r="E27" s="138" t="n"/>
-      <c r="F27" s="138" t="n"/>
-      <c r="G27" s="139" t="n"/>
-      <c r="H27" s="140" t="n"/>
-      <c r="I27" s="141" t="n"/>
+      <c r="B27" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C27" s="121" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="D27" s="122" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F27" s="123" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="G27" s="118" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H27" s="124" t="n">
+        <v>209743.55</v>
+      </c>
+      <c r="I27" s="125" t="inlineStr">
+        <is>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+        </is>
+      </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C28" s="143" t="n"/>
-      <c r="D28" s="143" t="n"/>
-      <c r="E28" s="143" t="n"/>
-      <c r="F28" s="143" t="n"/>
-      <c r="G28" s="143" t="n"/>
-      <c r="H28" s="143" t="n"/>
-      <c r="I28" s="143" t="n"/>
+      <c r="B28" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C28" s="115" t="inlineStr">
+        <is>
+          <t>KXS</t>
+        </is>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F28" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G28" s="118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H28" s="119" t="n">
+        <v>3333.46</v>
+      </c>
+      <c r="I28" s="120" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+        </is>
+      </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C29" s="145" t="n"/>
-      <c r="D29" s="145" t="n"/>
-      <c r="E29" s="145" t="n"/>
-      <c r="F29" s="145" t="n"/>
-      <c r="G29" s="145" t="n"/>
-      <c r="H29" s="145" t="n"/>
-      <c r="I29" s="145" t="n"/>
+      <c r="B29" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D29" s="122" t="inlineStr">
+        <is>
+          <t>Suncor Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F29" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G29" s="118" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="H29" s="124" t="n">
+        <v>80962.39</v>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+        </is>
+      </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="30.6" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="n"/>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="40" t="n"/>
-      <c r="G30" s="89" t="n"/>
-      <c r="H30" s="91" t="n"/>
-      <c r="I30" s="53" t="n"/>
+      <c r="B30" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C30" s="115" t="inlineStr">
+        <is>
+          <t>GEI</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F30" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G30" s="118" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="H30" s="119" t="n">
+        <v>3837.96</v>
+      </c>
+      <c r="I30" s="120" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+        </is>
+      </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="30.6" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="89" t="n"/>
-      <c r="H31" s="93" t="n"/>
-      <c r="I31" s="54" t="n"/>
+      <c r="B31" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C31" s="121" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="D31" s="122" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F31" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="H31" s="124" t="n">
+        <v>6794.59</v>
+      </c>
+      <c r="I31" s="125" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="91" t="n"/>
-      <c r="I32" s="53" t="n"/>
+      <c r="B32" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C32" s="115" t="inlineStr">
+        <is>
+          <t>TXG</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>Torex Gold Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="117" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F32" s="117" t="inlineStr">
+        <is>
+          <t>Metals and Mining</t>
+        </is>
+      </c>
+      <c r="G32" s="118" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="H32" s="119" t="n">
+        <v>4675.63</v>
+      </c>
+      <c r="I32" s="120" t="inlineStr">
+        <is>
+          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+        </is>
+      </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="20.4" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="89" t="n"/>
-      <c r="H33" s="93" t="n"/>
-      <c r="I33" s="54" t="n"/>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>NWC</t>
+        </is>
+      </c>
+      <c r="D33" s="122" t="inlineStr">
+        <is>
+          <t>The North West Company Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples Distribution and Retail</t>
+        </is>
+      </c>
+      <c r="G33" s="118" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="H33" s="124" t="n">
+        <v>1823.99</v>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+        </is>
+      </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="30.6" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="40" t="n"/>
-      <c r="F34" s="40" t="n"/>
-      <c r="G34" s="89" t="n"/>
-      <c r="H34" s="91" t="n"/>
-      <c r="I34" s="53" t="n"/>
+      <c r="B34" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C34" s="129" t="inlineStr">
+        <is>
+          <t>GUD</t>
+        </is>
+      </c>
+      <c r="D34" s="130" t="inlineStr">
+        <is>
+          <t>Knight Therapeutics Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="131" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F34" s="131" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G34" s="132" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="H34" s="133" t="n">
+        <v>732.01</v>
+      </c>
+      <c r="I34" s="134" t="inlineStr">
+        <is>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+        </is>
+      </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="30.6" customHeight="1">
+    <row r="35" ht="8" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="89" t="n"/>
-      <c r="H35" s="93" t="n"/>
-      <c r="I35" s="54" t="n"/>
+      <c r="B35" s="135" t="n"/>
+      <c r="C35" s="136" t="n"/>
+      <c r="D35" s="137" t="n"/>
+      <c r="E35" s="138" t="n"/>
+      <c r="F35" s="138" t="n"/>
+      <c r="G35" s="139" t="n"/>
+      <c r="H35" s="140" t="n"/>
+      <c r="I35" s="141" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="40.8" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="40" t="n"/>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="89" t="n"/>
-      <c r="H36" s="91" t="n"/>
-      <c r="I36" s="53" t="n"/>
+      <c r="B36" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C36" s="143" t="n"/>
+      <c r="D36" s="143" t="n"/>
+      <c r="E36" s="143" t="n"/>
+      <c r="F36" s="143" t="n"/>
+      <c r="G36" s="143" t="n"/>
+      <c r="H36" s="143" t="n"/>
+      <c r="I36" s="143" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="89" t="n"/>
-      <c r="H37" s="93" t="n"/>
-      <c r="I37" s="54" t="n"/>
+      <c r="B37" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C37" s="145" t="n"/>
+      <c r="D37" s="145" t="n"/>
+      <c r="E37" s="145" t="n"/>
+      <c r="F37" s="145" t="n"/>
+      <c r="G37" s="145" t="n"/>
+      <c r="H37" s="145" t="n"/>
+      <c r="I37" s="145" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -3353,11 +3553,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G26">
+  <conditionalFormatting sqref="G8:G34">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4298,7 +4498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4338,7 +4538,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46311.62926232007</v>
+        <v>46314.72081556527</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4443,7 +4643,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -4452,33 +4652,33 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.575</v>
+        <v>0.442</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>17950.14</v>
+        <v>104249.82</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
@@ -4512,7 +4712,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.424</v>
+        <v>0.434</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>480788.44</v>
@@ -4525,7 +4725,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4534,39 +4734,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.385</v>
+        <v>0.405</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>33875.2</v>
+        <v>26039.81</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4575,33 +4775,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.385</v>
+        <v>0.381</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>26039.81</v>
+        <v>33875.2</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -4635,7 +4835,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>24969.64</v>
@@ -4657,39 +4857,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.334</v>
+        <v>0.321</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>61019.13</v>
+        <v>241617.28</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="88" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4698,39 +4898,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.319</v>
+        <v>0.309</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>11772.74</v>
+        <v>15537.74</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4739,33 +4939,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.312</v>
+        <v>0.307</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>241617.28</v>
+        <v>11772.74</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -4799,7 +4999,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.291</v>
+        <v>0.298</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>682021.24</v>
@@ -4812,7 +5012,7 @@
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -4821,39 +5021,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.285</v>
+        <v>0.289</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>33430.82</v>
+        <v>21455.05</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -4862,33 +5062,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.262</v>
+        <v>0.28</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>28342.5</v>
+        <v>20324.32</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -4903,39 +5103,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.253</v>
+        <v>0.269</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>156513.85</v>
+        <v>371563.85</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="106" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -4944,39 +5144,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.24</v>
+        <v>0.261</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>48910.32</v>
+        <v>116683.09</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -4985,39 +5185,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.239</v>
+        <v>0.26</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>21455.05</v>
+        <v>28342.5</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5026,12 +5226,12 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
@@ -5041,24 +5241,24 @@
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.235</v>
+        <v>0.254</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>30639.57</v>
+        <v>54537.32</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="126" t="inlineStr">
         <is>
@@ -5067,39 +5267,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.232</v>
+        <v>0.242</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>404759.18</v>
+        <v>30639.57</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="106" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5108,12 +5308,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -5123,18 +5323,18 @@
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.212</v>
+        <v>0.241</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>54537.32</v>
+        <v>48910.32</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5149,33 +5349,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.209</v>
+        <v>0.227</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>677009.86</v>
+        <v>33430.82</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -5190,39 +5390,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.202</v>
+        <v>0.227</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>498865.76</v>
+        <v>151241.83</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="126" t="inlineStr">
         <is>
@@ -5231,33 +5431,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.186</v>
+        <v>0.226</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>116683.09</v>
+        <v>404759.18</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5272,39 +5472,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.181</v>
+        <v>0.209</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>151241.83</v>
+        <v>677009.86</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5313,33 +5513,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.171</v>
+        <v>0.208</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>108638.32</v>
+        <v>498865.76</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5354,39 +5554,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.168</v>
+        <v>0.2</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>183538.16</v>
+        <v>156513.85</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="88" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5395,33 +5595,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.144</v>
+        <v>0.2</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>111058.59</v>
+        <v>75763.52</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -5436,12 +5636,12 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
@@ -5451,18 +5651,18 @@
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.114</v>
+        <v>0.176</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>159089.29</v>
+        <v>183538.16</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5496,7 +5696,7 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.096</v>
+        <v>0.147</v>
       </c>
       <c r="H33" s="124" t="n">
         <v>25579.38</v>
@@ -5511,60 +5711,60 @@
     </row>
     <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B34" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>1.24</v>
+        <v>0.136</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>123883.6</v>
+        <v>111058.59</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="52" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B35" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
@@ -5574,141 +5774,141 @@
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.992</v>
+        <v>0.133</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>48504.52</v>
+        <v>159089.29</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="88" customHeight="1">
+    <row r="36" ht="52" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B36" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.979</v>
+        <v>0.128</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>122343.55</v>
+        <v>22965.61</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Church &amp; Dwight Co</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="88" customHeight="1">
+    <row r="37" ht="52" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B37" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>NetApp Inc.</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.945</v>
+        <v>0.121</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>46186.75</v>
+        <v>66372.58</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>NetApp Inc develops enterprise software systems and services to transform data infrastructures in the United States Canada Latin America Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row r="38" ht="52" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B38" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Cencora Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.894</v>
+        <v>0.104</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>109006.53</v>
+        <v>61416.01</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
@@ -5716,87 +5916,87 @@
     </row>
     <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B39" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.848</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>45576.53</v>
+        <v>27315.89</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="52" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B40" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.373</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>21029.38</v>
+        <v>31594.32</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="88" customHeight="1">
+    <row r="41" ht="70" customHeight="1">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="127" t="inlineStr">
         <is>
@@ -5805,53 +6005,53 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.299</v>
+        <v>1.164</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>459224.48</v>
+        <v>123883.6</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States the United Kingdom and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="52" customHeight="1" thickBot="1">
+    <row r="42" ht="70" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B42" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
@@ -5861,187 +6061,395 @@
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>2.935</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>45576.53</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="70" customHeight="1">
+    <row r="43" ht="88" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B43" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.866</v>
+        <v>0.89</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>49676.52</v>
+        <v>122343.55</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="70" customHeight="1" thickBot="1">
+    <row r="44" ht="52" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C44" s="129" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="D44" s="130" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="E44" s="131" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F44" s="131" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G44" s="132" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="H44" s="133" t="n">
-        <v>3913396.13</v>
-      </c>
-      <c r="I44" s="134" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+      <c r="B44" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C44" s="115" t="inlineStr">
+        <is>
+          <t>HUM</t>
+        </is>
+      </c>
+      <c r="D44" s="116" t="inlineStr">
+        <is>
+          <t>Humana Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F44" s="117" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G44" s="118" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="H44" s="119" t="n">
+        <v>48504.52</v>
+      </c>
+      <c r="I44" s="120" t="inlineStr">
+        <is>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="8" customHeight="1">
+    <row r="45" ht="70" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="147" t="n"/>
-      <c r="C45" s="147" t="n"/>
-      <c r="D45" s="147" t="n"/>
-      <c r="E45" s="147" t="n"/>
-      <c r="F45" s="147" t="n"/>
-      <c r="G45" s="147" t="n"/>
-      <c r="H45" s="147" t="n"/>
-      <c r="I45" s="147" t="n"/>
+      <c r="B45" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C45" s="121" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="D45" s="122" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="E45" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F45" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G45" s="118" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="H45" s="124" t="n">
+        <v>109006.53</v>
+      </c>
+      <c r="I45" s="125" t="inlineStr">
+        <is>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+        </is>
+      </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="34" customHeight="1">
+    <row r="46" ht="52" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C46" s="143" t="n"/>
-      <c r="D46" s="143" t="n"/>
-      <c r="E46" s="143" t="n"/>
-      <c r="F46" s="143" t="n"/>
-      <c r="G46" s="143" t="n"/>
-      <c r="H46" s="143" t="n"/>
-      <c r="I46" s="143" t="n"/>
+      <c r="B46" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C46" s="115" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D46" s="116" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="E46" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F46" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G46" s="118" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="H46" s="119" t="n">
+        <v>21029.38</v>
+      </c>
+      <c r="I46" s="120" t="inlineStr">
+        <is>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="28" customHeight="1" thickBot="1">
+    <row r="47" ht="52" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C47" s="145" t="n"/>
-      <c r="D47" s="145" t="n"/>
-      <c r="E47" s="145" t="n"/>
-      <c r="F47" s="145" t="n"/>
-      <c r="G47" s="145" t="n"/>
-      <c r="H47" s="145" t="n"/>
-      <c r="I47" s="145" t="n"/>
+      <c r="B47" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C47" s="121" t="inlineStr">
+        <is>
+          <t>MCK</t>
+        </is>
+      </c>
+      <c r="D47" s="122" t="inlineStr">
+        <is>
+          <t>McKesson Corporation</t>
+        </is>
+      </c>
+      <c r="E47" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F47" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G47" s="118" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H47" s="124" t="n">
+        <v>108638.32</v>
+      </c>
+      <c r="I47" s="125" t="inlineStr">
+        <is>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="52" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
-      <c r="H48" s="43" t="n"/>
-      <c r="I48" s="43" t="n"/>
+      <c r="B48" s="146" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C48" s="115" t="inlineStr">
+        <is>
+          <t>MRNA</t>
+        </is>
+      </c>
+      <c r="D48" s="116" t="inlineStr">
+        <is>
+          <t>Moderna Inc.</t>
+        </is>
+      </c>
+      <c r="E48" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F48" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G48" s="118" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="H48" s="119" t="n">
+        <v>74971.71000000001</v>
+      </c>
+      <c r="I48" s="120" t="inlineStr">
+        <is>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+        </is>
+      </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="47" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="47" t="n"/>
-      <c r="E49" s="47" t="n"/>
-      <c r="F49" s="47" t="n"/>
-      <c r="G49" s="47" t="n"/>
-      <c r="H49" s="47" t="n"/>
-      <c r="I49" s="47" t="n"/>
+      <c r="B49" s="146" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C49" s="121" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D49" s="122" t="inlineStr">
+        <is>
+          <t>Everpure Inc.</t>
+        </is>
+      </c>
+      <c r="E49" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F49" s="123" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G49" s="118" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H49" s="124" t="n">
+        <v>49676.52</v>
+      </c>
+      <c r="I49" s="125" t="inlineStr">
+        <is>
+          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="70" customHeight="1">
+      <c r="B50" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C50" s="129" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D50" s="130" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E50" s="131" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F50" s="131" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G50" s="132" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="H50" s="133" t="n">
+        <v>3913396.13</v>
+      </c>
+      <c r="I50" s="134" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="8" customHeight="1">
+      <c r="B51" s="147" t="n"/>
+      <c r="C51" s="147" t="n"/>
+      <c r="D51" s="147" t="n"/>
+      <c r="E51" s="147" t="n"/>
+      <c r="F51" s="147" t="n"/>
+      <c r="G51" s="147" t="n"/>
+      <c r="H51" s="147" t="n"/>
+      <c r="I51" s="147" t="n"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="B52" s="142" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C52" s="143" t="n"/>
+      <c r="D52" s="143" t="n"/>
+      <c r="E52" s="143" t="n"/>
+      <c r="F52" s="143" t="n"/>
+      <c r="G52" s="143" t="n"/>
+      <c r="H52" s="143" t="n"/>
+      <c r="I52" s="143" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="B53" s="144" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C53" s="145" t="n"/>
+      <c r="D53" s="145" t="n"/>
+      <c r="E53" s="145" t="n"/>
+      <c r="F53" s="145" t="n"/>
+      <c r="G53" s="145" t="n"/>
+      <c r="H53" s="145" t="n"/>
+      <c r="I53" s="145" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B53:I53"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="B46:I46"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G44">
+  <conditionalFormatting sqref="G8:G50">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -945,9 +945,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2072,7 +2069,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46314.72081556527</v>
+        <v>46315.64681052112</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2134,7 +2131,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46314.72081556527</v>
+        <v>46315.64681052112</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2267,7 +2264,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>884.7</v>
@@ -2289,39 +2286,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.513</v>
+        <v>0.399</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>600.1</v>
+        <v>804.05</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2330,12 +2327,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2349,20 +2346,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.44</v>
+        <v>0.363</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>804.05</v>
+        <v>15597.29</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2371,12 +2368,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -2390,20 +2387,20 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.411</v>
+        <v>0.363</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>15597.29</v>
+        <v>1545.36</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2412,33 +2409,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.41</v>
+        <v>0.311</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>1545.36</v>
+        <v>43014.26</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -2453,12 +2450,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -2472,14 +2469,14 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.306</v>
+        <v>0.287</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>336.54</v>
+        <v>373.79</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2494,12 +2491,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2513,14 +2510,14 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.297</v>
+        <v>0.269</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>373.79</v>
+        <v>336.54</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -2535,39 +2532,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>POU</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Paramount Resources Ltd.</t>
+          <t>Open Text Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.288</v>
+        <v>0.249</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>3216.97</v>
+        <v>5405.28</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Paramount Resources Ltd an energy company explores for and develops conventional and unconventional petroleum and natural gas reserves and resources in Canada</t>
+          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="106" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2576,12 +2573,12 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
@@ -2595,20 +2592,20 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.274</v>
+        <v>0.228</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>99672.56</v>
+        <v>4428.98</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2617,33 +2614,33 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.268</v>
+        <v>0.222</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>4428.98</v>
+        <v>35208.26</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
@@ -2677,7 +2674,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.239</v>
+        <v>0.205</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>2245.27</v>
@@ -2690,7 +2687,7 @@
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -2699,12 +2696,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -2714,18 +2711,18 @@
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.205</v>
+        <v>0.204</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>35208.26</v>
+        <v>382.43</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
@@ -2759,7 +2756,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.174</v>
+        <v>0.19</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>389.1</v>
@@ -2800,7 +2797,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.165</v>
+        <v>0.178</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>4283.74</v>
@@ -2841,7 +2838,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.16</v>
+        <v>0.113</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>398.33</v>
@@ -2854,42 +2851,42 @@
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="88" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.143</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>382.43</v>
+        <v>498.51</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2904,39 +2901,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>1.038</v>
+        <v>0.699</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>498.51</v>
+        <v>600.1</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2945,39 +2942,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.541</v>
+        <v>0.498</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>925.72</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2986,33 +2983,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.463</v>
+        <v>0.478</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>743.0700000000001</v>
+        <v>925.72</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3046,7 +3043,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.335</v>
+        <v>0.437</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>209743.55</v>
@@ -3087,7 +3084,7 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.29</v>
+        <v>0.391</v>
       </c>
       <c r="H28" s="119" t="n">
         <v>3333.46</v>
@@ -3100,7 +3097,7 @@
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3109,39 +3106,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.289</v>
+        <v>0.265</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>80962.39</v>
+        <v>6794.59</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -3150,12 +3147,12 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
@@ -3169,20 +3166,20 @@
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.241</v>
+        <v>0.245</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>3837.96</v>
+        <v>80962.39</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="106" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3191,33 +3188,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.196</v>
+        <v>0.239</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>6794.59</v>
+        <v>99672.56</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -3232,33 +3229,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>TXG</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.178</v>
+        <v>0.227</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>4675.63</v>
+        <v>3837.96</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc a mineral exploration company engages in the acquisition exploration and development of mineral properties in Mexico and the United States</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -3292,7 +3289,7 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.117</v>
+        <v>0.128</v>
       </c>
       <c r="H33" s="124" t="n">
         <v>1823.99</v>
@@ -3333,7 +3330,7 @@
         </is>
       </c>
       <c r="G34" s="132" t="n">
-        <v>0.524</v>
+        <v>0.531</v>
       </c>
       <c r="H34" s="133" t="n">
         <v>732.01</v>
@@ -4498,7 +4495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4538,7 +4535,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46314.72081556527</v>
+        <v>46315.64681052112</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4643,7 +4640,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -4652,39 +4649,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Charles River Laboratories International Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.442</v>
+        <v>0.864</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>104249.82</v>
+        <v>14054.04</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -4693,39 +4690,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.434</v>
+        <v>0.492</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>480788.44</v>
+        <v>104249.82</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="88" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4734,12 +4731,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -4753,20 +4750,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.405</v>
+        <v>0.467</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>26039.81</v>
+        <v>241617.28</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4775,39 +4772,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.381</v>
+        <v>0.457</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>33875.2</v>
+        <v>480788.44</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4816,33 +4813,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.338</v>
+        <v>0.457</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>24969.64</v>
+        <v>11772.74</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -4857,12 +4854,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4872,24 +4869,24 @@
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.321</v>
+        <v>0.419</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>241617.28</v>
+        <v>1054668.83</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4898,39 +4895,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.309</v>
+        <v>0.394</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>15537.74</v>
+        <v>33875.2</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4939,12 +4936,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -4958,20 +4955,20 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.307</v>
+        <v>0.374</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>11772.74</v>
+        <v>116683.09</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4980,39 +4977,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.298</v>
+        <v>0.329</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>682021.24</v>
+        <v>24969.64</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="88" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5021,33 +5018,33 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.289</v>
+        <v>0.324</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>21455.05</v>
+        <v>28342.5</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -5062,33 +5059,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.28</v>
+        <v>0.303</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>20324.32</v>
+        <v>21455.05</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5103,33 +5100,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.269</v>
+        <v>0.295</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>371563.85</v>
+        <v>33430.82</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5144,39 +5141,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.261</v>
+        <v>0.283</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>116683.09</v>
+        <v>15537.74</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5185,39 +5182,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.26</v>
+        <v>0.268</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>28342.5</v>
+        <v>20324.32</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="106" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5226,12 +5223,12 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
@@ -5241,18 +5238,18 @@
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.254</v>
+        <v>0.263</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>54537.32</v>
+        <v>48910.32</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5267,12 +5264,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -5286,20 +5283,20 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.242</v>
+        <v>0.261</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>30639.57</v>
+        <v>151241.83</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="106" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5308,12 +5305,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -5323,24 +5320,24 @@
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.241</v>
+        <v>0.254</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>48910.32</v>
+        <v>54537.32</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="126" t="inlineStr">
         <is>
@@ -5349,12 +5346,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5364,18 +5361,18 @@
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.227</v>
+        <v>0.25</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>33430.82</v>
+        <v>26039.81</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -5390,39 +5387,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.227</v>
+        <v>0.246</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>151241.83</v>
+        <v>25579.38</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="126" t="inlineStr">
         <is>
@@ -5431,33 +5428,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.226</v>
+        <v>0.244</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>404759.18</v>
+        <v>498865.76</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5472,39 +5469,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.209</v>
+        <v>0.235</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>677009.86</v>
+        <v>371563.85</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5513,33 +5510,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.208</v>
+        <v>0.209</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>498865.76</v>
+        <v>404759.18</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5554,39 +5551,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.2</v>
+        <v>0.184</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>156513.85</v>
+        <v>183538.16</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="88" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5595,12 +5592,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>EOG Resources Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5614,20 +5611,20 @@
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.2</v>
+        <v>0.183</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>75763.52</v>
+        <v>677009.86</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="126" t="inlineStr">
         <is>
@@ -5636,33 +5633,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.176</v>
+        <v>0.182</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>183538.16</v>
+        <v>75763.52</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5677,33 +5674,33 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.147</v>
+        <v>0.177</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>25579.38</v>
+        <v>156513.85</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -5718,12 +5715,12 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
@@ -5733,18 +5730,18 @@
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.136</v>
+        <v>0.168</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>111058.59</v>
+        <v>159089.29</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -5759,12 +5756,12 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
@@ -5774,18 +5771,18 @@
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.133</v>
+        <v>0.144</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>159089.29</v>
+        <v>111058.59</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
@@ -5819,7 +5816,7 @@
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.128</v>
+        <v>0.121</v>
       </c>
       <c r="H36" s="119" t="n">
         <v>22965.61</v>
@@ -5832,7 +5829,7 @@
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="52" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="126" t="inlineStr">
         <is>
@@ -5841,39 +5838,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Republic Services Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
         <v>0.121</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>66372.58</v>
+        <v>31594.32</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -5882,39 +5879,39 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Cencora Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>61416.01</v>
+        <v>27315.89</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row r="39" ht="52" customHeight="1">
       <c r="A39" s="28" t="n"/>
       <c r="B39" s="126" t="inlineStr">
         <is>
@@ -5923,33 +5920,33 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Dollar General Corporation</t>
+          <t>Cencora Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>27315.89</v>
+        <v>61416.01</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
+          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
@@ -5964,80 +5961,80 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>31594.32</v>
+        <v>12857.61</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="70" customHeight="1">
+    <row r="41" ht="52" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B41" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>1.164</v>
+        <v>0.091</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>123883.6</v>
+        <v>66372.58</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="70" customHeight="1" thickBot="1">
+    <row r="42" ht="52" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
       <c r="B42" s="127" t="inlineStr">
         <is>
@@ -6046,12 +6043,12 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
@@ -6061,24 +6058,24 @@
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.9340000000000001</v>
+        <v>3.421</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>45576.53</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="88" customHeight="1">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6087,12 +6084,12 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
@@ -6106,20 +6103,20 @@
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.89</v>
+        <v>1.136</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>122343.55</v>
+        <v>123883.6</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="52" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
       <c r="B44" s="127" t="inlineStr">
         <is>
@@ -6128,12 +6125,12 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
@@ -6143,24 +6140,24 @@
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.888</v>
+        <v>1.043</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>48504.52</v>
+        <v>45576.53</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="70" customHeight="1">
+    <row r="45" ht="52" customHeight="1">
       <c r="A45" s="43" t="n"/>
       <c r="B45" s="127" t="inlineStr">
         <is>
@@ -6169,39 +6166,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.841</v>
+        <v>0.993</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>109006.53</v>
+        <v>48504.52</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="52" customHeight="1">
+    <row r="46" ht="88" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6210,39 +6207,39 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.374</v>
+        <v>0.859</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>21029.38</v>
+        <v>122343.55</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="52" customHeight="1" thickBot="1">
+    <row r="47" ht="70" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6251,33 +6248,33 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.213</v>
+        <v>0.831</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>108638.32</v>
+        <v>109006.53</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6285,171 +6282,247 @@
     </row>
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B48" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>3.023</v>
+        <v>0.423</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>21029.38</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="1">
+    <row r="49" ht="52" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="146" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B49" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Everpure Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.844</v>
+        <v>0.325</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>49676.52</v>
+        <v>682021.24</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Everpure Inc provides data storage and management technologies products and services in the United States and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
     <row r="50" ht="70" customHeight="1">
-      <c r="B50" s="128" t="inlineStr">
+      <c r="B50" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C50" s="115" t="inlineStr">
+        <is>
+          <t>MTD</t>
+        </is>
+      </c>
+      <c r="D50" s="116" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo International Inc.</t>
+        </is>
+      </c>
+      <c r="E50" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F50" s="117" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G50" s="118" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H50" s="119" t="n">
+        <v>30639.57</v>
+      </c>
+      <c r="I50" s="120" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="B51" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C51" s="121" t="inlineStr">
+        <is>
+          <t>MCK</t>
+        </is>
+      </c>
+      <c r="D51" s="122" t="inlineStr">
+        <is>
+          <t>McKesson Corporation</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F51" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G51" s="118" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="H51" s="124" t="n">
+        <v>108638.32</v>
+      </c>
+      <c r="I51" s="125" t="inlineStr">
+        <is>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1">
+      <c r="B52" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C50" s="129" t="inlineStr">
+      <c r="C52" s="129" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D50" s="130" t="inlineStr">
+      <c r="D52" s="130" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="E50" s="131" t="inlineStr">
+      <c r="E52" s="131" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F50" s="131" t="inlineStr">
+      <c r="F52" s="131" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G50" s="132" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="H50" s="133" t="n">
+      <c r="G52" s="132" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="H52" s="133" t="n">
         <v>3913396.13</v>
       </c>
-      <c r="I50" s="134" t="inlineStr">
+      <c r="I52" s="134" t="inlineStr">
         <is>
           <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="8" customHeight="1">
-      <c r="B51" s="147" t="n"/>
-      <c r="C51" s="147" t="n"/>
-      <c r="D51" s="147" t="n"/>
-      <c r="E51" s="147" t="n"/>
-      <c r="F51" s="147" t="n"/>
-      <c r="G51" s="147" t="n"/>
-      <c r="H51" s="147" t="n"/>
-      <c r="I51" s="147" t="n"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="B52" s="142" t="inlineStr">
+    <row r="53" ht="8" customHeight="1">
+      <c r="B53" s="146" t="n"/>
+      <c r="C53" s="146" t="n"/>
+      <c r="D53" s="146" t="n"/>
+      <c r="E53" s="146" t="n"/>
+      <c r="F53" s="146" t="n"/>
+      <c r="G53" s="146" t="n"/>
+      <c r="H53" s="146" t="n"/>
+      <c r="I53" s="146" t="n"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="B54" s="142" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C52" s="143" t="n"/>
-      <c r="D52" s="143" t="n"/>
-      <c r="E52" s="143" t="n"/>
-      <c r="F52" s="143" t="n"/>
-      <c r="G52" s="143" t="n"/>
-      <c r="H52" s="143" t="n"/>
-      <c r="I52" s="143" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="B53" s="144" t="inlineStr">
+      <c r="C54" s="143" t="n"/>
+      <c r="D54" s="143" t="n"/>
+      <c r="E54" s="143" t="n"/>
+      <c r="F54" s="143" t="n"/>
+      <c r="G54" s="143" t="n"/>
+      <c r="H54" s="143" t="n"/>
+      <c r="I54" s="143" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="B55" s="144" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C53" s="145" t="n"/>
-      <c r="D53" s="145" t="n"/>
-      <c r="E53" s="145" t="n"/>
-      <c r="F53" s="145" t="n"/>
-      <c r="G53" s="145" t="n"/>
-      <c r="H53" s="145" t="n"/>
-      <c r="I53" s="145" t="n"/>
+      <c r="C55" s="145" t="n"/>
+      <c r="D55" s="145" t="n"/>
+      <c r="E55" s="145" t="n"/>
+      <c r="F55" s="145" t="n"/>
+      <c r="G55" s="145" t="n"/>
+      <c r="H55" s="145" t="n"/>
+      <c r="I55" s="145" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B52:I52"/>
-    <mergeCell ref="B53:I53"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G50">
+  <conditionalFormatting sqref="G8:G52">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -895,25 +895,28 @@
     <xf numFmtId="0" fontId="34" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2069,7 +2072,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46315.64681052112</v>
+        <v>46316.65831913189</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2131,7 +2134,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46315.64681052112</v>
+        <v>46316.65831913189</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2264,7 +2267,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.673</v>
+        <v>0.662</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>884.7</v>
@@ -2305,7 +2308,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.399</v>
+        <v>0.386</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>804.05</v>
@@ -2327,12 +2330,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2346,20 +2349,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.363</v>
+        <v>0.369</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>15597.29</v>
+        <v>373.79</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2368,39 +2371,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>1545.36</v>
+        <v>43014.26</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2409,33 +2412,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.311</v>
+        <v>0.361</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>43014.26</v>
+        <v>1545.36</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -2450,33 +2453,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Open Text Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.287</v>
+        <v>0.263</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>373.79</v>
+        <v>5405.28</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2491,12 +2494,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2510,20 +2513,20 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.269</v>
+        <v>0.234</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>336.54</v>
+        <v>4428.98</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2532,39 +2535,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Open Text Corporation</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.249</v>
+        <v>0.219</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>5405.28</v>
+        <v>389.1</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2573,33 +2576,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>XTC</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Exco Technologies Limited</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Automobile Components</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.228</v>
+        <v>0.212</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>4428.98</v>
+        <v>220.37</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2633,7 +2636,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.222</v>
+        <v>0.207</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>35208.26</v>
@@ -2674,7 +2677,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>2245.27</v>
@@ -2687,171 +2690,171 @@
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.204</v>
+        <v>0.736</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>382.43</v>
+        <v>600.1</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.19</v>
+        <v>0.526</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>389.1</v>
+        <v>925.72</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="52" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B21" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.178</v>
+        <v>0.456</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>4283.74</v>
+        <v>209743.55</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="106" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B22" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.113</v>
+        <v>0.45</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>398.33</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2860,39 +2863,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>498.51</v>
+        <v>3333.46</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2901,39 +2904,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.699</v>
+        <v>0.385</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>600.1</v>
+        <v>15597.29</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2942,39 +2945,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.498</v>
+        <v>0.294</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>336.54</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="106" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2983,12 +2986,12 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
@@ -3002,20 +3005,20 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.478</v>
+        <v>0.287</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>925.72</v>
+        <v>99672.56</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="88" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3024,33 +3027,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.437</v>
+        <v>0.281</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>209743.55</v>
+        <v>80962.39</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
@@ -3065,39 +3068,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.391</v>
+        <v>0.221</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>3333.46</v>
+        <v>3837.96</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3106,33 +3109,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.265</v>
+        <v>0.194</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>6794.59</v>
+        <v>382.43</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
@@ -3147,39 +3150,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.245</v>
+        <v>0.182</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>80962.39</v>
+        <v>4283.74</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="106" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3188,33 +3191,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.239</v>
+        <v>0.104</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>99672.56</v>
+        <v>1823.99</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -3222,40 +3225,40 @@
     </row>
     <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.227</v>
+        <v>0.517</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>3837.96</v>
+        <v>732.01</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -3263,130 +3266,102 @@
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C33" s="121" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D33" s="122" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F33" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G33" s="118" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="H33" s="124" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I33" s="125" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+      <c r="B33" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C33" s="130" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="D33" s="131" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="132" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F33" s="132" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G33" s="133" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H33" s="134" t="n">
+        <v>6794.59</v>
+      </c>
+      <c r="I33" s="135" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="8" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C34" s="129" t="inlineStr">
-        <is>
-          <t>GUD</t>
-        </is>
-      </c>
-      <c r="D34" s="130" t="inlineStr">
-        <is>
-          <t>Knight Therapeutics Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="131" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F34" s="131" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G34" s="132" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="H34" s="133" t="n">
-        <v>732.01</v>
-      </c>
-      <c r="I34" s="134" t="inlineStr">
-        <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
-        </is>
-      </c>
+      <c r="B34" s="136" t="n"/>
+      <c r="C34" s="137" t="n"/>
+      <c r="D34" s="138" t="n"/>
+      <c r="E34" s="139" t="n"/>
+      <c r="F34" s="139" t="n"/>
+      <c r="G34" s="140" t="n"/>
+      <c r="H34" s="141" t="n"/>
+      <c r="I34" s="142" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="8" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="135" t="n"/>
-      <c r="C35" s="136" t="n"/>
-      <c r="D35" s="137" t="n"/>
-      <c r="E35" s="138" t="n"/>
-      <c r="F35" s="138" t="n"/>
-      <c r="G35" s="139" t="n"/>
-      <c r="H35" s="140" t="n"/>
-      <c r="I35" s="141" t="n"/>
+      <c r="B35" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C35" s="144" t="n"/>
+      <c r="D35" s="144" t="n"/>
+      <c r="E35" s="144" t="n"/>
+      <c r="F35" s="144" t="n"/>
+      <c r="G35" s="144" t="n"/>
+      <c r="H35" s="144" t="n"/>
+      <c r="I35" s="144" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="142" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C36" s="143" t="n"/>
-      <c r="D36" s="143" t="n"/>
-      <c r="E36" s="143" t="n"/>
-      <c r="F36" s="143" t="n"/>
-      <c r="G36" s="143" t="n"/>
-      <c r="H36" s="143" t="n"/>
-      <c r="I36" s="143" t="n"/>
+      <c r="B36" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C36" s="146" t="n"/>
+      <c r="D36" s="146" t="n"/>
+      <c r="E36" s="146" t="n"/>
+      <c r="F36" s="146" t="n"/>
+      <c r="G36" s="146" t="n"/>
+      <c r="H36" s="146" t="n"/>
+      <c r="I36" s="146" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="144" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C37" s="145" t="n"/>
-      <c r="D37" s="145" t="n"/>
-      <c r="E37" s="145" t="n"/>
-      <c r="F37" s="145" t="n"/>
-      <c r="G37" s="145" t="n"/>
-      <c r="H37" s="145" t="n"/>
-      <c r="I37" s="145" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="89" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -3551,10 +3526,10 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G34">
+  <conditionalFormatting sqref="G8:G33">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4495,7 +4470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4535,7 +4510,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46315.64681052112</v>
+        <v>46316.65831913189</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4668,7 +4643,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.864</v>
+        <v>0.984</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>14054.04</v>
@@ -4690,33 +4665,33 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Revvity Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.492</v>
+        <v>0.819</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>104249.82</v>
+        <v>16701.36</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Revvity Inc provides health sciences solutions technologies and services</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -4731,33 +4706,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>ServiceNow Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.467</v>
+        <v>0.696</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>241617.28</v>
+        <v>142623.33</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4772,12 +4747,12 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
@@ -4787,24 +4762,24 @@
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.457</v>
+        <v>0.676</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>480788.44</v>
+        <v>32165.5</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4813,39 +4788,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.457</v>
+        <v>0.539</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>11772.74</v>
+        <v>47137.94</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4854,39 +4829,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.419</v>
+        <v>0.524</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>1054668.83</v>
+        <v>104249.82</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4895,39 +4870,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.394</v>
+        <v>0.496</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>33875.2</v>
+        <v>241617.28</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4936,12 +4911,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -4955,20 +4930,20 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.374</v>
+        <v>0.47</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>116683.09</v>
+        <v>11772.74</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4977,33 +4952,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.329</v>
+        <v>0.47</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>24969.64</v>
+        <v>42201.2</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -5018,39 +4993,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.324</v>
+        <v>0.436</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>28342.5</v>
+        <v>1054668.83</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -5059,39 +5034,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.303</v>
+        <v>0.424</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>21455.05</v>
+        <v>9701.92</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5100,33 +5075,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.295</v>
+        <v>0.351</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>33430.82</v>
+        <v>33875.2</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5141,39 +5116,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.283</v>
+        <v>0.351</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>15537.74</v>
+        <v>24969.64</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5182,39 +5157,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.268</v>
+        <v>0.341</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>20324.32</v>
+        <v>15537.74</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="106" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5223,33 +5198,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.263</v>
+        <v>0.338</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>48910.32</v>
+        <v>28342.5</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5283,7 +5258,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.261</v>
+        <v>0.317</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>151241.83</v>
@@ -5296,7 +5271,7 @@
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="88" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5305,12 +5280,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -5320,24 +5295,24 @@
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.254</v>
+        <v>0.295</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>54537.32</v>
+        <v>20324.32</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="88" customHeight="1">
+    <row r="25" ht="106" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="126" t="inlineStr">
         <is>
@@ -5346,12 +5321,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5361,24 +5336,24 @@
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.25</v>
+        <v>0.291</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>26039.81</v>
+        <v>48910.32</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="126" t="inlineStr">
         <is>
@@ -5387,39 +5362,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.246</v>
+        <v>0.291</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>25579.38</v>
+        <v>54537.32</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="88" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="126" t="inlineStr">
         <is>
@@ -5428,33 +5403,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.244</v>
+        <v>0.287</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>498865.76</v>
+        <v>26039.81</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5469,39 +5444,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.235</v>
+        <v>0.272</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>371563.85</v>
+        <v>25579.38</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5510,33 +5485,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.209</v>
+        <v>0.241</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>404759.18</v>
+        <v>498865.76</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5551,33 +5526,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.184</v>
+        <v>0.226</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>183538.16</v>
+        <v>371563.85</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -5592,12 +5567,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5611,14 +5586,14 @@
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.183</v>
+        <v>0.215</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>677009.86</v>
+        <v>156513.85</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -5652,7 +5627,7 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.182</v>
+        <v>0.202</v>
       </c>
       <c r="H32" s="119" t="n">
         <v>75763.52</v>
@@ -5674,33 +5649,33 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.177</v>
+        <v>0.186</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>156513.85</v>
+        <v>12857.61</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -5734,7 +5709,7 @@
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.168</v>
+        <v>0.139</v>
       </c>
       <c r="H34" s="119" t="n">
         <v>159089.29</v>
@@ -5775,7 +5750,7 @@
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.144</v>
+        <v>0.138</v>
       </c>
       <c r="H35" s="124" t="n">
         <v>111058.59</v>
@@ -5788,7 +5763,7 @@
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="52" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="126" t="inlineStr">
         <is>
@@ -5797,33 +5772,33 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>22965.61</v>
+        <v>31594.32</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co</t>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
@@ -5838,39 +5813,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>31594.32</v>
+        <v>27315.89</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row r="38" ht="52" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -5879,12 +5854,12 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Dollar General Corporation</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
@@ -5894,18 +5869,18 @@
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>27315.89</v>
+        <v>22965.61</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
+          <t>Church &amp; Dwight Co</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
@@ -5939,7 +5914,7 @@
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="H39" s="124" t="n">
         <v>61416.01</v>
@@ -5952,7 +5927,7 @@
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="70" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="126" t="inlineStr">
         <is>
@@ -5961,33 +5936,33 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>12857.61</v>
+        <v>66372.58</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
@@ -6002,33 +5977,33 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Republic Services Inc.</t>
+          <t>Ulta Beauty Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.091</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>66372.58</v>
+        <v>23628.33</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -6062,7 +6037,7 @@
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>3.421</v>
+        <v>3.844</v>
       </c>
       <c r="H42" s="119" t="n">
         <v>74971.71000000001</v>
@@ -6075,7 +6050,7 @@
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="70" customHeight="1">
+    <row r="43" ht="52" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6084,33 +6059,33 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>1.136</v>
+        <v>0.994</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>123883.6</v>
+        <v>48504.52</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
@@ -6144,7 +6119,7 @@
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>1.043</v>
+        <v>0.988</v>
       </c>
       <c r="H44" s="119" t="n">
         <v>45576.53</v>
@@ -6157,7 +6132,7 @@
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="52" customHeight="1">
+    <row r="45" ht="70" customHeight="1">
       <c r="A45" s="43" t="n"/>
       <c r="B45" s="127" t="inlineStr">
         <is>
@@ -6166,39 +6141,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.993</v>
+        <v>0.709</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>48504.52</v>
+        <v>17950.14</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="88" customHeight="1">
+    <row r="46" ht="70" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6207,39 +6182,39 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.859</v>
+        <v>0.444</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>122343.55</v>
+        <v>480788.44</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="70" customHeight="1" thickBot="1">
+    <row r="47" ht="52" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6248,39 +6223,39 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.831</v>
+        <v>0.414</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>109006.53</v>
+        <v>21029.38</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>Phillips 66 operates as an integrated downstream energy provider in the United States the United Kingdom Germany and internationally</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
-    <row r="48" ht="52" customHeight="1">
+    <row r="48" ht="70" customHeight="1">
       <c r="A48" s="43" t="n"/>
       <c r="B48" s="127" t="inlineStr">
         <is>
@@ -6289,12 +6264,12 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
@@ -6304,18 +6279,18 @@
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.423</v>
+        <v>0.378</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>21029.38</v>
+        <v>116683.09</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
@@ -6349,7 +6324,7 @@
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="H49" s="124" t="n">
         <v>682021.24</v>
@@ -6370,159 +6345,349 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="D50" s="116" t="inlineStr">
+        <is>
+          <t>Biogen Inc.</t>
+        </is>
+      </c>
+      <c r="E50" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F50" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G50" s="118" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H50" s="119" t="n">
+        <v>33430.82</v>
+      </c>
+      <c r="I50" s="120" t="inlineStr">
+        <is>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="70" customHeight="1">
+      <c r="B51" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C51" s="121" t="inlineStr">
+        <is>
           <t>MTD</t>
         </is>
       </c>
-      <c r="D50" s="116" t="inlineStr">
+      <c r="D51" s="122" t="inlineStr">
         <is>
           <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
-      <c r="E50" s="117" t="inlineStr">
+      <c r="E51" s="123" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F50" s="117" t="inlineStr">
+      <c r="F51" s="123" t="inlineStr">
         <is>
           <t>Life Sciences Tools and Services</t>
         </is>
       </c>
-      <c r="G50" s="118" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="H50" s="119" t="n">
+      <c r="G51" s="118" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="H51" s="124" t="n">
         <v>30639.57</v>
       </c>
-      <c r="I50" s="120" t="inlineStr">
+      <c r="I51" s="125" t="inlineStr">
         <is>
           <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="52" customHeight="1">
-      <c r="B51" s="127" t="inlineStr">
+    <row r="52" ht="88" customHeight="1">
+      <c r="B52" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C51" s="121" t="inlineStr">
+      <c r="C52" s="115" t="inlineStr">
+        <is>
+          <t>IFF</t>
+        </is>
+      </c>
+      <c r="D52" s="116" t="inlineStr">
+        <is>
+          <t>International Flavors &amp; Fragrances Inc.</t>
+        </is>
+      </c>
+      <c r="E52" s="117" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F52" s="117" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="G52" s="118" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="H52" s="119" t="n">
+        <v>21455.05</v>
+      </c>
+      <c r="I52" s="120" t="inlineStr">
+        <is>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="52" customHeight="1">
+      <c r="B53" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C53" s="121" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="D53" s="122" t="inlineStr">
+        <is>
+          <t>Chevron Corporation</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F53" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G53" s="118" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H53" s="124" t="n">
+        <v>404759.18</v>
+      </c>
+      <c r="I53" s="125" t="inlineStr">
+        <is>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="52" customHeight="1">
+      <c r="B54" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C54" s="115" t="inlineStr">
         <is>
           <t>MCK</t>
         </is>
       </c>
-      <c r="D51" s="122" t="inlineStr">
+      <c r="D54" s="116" t="inlineStr">
         <is>
           <t>McKesson Corporation</t>
         </is>
       </c>
-      <c r="E51" s="123" t="inlineStr">
+      <c r="E54" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F51" s="123" t="inlineStr">
+      <c r="F54" s="117" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
       </c>
-      <c r="G51" s="118" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="H51" s="124" t="n">
+      <c r="G54" s="118" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="H54" s="119" t="n">
         <v>108638.32</v>
       </c>
-      <c r="I51" s="125" t="inlineStr">
+      <c r="I54" s="120" t="inlineStr">
         <is>
           <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="70" customHeight="1">
-      <c r="B52" s="128" t="inlineStr">
+    <row r="55" ht="70" customHeight="1">
+      <c r="B55" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C55" s="121" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D55" s="122" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F55" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G55" s="118" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="H55" s="124" t="n">
+        <v>677009.86</v>
+      </c>
+      <c r="I55" s="125" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="B56" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C56" s="115" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D56" s="116" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F56" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="H56" s="119" t="n">
+        <v>183538.16</v>
+      </c>
+      <c r="I56" s="120" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="B57" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C52" s="129" t="inlineStr">
+      <c r="C57" s="130" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="D52" s="130" t="inlineStr">
+      <c r="D57" s="131" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="E52" s="131" t="inlineStr">
+      <c r="E57" s="132" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F52" s="131" t="inlineStr">
+      <c r="F57" s="132" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G52" s="132" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="H52" s="133" t="n">
+      <c r="G57" s="133" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="H57" s="134" t="n">
         <v>3913396.13</v>
       </c>
-      <c r="I52" s="134" t="inlineStr">
+      <c r="I57" s="135" t="inlineStr">
         <is>
           <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="8" customHeight="1">
-      <c r="B53" s="146" t="n"/>
-      <c r="C53" s="146" t="n"/>
-      <c r="D53" s="146" t="n"/>
-      <c r="E53" s="146" t="n"/>
-      <c r="F53" s="146" t="n"/>
-      <c r="G53" s="146" t="n"/>
-      <c r="H53" s="146" t="n"/>
-      <c r="I53" s="146" t="n"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="B54" s="142" t="inlineStr">
+    <row r="58" ht="8" customHeight="1">
+      <c r="B58" s="147" t="n"/>
+      <c r="C58" s="147" t="n"/>
+      <c r="D58" s="147" t="n"/>
+      <c r="E58" s="147" t="n"/>
+      <c r="F58" s="147" t="n"/>
+      <c r="G58" s="147" t="n"/>
+      <c r="H58" s="147" t="n"/>
+      <c r="I58" s="147" t="n"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="B59" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C54" s="143" t="n"/>
-      <c r="D54" s="143" t="n"/>
-      <c r="E54" s="143" t="n"/>
-      <c r="F54" s="143" t="n"/>
-      <c r="G54" s="143" t="n"/>
-      <c r="H54" s="143" t="n"/>
-      <c r="I54" s="143" t="n"/>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="144" t="inlineStr">
+      <c r="C59" s="144" t="n"/>
+      <c r="D59" s="144" t="n"/>
+      <c r="E59" s="144" t="n"/>
+      <c r="F59" s="144" t="n"/>
+      <c r="G59" s="144" t="n"/>
+      <c r="H59" s="144" t="n"/>
+      <c r="I59" s="144" t="n"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="B60" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C55" s="145" t="n"/>
-      <c r="D55" s="145" t="n"/>
-      <c r="E55" s="145" t="n"/>
-      <c r="F55" s="145" t="n"/>
-      <c r="G55" s="145" t="n"/>
-      <c r="H55" s="145" t="n"/>
-      <c r="I55" s="145" t="n"/>
+      <c r="C60" s="146" t="n"/>
+      <c r="D60" s="146" t="n"/>
+      <c r="E60" s="146" t="n"/>
+      <c r="F60" s="146" t="n"/>
+      <c r="G60" s="146" t="n"/>
+      <c r="H60" s="146" t="n"/>
+      <c r="I60" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G52">
+  <conditionalFormatting sqref="G8:G57">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -901,22 +901,22 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -948,6 +948,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2072,7 +2090,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46316.65831913189</v>
+        <v>46317.65719571945</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2134,7 +2152,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46316.65831913189</v>
+        <v>46317.65719571945</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2267,7 +2285,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.662</v>
+        <v>0.59</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>884.7</v>
@@ -2289,33 +2307,33 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.386</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>804.05</v>
+        <v>1836.63</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2330,33 +2348,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.369</v>
+        <v>0.546</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>373.79</v>
+        <v>732.01</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2390,7 +2408,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.366</v>
+        <v>0.463</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>43014.26</v>
@@ -2412,39 +2430,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Constellation Software Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.361</v>
+        <v>0.373</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>1545.36</v>
+        <v>43632.38</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2453,33 +2471,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Open Text Corporation</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.263</v>
+        <v>0.333</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>5405.28</v>
+        <v>804.05</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2494,12 +2512,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2513,20 +2531,20 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.234</v>
+        <v>0.297</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>4428.98</v>
+        <v>373.79</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2535,39 +2553,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>Open Text Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.219</v>
+        <v>0.29</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>389.1</v>
+        <v>5405.28</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2576,12 +2594,12 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>XTC</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
@@ -2591,24 +2609,24 @@
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Automobile Components</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.212</v>
+        <v>0.231</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>220.37</v>
+        <v>35208.26</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2617,39 +2635,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.207</v>
+        <v>0.228</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>35208.26</v>
+        <v>69914.25999999999</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2658,33 +2676,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.18</v>
+        <v>0.203</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>2245.27</v>
+        <v>389.1</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2692,169 +2710,169 @@
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>WCN</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Waste Connections Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.736</v>
+        <v>0.172</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>600.1</v>
+        <v>39435.42</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="88" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>XTC</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Exco Technologies Limited</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Automobile Components</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.526</v>
+        <v>0.167</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>925.72</v>
+        <v>220.37</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.456</v>
+        <v>0.164</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>209743.55</v>
+        <v>4428.98</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Shopify Inc a commerce technology company provides tools to start scale market and run a business of various sizes in Canada the United States Europe the Middle East Africa the Asia Pacific and Latin America</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.45</v>
+        <v>0.116</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>743.0700000000001</v>
+        <v>2245.27</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2863,12 +2881,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -2882,20 +2900,20 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.41</v>
+        <v>0.719</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>3333.46</v>
+        <v>600.1</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2904,33 +2922,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.385</v>
+        <v>0.47</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>15597.29</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2945,12 +2963,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -2964,20 +2982,20 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.294</v>
+        <v>0.427</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>336.54</v>
+        <v>925.72</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="106" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2986,12 +3004,12 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
@@ -3005,14 +3023,14 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.287</v>
+        <v>0.323</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>99672.56</v>
+        <v>15597.29</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3046,7 +3064,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.281</v>
+        <v>0.242</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>80962.39</v>
@@ -3059,7 +3077,7 @@
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="106" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3068,12 +3086,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3087,20 +3105,20 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.221</v>
+        <v>0.237</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>3837.96</v>
+        <v>99672.56</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3109,39 +3127,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.194</v>
+        <v>0.232</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>382.43</v>
+        <v>336.54</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -3150,39 +3168,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>4283.74</v>
+        <v>1545.36</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3191,33 +3209,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>NWC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>The North West Company Inc.</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.104</v>
+        <v>0.176</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>1823.99</v>
+        <v>4283.74</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -3225,169 +3243,253 @@
     </row>
     <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B32" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.517</v>
+        <v>0.175</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>732.01</v>
+        <v>3837.96</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="88" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C33" s="130" t="inlineStr">
-        <is>
-          <t>DSG</t>
-        </is>
-      </c>
-      <c r="D33" s="131" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="132" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F33" s="132" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G33" s="133" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H33" s="134" t="n">
-        <v>6794.59</v>
-      </c>
-      <c r="I33" s="135" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>DTOL</t>
+        </is>
+      </c>
+      <c r="D33" s="122" t="inlineStr">
+        <is>
+          <t>D2L Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Diversified Consumer Services</t>
+        </is>
+      </c>
+      <c r="G33" s="118" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H33" s="124" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="8" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="136" t="n"/>
-      <c r="C34" s="137" t="n"/>
-      <c r="D34" s="138" t="n"/>
-      <c r="E34" s="139" t="n"/>
-      <c r="F34" s="139" t="n"/>
-      <c r="G34" s="140" t="n"/>
-      <c r="H34" s="141" t="n"/>
-      <c r="I34" s="142" t="n"/>
+      <c r="B34" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C34" s="115" t="inlineStr">
+        <is>
+          <t>KXS</t>
+        </is>
+      </c>
+      <c r="D34" s="116" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F34" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G34" s="118" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="H34" s="119" t="n">
+        <v>3333.46</v>
+      </c>
+      <c r="I34" s="120" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+        </is>
+      </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C35" s="144" t="n"/>
-      <c r="D35" s="144" t="n"/>
-      <c r="E35" s="144" t="n"/>
-      <c r="F35" s="144" t="n"/>
-      <c r="G35" s="144" t="n"/>
-      <c r="H35" s="144" t="n"/>
-      <c r="I35" s="144" t="n"/>
+      <c r="B35" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C35" s="121" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="D35" s="122" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F35" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G35" s="118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H35" s="124" t="n">
+        <v>6794.59</v>
+      </c>
+      <c r="I35" s="125" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="28" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C36" s="146" t="n"/>
-      <c r="D36" s="146" t="n"/>
-      <c r="E36" s="146" t="n"/>
-      <c r="F36" s="146" t="n"/>
-      <c r="G36" s="146" t="n"/>
-      <c r="H36" s="146" t="n"/>
-      <c r="I36" s="146" t="n"/>
+      <c r="B36" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C36" s="130" t="inlineStr">
+        <is>
+          <t>NWC</t>
+        </is>
+      </c>
+      <c r="D36" s="131" t="inlineStr">
+        <is>
+          <t>The North West Company Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="132" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F36" s="132" t="inlineStr">
+        <is>
+          <t>Consumer Staples Distribution and Retail</t>
+        </is>
+      </c>
+      <c r="G36" s="133" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H36" s="134" t="n">
+        <v>1823.99</v>
+      </c>
+      <c r="I36" s="135" t="inlineStr">
+        <is>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+        </is>
+      </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1">
+    <row r="37" ht="8" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="89" t="n"/>
-      <c r="H37" s="93" t="n"/>
-      <c r="I37" s="54" t="n"/>
+      <c r="B37" s="136" t="n"/>
+      <c r="C37" s="137" t="n"/>
+      <c r="D37" s="138" t="n"/>
+      <c r="E37" s="139" t="n"/>
+      <c r="F37" s="139" t="n"/>
+      <c r="G37" s="140" t="n"/>
+      <c r="H37" s="141" t="n"/>
+      <c r="I37" s="142" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="20.4" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="40" t="n"/>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="89" t="n"/>
-      <c r="H38" s="91" t="n"/>
-      <c r="I38" s="53" t="n"/>
+      <c r="B38" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C38" s="144" t="n"/>
+      <c r="D38" s="144" t="n"/>
+      <c r="E38" s="144" t="n"/>
+      <c r="F38" s="144" t="n"/>
+      <c r="G38" s="144" t="n"/>
+      <c r="H38" s="144" t="n"/>
+      <c r="I38" s="144" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="89" t="n"/>
-      <c r="H39" s="93" t="n"/>
-      <c r="I39" s="54" t="n"/>
+      <c r="B39" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C39" s="146" t="n"/>
+      <c r="D39" s="146" t="n"/>
+      <c r="E39" s="146" t="n"/>
+      <c r="F39" s="146" t="n"/>
+      <c r="G39" s="146" t="n"/>
+      <c r="H39" s="146" t="n"/>
+      <c r="I39" s="146" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
@@ -3525,11 +3627,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B38:I38"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G33">
+  <conditionalFormatting sqref="G8:G36">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4470,7 +4572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4510,7 +4612,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46316.65831913189</v>
+        <v>46317.65719571945</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4643,7 +4745,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.984</v>
+        <v>1.034</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>14054.04</v>
@@ -4684,7 +4786,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.819</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>16701.36</v>
@@ -4697,7 +4799,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4706,12 +4808,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>ServiceNow Inc.</t>
+          <t>Workday Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -4725,14 +4827,14 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.696</v>
+        <v>0.767</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>142623.33</v>
+        <v>45398.38</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
+          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4747,39 +4849,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>ServiceNow Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.676</v>
+        <v>0.735</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>32165.5</v>
+        <v>142623.33</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
+          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4788,12 +4890,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -4807,20 +4909,20 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.539</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>47137.94</v>
+        <v>42172.99</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4829,33 +4931,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.524</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>104249.82</v>
+        <v>17904.45</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4870,12 +4972,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -4885,24 +4987,24 @@
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.496</v>
+        <v>0.66</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>241617.28</v>
+        <v>32165.5</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4911,39 +5013,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.47</v>
+        <v>0.571</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>11772.74</v>
+        <v>104249.82</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -4952,33 +5054,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.47</v>
+        <v>0.516</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>42201.2</v>
+        <v>9701.92</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -5012,7 +5114,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.436</v>
+        <v>0.516</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>1054668.83</v>
@@ -5034,33 +5136,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.424</v>
+        <v>0.515</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>9701.92</v>
+        <v>47137.94</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5075,33 +5177,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.351</v>
+        <v>0.51</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>33875.2</v>
+        <v>42201.2</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5116,39 +5218,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
         <v>0.351</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>24969.64</v>
+        <v>28342.5</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="52" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5157,39 +5259,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.341</v>
+        <v>0.349</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>15537.74</v>
+        <v>12451.88</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5198,33 +5300,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
         <v>0.338</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>28342.5</v>
+        <v>224207.66</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5239,39 +5341,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.317</v>
+        <v>0.332</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>151241.83</v>
+        <v>61019.13</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="88" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5280,39 +5382,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.295</v>
+        <v>0.271</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>20324.32</v>
+        <v>371563.85</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="106" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="126" t="inlineStr">
         <is>
@@ -5321,12 +5423,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Elevance Health Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5336,24 +5438,24 @@
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.291</v>
+        <v>0.27</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>48910.32</v>
+        <v>87408.73</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="126" t="inlineStr">
         <is>
@@ -5362,39 +5464,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.291</v>
+        <v>0.269</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>54537.32</v>
+        <v>41984.2</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="88" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="126" t="inlineStr">
         <is>
@@ -5403,39 +5505,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.287</v>
+        <v>0.266</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>26039.81</v>
+        <v>15537.74</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="126" t="inlineStr">
         <is>
@@ -5444,33 +5546,33 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.272</v>
+        <v>0.266</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>25579.38</v>
+        <v>20324.32</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
@@ -5485,33 +5587,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.241</v>
+        <v>0.243</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>498865.76</v>
+        <v>12857.61</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5526,39 +5628,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.226</v>
+        <v>0.229</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>371563.85</v>
+        <v>47993.25</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>eBay Inc together with its subsidiaries operates marketplace platforms that connect buyers and sellers in the United States the United Kingdom China Germany and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5567,39 +5669,39 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
         <v>0.215</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>156513.85</v>
+        <v>16850.47</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="88" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="126" t="inlineStr">
         <is>
@@ -5608,33 +5710,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>EOG Resources Inc.</t>
+          <t>Broadridge Financial Solutions Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.202</v>
+        <v>0.205</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>75763.52</v>
+        <v>17905.95</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5649,39 +5751,39 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.186</v>
+        <v>0.202</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>12857.61</v>
+        <v>156513.85</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="52" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="126" t="inlineStr">
         <is>
@@ -5690,39 +5792,39 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.139</v>
+        <v>0.192</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>159089.29</v>
+        <v>23268.86</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="70" customHeight="1">
+    <row r="35" ht="88" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="126" t="inlineStr">
         <is>
@@ -5731,39 +5833,39 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.138</v>
+        <v>0.187</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>111058.59</v>
+        <v>75763.52</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row r="36" ht="52" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="126" t="inlineStr">
         <is>
@@ -5772,33 +5874,33 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.126</v>
+        <v>0.185</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>31594.32</v>
+        <v>12320.13</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
@@ -5832,7 +5934,7 @@
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.118</v>
+        <v>0.178</v>
       </c>
       <c r="H37" s="124" t="n">
         <v>27315.89</v>
@@ -5845,7 +5947,7 @@
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -5854,33 +5956,33 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.112</v>
+        <v>0.175</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>22965.61</v>
+        <v>15869.76</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co</t>
+          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
@@ -5895,39 +5997,39 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Cencora Inc.</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.105</v>
+        <v>0.17</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>61416.01</v>
+        <v>66372.58</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="52" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="126" t="inlineStr">
         <is>
@@ -5936,39 +6038,39 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Republic Services Inc.</t>
+          <t>Tyler Technologies Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.105</v>
+        <v>0.165</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>66372.58</v>
+        <v>13525.55</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="52" customHeight="1">
+    <row r="41" ht="70" customHeight="1">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="126" t="inlineStr">
         <is>
@@ -5977,74 +6079,74 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>23628.33</v>
+        <v>57901.58</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="52" customHeight="1" thickBot="1">
+    <row r="42" ht="70" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B42" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Nasdaq Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>3.844</v>
+        <v>0.145</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>51024.57</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
@@ -6052,163 +6154,163 @@
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B43" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.994</v>
+        <v>0.143</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>48504.52</v>
+        <v>22965.61</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Humana Inc provides medical and specialty insurance products in the United States</t>
+          <t>Church &amp; Dwight Co</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="70" customHeight="1" thickBot="1">
+    <row r="44" ht="52" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B44" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.988</v>
+        <v>0.131</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>45576.53</v>
+        <v>345602.03</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="70" customHeight="1">
+    <row r="45" ht="52" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B45" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.709</v>
+        <v>0.119</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>17950.14</v>
+        <v>73585.95</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row r="46" ht="52" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B46" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.444</v>
+        <v>0.114</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>480788.44</v>
+        <v>178216.54</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>The Walt Disney Company operates as an entertainment company in Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
@@ -6223,33 +6325,33 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.414</v>
+        <v>3.619</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>21029.38</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6264,39 +6366,39 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.378</v>
+        <v>1.017</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>116683.09</v>
+        <v>45576.53</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="52" customHeight="1">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6305,39 +6407,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.327</v>
+        <v>0.716</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>682021.24</v>
+        <v>17950.14</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="70" customHeight="1">
+    <row r="50" ht="88" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6345,33 +6447,33 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F50" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G50" s="118" t="n">
-        <v>0.308</v>
+        <v>0.539</v>
       </c>
       <c r="H50" s="119" t="n">
-        <v>33430.82</v>
+        <v>11772.74</v>
       </c>
       <c r="I50" s="120" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6485,12 @@
       </c>
       <c r="C51" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D51" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E51" s="123" t="inlineStr">
@@ -6402,18 +6504,18 @@
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.296</v>
+        <v>0.461</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>30639.57</v>
+        <v>241617.28</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="88" customHeight="1">
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1">
       <c r="B52" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6421,37 +6523,37 @@
       </c>
       <c r="C52" s="115" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D52" s="116" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E52" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F52" s="117" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G52" s="118" t="n">
-        <v>0.287</v>
+        <v>0.457</v>
       </c>
       <c r="H52" s="119" t="n">
-        <v>21455.05</v>
+        <v>480788.44</v>
       </c>
       <c r="I52" s="120" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="52" customHeight="1">
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="70" customHeight="1">
       <c r="B53" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6459,33 +6561,33 @@
       </c>
       <c r="C53" s="121" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D53" s="122" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E53" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F53" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G53" s="118" t="n">
-        <v>0.242</v>
+        <v>0.441</v>
       </c>
       <c r="H53" s="124" t="n">
-        <v>404759.18</v>
+        <v>116683.09</v>
       </c>
       <c r="I53" s="125" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
     </row>
@@ -6497,37 +6599,37 @@
       </c>
       <c r="C54" s="115" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D54" s="116" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E54" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F54" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G54" s="118" t="n">
-        <v>0.225</v>
+        <v>0.424</v>
       </c>
       <c r="H54" s="119" t="n">
-        <v>108638.32</v>
+        <v>21029.38</v>
       </c>
       <c r="I54" s="120" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="70" customHeight="1">
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1">
       <c r="B55" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6535,33 +6637,33 @@
       </c>
       <c r="C55" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D55" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E55" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F55" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G55" s="118" t="n">
-        <v>0.207</v>
+        <v>0.387</v>
       </c>
       <c r="H55" s="124" t="n">
-        <v>677009.86</v>
+        <v>33875.2</v>
       </c>
       <c r="I55" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
     </row>
@@ -6573,121 +6675,805 @@
       </c>
       <c r="C56" s="115" t="inlineStr">
         <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="D56" s="116" t="inlineStr">
+        <is>
+          <t>Biogen Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F56" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="H56" s="119" t="n">
+        <v>33430.82</v>
+      </c>
+      <c r="I56" s="120" t="inlineStr">
+        <is>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="106" customHeight="1">
+      <c r="B57" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C57" s="121" t="inlineStr">
+        <is>
+          <t>BDX</t>
+        </is>
+      </c>
+      <c r="D57" s="122" t="inlineStr">
+        <is>
+          <t>Becton Dickinson and Company</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F57" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G57" s="118" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="H57" s="124" t="n">
+        <v>48910.32</v>
+      </c>
+      <c r="I57" s="125" t="inlineStr">
+        <is>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="70" customHeight="1">
+      <c r="B58" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C58" s="115" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D58" s="116" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E58" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F58" s="117" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="G58" s="118" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H58" s="119" t="n">
+        <v>25579.38</v>
+      </c>
+      <c r="I58" s="120" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1">
+      <c r="B59" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C59" s="121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D59" s="122" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F59" s="123" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G59" s="118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H59" s="124" t="n">
+        <v>682021.24</v>
+      </c>
+      <c r="I59" s="125" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
+      <c r="B60" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C60" s="115" t="inlineStr">
+        <is>
+          <t>EXPD</t>
+        </is>
+      </c>
+      <c r="D60" s="116" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F60" s="117" t="inlineStr">
+        <is>
+          <t>Air Freight and Logistics</t>
+        </is>
+      </c>
+      <c r="G60" s="118" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="H60" s="119" t="n">
+        <v>24969.64</v>
+      </c>
+      <c r="I60" s="120" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="70" customHeight="1">
+      <c r="B61" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C61" s="121" t="inlineStr">
+        <is>
+          <t>MTD</t>
+        </is>
+      </c>
+      <c r="D61" s="122" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo International Inc.</t>
+        </is>
+      </c>
+      <c r="E61" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F61" s="123" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G61" s="118" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H61" s="124" t="n">
+        <v>30639.57</v>
+      </c>
+      <c r="I61" s="125" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="88" customHeight="1">
+      <c r="B62" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C62" s="115" t="inlineStr">
+        <is>
+          <t>IFF</t>
+        </is>
+      </c>
+      <c r="D62" s="116" t="inlineStr">
+        <is>
+          <t>International Flavors &amp; Fragrances Inc.</t>
+        </is>
+      </c>
+      <c r="E62" s="117" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F62" s="117" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="G62" s="118" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="H62" s="119" t="n">
+        <v>21455.05</v>
+      </c>
+      <c r="I62" s="120" t="inlineStr">
+        <is>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="B63" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C63" s="121" t="inlineStr">
+        <is>
+          <t>WST</t>
+        </is>
+      </c>
+      <c r="D63" s="122" t="inlineStr">
+        <is>
+          <t>West Pharmaceutical Services Inc.</t>
+        </is>
+      </c>
+      <c r="E63" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F63" s="123" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G63" s="118" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="H63" s="124" t="n">
+        <v>26039.81</v>
+      </c>
+      <c r="I63" s="125" t="inlineStr">
+        <is>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="70" customHeight="1">
+      <c r="B64" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C64" s="115" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="D64" s="116" t="inlineStr">
+        <is>
+          <t>Danaher Corporation</t>
+        </is>
+      </c>
+      <c r="E64" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F64" s="117" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G64" s="118" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="H64" s="119" t="n">
+        <v>151241.83</v>
+      </c>
+      <c r="I64" s="120" t="inlineStr">
+        <is>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="52" customHeight="1">
+      <c r="B65" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C65" s="121" t="inlineStr">
+        <is>
+          <t>CAH</t>
+        </is>
+      </c>
+      <c r="D65" s="122" t="inlineStr">
+        <is>
+          <t>Cardinal Health Inc.</t>
+        </is>
+      </c>
+      <c r="E65" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F65" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G65" s="118" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H65" s="124" t="n">
+        <v>54537.32</v>
+      </c>
+      <c r="I65" s="125" t="inlineStr">
+        <is>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="70" customHeight="1">
+      <c r="B66" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C66" s="115" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D66" s="116" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="E66" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F66" s="117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G66" s="118" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H66" s="119" t="n">
+        <v>498865.76</v>
+      </c>
+      <c r="I66" s="120" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="B67" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C67" s="121" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="D67" s="122" t="inlineStr">
+        <is>
+          <t>Chevron Corporation</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F67" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G67" s="118" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="H67" s="124" t="n">
+        <v>404759.18</v>
+      </c>
+      <c r="I67" s="125" t="inlineStr">
+        <is>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="70" customHeight="1">
+      <c r="B68" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C68" s="115" t="inlineStr">
+        <is>
           <t>GILD</t>
         </is>
       </c>
-      <c r="D56" s="116" t="inlineStr">
+      <c r="D68" s="116" t="inlineStr">
         <is>
           <t>Gilead Sciences Inc.</t>
         </is>
       </c>
-      <c r="E56" s="117" t="inlineStr">
+      <c r="E68" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F56" s="117" t="inlineStr">
+      <c r="F68" s="117" t="inlineStr">
         <is>
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="G56" s="118" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="H56" s="119" t="n">
+      <c r="G68" s="118" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="H68" s="119" t="n">
         <v>183538.16</v>
       </c>
-      <c r="I56" s="120" t="inlineStr">
+      <c r="I68" s="120" t="inlineStr">
         <is>
           <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="70" customHeight="1">
-      <c r="B57" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C57" s="130" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="D57" s="131" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="E57" s="132" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F57" s="132" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G57" s="133" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="H57" s="134" t="n">
-        <v>3913396.13</v>
-      </c>
-      <c r="I57" s="135" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation a technology company develops and supports a portfolio of technology solutions for individuals and businesses worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="8" customHeight="1">
-      <c r="B58" s="147" t="n"/>
-      <c r="C58" s="147" t="n"/>
-      <c r="D58" s="147" t="n"/>
-      <c r="E58" s="147" t="n"/>
-      <c r="F58" s="147" t="n"/>
-      <c r="G58" s="147" t="n"/>
-      <c r="H58" s="147" t="n"/>
-      <c r="I58" s="147" t="n"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="B59" s="143" t="inlineStr">
+    <row r="69" ht="52" customHeight="1">
+      <c r="B69" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C69" s="121" t="inlineStr">
+        <is>
+          <t>MCK</t>
+        </is>
+      </c>
+      <c r="D69" s="122" t="inlineStr">
+        <is>
+          <t>McKesson Corporation</t>
+        </is>
+      </c>
+      <c r="E69" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F69" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G69" s="118" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H69" s="124" t="n">
+        <v>108638.32</v>
+      </c>
+      <c r="I69" s="125" t="inlineStr">
+        <is>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="70" customHeight="1">
+      <c r="B70" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C70" s="115" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D70" s="116" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="E70" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F70" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G70" s="118" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="H70" s="119" t="n">
+        <v>677009.86</v>
+      </c>
+      <c r="I70" s="120" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="70" customHeight="1">
+      <c r="B71" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C71" s="121" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="D71" s="122" t="inlineStr">
+        <is>
+          <t>Medtronic plc</t>
+        </is>
+      </c>
+      <c r="E71" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F71" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G71" s="118" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="H71" s="124" t="n">
+        <v>111058.59</v>
+      </c>
+      <c r="I71" s="125" t="inlineStr">
+        <is>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="52" customHeight="1">
+      <c r="B72" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C72" s="115" t="inlineStr">
+        <is>
+          <t>ULTA</t>
+        </is>
+      </c>
+      <c r="D72" s="116" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc.</t>
+        </is>
+      </c>
+      <c r="E72" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F72" s="117" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G72" s="118" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H72" s="119" t="n">
+        <v>23628.33</v>
+      </c>
+      <c r="I72" s="120" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="70" customHeight="1">
+      <c r="B73" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C73" s="121" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D73" s="122" t="inlineStr">
+        <is>
+          <t>Pfizer Inc.</t>
+        </is>
+      </c>
+      <c r="E73" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F73" s="123" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G73" s="118" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="H73" s="124" t="n">
+        <v>159089.29</v>
+      </c>
+      <c r="I73" s="125" t="inlineStr">
+        <is>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="70" customHeight="1">
+      <c r="B74" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C74" s="115" t="inlineStr">
+        <is>
+          <t>RMD</t>
+        </is>
+      </c>
+      <c r="D74" s="116" t="inlineStr">
+        <is>
+          <t>ResMed Inc.</t>
+        </is>
+      </c>
+      <c r="E74" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F74" s="117" t="inlineStr">
+        <is>
+          <t>Health Care Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G74" s="118" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H74" s="119" t="n">
+        <v>31594.32</v>
+      </c>
+      <c r="I74" s="120" t="inlineStr">
+        <is>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="52" customHeight="1">
+      <c r="B75" s="147" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C75" s="148" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D75" s="149" t="inlineStr">
+        <is>
+          <t>Cencora Inc.</t>
+        </is>
+      </c>
+      <c r="E75" s="150" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F75" s="150" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G75" s="133" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="H75" s="151" t="n">
+        <v>61416.01</v>
+      </c>
+      <c r="I75" s="152" t="inlineStr">
+        <is>
+          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1">
+      <c r="B76" s="153" t="n"/>
+      <c r="C76" s="153" t="n"/>
+      <c r="D76" s="153" t="n"/>
+      <c r="E76" s="153" t="n"/>
+      <c r="F76" s="153" t="n"/>
+      <c r="G76" s="153" t="n"/>
+      <c r="H76" s="153" t="n"/>
+      <c r="I76" s="153" t="n"/>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="B77" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C59" s="144" t="n"/>
-      <c r="D59" s="144" t="n"/>
-      <c r="E59" s="144" t="n"/>
-      <c r="F59" s="144" t="n"/>
-      <c r="G59" s="144" t="n"/>
-      <c r="H59" s="144" t="n"/>
-      <c r="I59" s="144" t="n"/>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="B60" s="145" t="inlineStr">
+      <c r="C77" s="144" t="n"/>
+      <c r="D77" s="144" t="n"/>
+      <c r="E77" s="144" t="n"/>
+      <c r="F77" s="144" t="n"/>
+      <c r="G77" s="144" t="n"/>
+      <c r="H77" s="144" t="n"/>
+      <c r="I77" s="144" t="n"/>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="B78" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C60" s="146" t="n"/>
-      <c r="D60" s="146" t="n"/>
-      <c r="E60" s="146" t="n"/>
-      <c r="F60" s="146" t="n"/>
-      <c r="G60" s="146" t="n"/>
-      <c r="H60" s="146" t="n"/>
-      <c r="I60" s="146" t="n"/>
+      <c r="C78" s="146" t="n"/>
+      <c r="D78" s="146" t="n"/>
+      <c r="E78" s="146" t="n"/>
+      <c r="F78" s="146" t="n"/>
+      <c r="G78" s="146" t="n"/>
+      <c r="H78" s="146" t="n"/>
+      <c r="I78" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B59:I59"/>
-    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G57">
+  <conditionalFormatting sqref="G8:G75">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -383,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -558,11 +558,24 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top style="medium">
+        <color theme="2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -901,45 +914,25 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -948,25 +941,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2090,7 +2079,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46317.65719571945</v>
+        <v>46318.66168135779</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2152,7 +2141,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46317.65719571945</v>
+        <v>46318.66168135779</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2285,7 +2274,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.59</v>
+        <v>0.662</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>884.7</v>
@@ -2298,7 +2287,7 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2307,39 +2296,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>1836.63</v>
+        <v>732.01</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2348,33 +2337,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.546</v>
+        <v>0.53</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>732.01</v>
+        <v>1836.63</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2408,7 +2397,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.463</v>
+        <v>0.451</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>43014.26</v>
@@ -2421,7 +2410,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2430,39 +2419,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Constellation Software Inc.</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.373</v>
+        <v>0.409</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>43632.38</v>
+        <v>804.05</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2471,33 +2460,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Constellation Software Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.333</v>
+        <v>0.393</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>804.05</v>
+        <v>43632.38</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2531,7 +2520,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.297</v>
+        <v>0.383</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>373.79</v>
@@ -2572,7 +2561,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>5405.28</v>
@@ -2585,7 +2574,7 @@
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2594,33 +2583,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>TNZ</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>Tenaz Energy Corp.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.231</v>
+        <v>0.239</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>35208.26</v>
+        <v>1570.2</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>Tenaz Energy Corp an energy company engages in the acquisition and development of oil and gas assets in Canada and the Netherlands</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2635,39 +2624,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.228</v>
+        <v>0.22</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>69914.25999999999</v>
+        <v>4428.98</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2676,33 +2665,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.203</v>
+        <v>0.205</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>389.1</v>
+        <v>69914.25999999999</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2736,7 +2725,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>39435.42</v>
@@ -2758,33 +2747,33 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>XTC</t>
+          <t>VET</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited</t>
+          <t>Vermilion Energy Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Automobile Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.167</v>
+        <v>0.182</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>220.37</v>
+        <v>1789.16</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
+          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
@@ -2799,12 +2788,12 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -2818,20 +2807,20 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>4428.98</v>
+        <v>2245.27</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -2840,156 +2829,156 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>ENGH</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Enghouse Systems Limited</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.116</v>
+        <v>0.158</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>2245.27</v>
+        <v>634.6900000000001</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="88" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>XTC</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Exco Technologies Limited</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Automobile Components</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.719</v>
+        <v>0.155</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>600.1</v>
+        <v>220.37</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>GFR</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Greenfire Resources Ltd.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.47</v>
+        <v>0.152</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>743.0700000000001</v>
+        <v>1476.14</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Greenfire Resources Ltd together with its subsidiaries engages in the exploration development and operation of oil and gas properties in the Athabasca oil sands region of Alberta Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="106" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B25" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Loblaw Companies Limited</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.427</v>
+        <v>0.12</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>925.72</v>
+        <v>50539.87</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2997,40 +2986,40 @@
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B26" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.323</v>
+        <v>0.119</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>15597.29</v>
+        <v>1823.99</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3045,39 +3034,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.242</v>
+        <v>0.709</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>80962.39</v>
+        <v>600.1</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="106" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3086,12 +3075,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3105,20 +3094,20 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.237</v>
+        <v>0.519</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>99672.56</v>
+        <v>925.72</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3127,39 +3116,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.232</v>
+        <v>0.464</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>336.54</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="88" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -3168,12 +3157,12 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
@@ -3187,20 +3176,20 @@
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.178</v>
+        <v>0.376</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>1545.36</v>
+        <v>15597.29</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3209,39 +3198,39 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.176</v>
+        <v>0.294</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>4283.74</v>
+        <v>336.54</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="106" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -3250,12 +3239,12 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
@@ -3269,20 +3258,20 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.175</v>
+        <v>0.287</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>3837.96</v>
+        <v>99672.56</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="88" customHeight="1">
+    <row r="33" ht="52" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="127" t="inlineStr">
         <is>
@@ -3291,115 +3280,115 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.125</v>
+        <v>0.284</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>382.43</v>
+        <v>80962.39</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="52" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.433</v>
+        <v>0.234</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>3333.46</v>
+        <v>35208.26</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="70" customHeight="1">
+    <row r="35" ht="88" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B35" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.36</v>
+        <v>0.225</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>6794.59</v>
+        <v>1545.36</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
@@ -3407,154 +3396,294 @@
     </row>
     <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C36" s="130" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D36" s="131" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E36" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F36" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G36" s="133" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H36" s="134" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I36" s="135" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+      <c r="B36" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C36" s="115" t="inlineStr">
+        <is>
+          <t>GEI</t>
+        </is>
+      </c>
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F36" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G36" s="118" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H36" s="119" t="n">
+        <v>3837.96</v>
+      </c>
+      <c r="I36" s="120" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="8" customHeight="1">
+    <row r="37" ht="52" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="136" t="n"/>
-      <c r="C37" s="137" t="n"/>
-      <c r="D37" s="138" t="n"/>
-      <c r="E37" s="139" t="n"/>
-      <c r="F37" s="139" t="n"/>
-      <c r="G37" s="140" t="n"/>
-      <c r="H37" s="141" t="n"/>
-      <c r="I37" s="142" t="n"/>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C37" s="121" t="inlineStr">
+        <is>
+          <t>ACQ</t>
+        </is>
+      </c>
+      <c r="D37" s="122" t="inlineStr">
+        <is>
+          <t>AutoCanada Inc.</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F37" s="123" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G37" s="118" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="H37" s="124" t="n">
+        <v>389.1</v>
+      </c>
+      <c r="I37" s="125" t="inlineStr">
+        <is>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+        </is>
+      </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="52" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C38" s="144" t="n"/>
-      <c r="D38" s="144" t="n"/>
-      <c r="E38" s="144" t="n"/>
-      <c r="F38" s="144" t="n"/>
-      <c r="G38" s="144" t="n"/>
-      <c r="H38" s="144" t="n"/>
-      <c r="I38" s="144" t="n"/>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C38" s="115" t="inlineStr">
+        <is>
+          <t>ELF</t>
+        </is>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>E-L Financial Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E38" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F38" s="117" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G38" s="118" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H38" s="119" t="n">
+        <v>4283.74</v>
+      </c>
+      <c r="I38" s="120" t="inlineStr">
+        <is>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+        </is>
+      </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="28" customHeight="1">
+    <row r="39" ht="88" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C39" s="146" t="n"/>
-      <c r="D39" s="146" t="n"/>
-      <c r="E39" s="146" t="n"/>
-      <c r="F39" s="146" t="n"/>
-      <c r="G39" s="146" t="n"/>
-      <c r="H39" s="146" t="n"/>
-      <c r="I39" s="146" t="n"/>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="inlineStr">
+        <is>
+          <t>DTOL</t>
+        </is>
+      </c>
+      <c r="D39" s="122" t="inlineStr">
+        <is>
+          <t>D2L Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F39" s="123" t="inlineStr">
+        <is>
+          <t>Diversified Consumer Services</t>
+        </is>
+      </c>
+      <c r="G39" s="118" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="H39" s="124" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="I39" s="125" t="inlineStr">
+        <is>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+        </is>
+      </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="20.4" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="40" t="n"/>
-      <c r="F40" s="40" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="91" t="n"/>
-      <c r="I40" s="53" t="n"/>
+      <c r="B40" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="inlineStr">
+        <is>
+          <t>KXS</t>
+        </is>
+      </c>
+      <c r="D40" s="116" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc.</t>
+        </is>
+      </c>
+      <c r="E40" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F40" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G40" s="118" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="H40" s="119" t="n">
+        <v>3333.46</v>
+      </c>
+      <c r="I40" s="120" t="inlineStr">
+        <is>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+        </is>
+      </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="15.6" customHeight="1" thickBot="1">
+    <row r="41" ht="70" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="70" t="n"/>
-      <c r="D41" s="71" t="n"/>
-      <c r="E41" s="72" t="n"/>
-      <c r="F41" s="72" t="n"/>
-      <c r="G41" s="94" t="n"/>
-      <c r="H41" s="96" t="n"/>
-      <c r="I41" s="74" t="n"/>
+      <c r="B41" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C41" s="130" t="inlineStr">
+        <is>
+          <t>DSG</t>
+        </is>
+      </c>
+      <c r="D41" s="131" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc.</t>
+        </is>
+      </c>
+      <c r="E41" s="132" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F41" s="132" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G41" s="133" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="H41" s="134" t="n">
+        <v>6794.59</v>
+      </c>
+      <c r="I41" s="135" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+        </is>
+      </c>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="8" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="43" t="n"/>
-      <c r="E42" s="43" t="n"/>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="43" t="n"/>
-      <c r="I42" s="43" t="n"/>
+      <c r="B42" s="136" t="n"/>
+      <c r="C42" s="136" t="n"/>
+      <c r="D42" s="136" t="n"/>
+      <c r="E42" s="136" t="n"/>
+      <c r="F42" s="136" t="n"/>
+      <c r="G42" s="136" t="n"/>
+      <c r="H42" s="136" t="n"/>
+      <c r="I42" s="136" t="n"/>
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
-    <row r="43" ht="15.6" customHeight="1" thickBot="1">
+    <row r="43" ht="34" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="137" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C43" s="138" t="n"/>
+      <c r="D43" s="138" t="n"/>
+      <c r="E43" s="138" t="n"/>
+      <c r="F43" s="138" t="n"/>
+      <c r="G43" s="138" t="n"/>
+      <c r="H43" s="138" t="n"/>
+      <c r="I43" s="138" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="12" customHeight="1">
+    <row r="44" ht="28" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="58" t="n"/>
-      <c r="C44" s="59" t="n"/>
-      <c r="D44" s="59" t="n"/>
-      <c r="E44" s="59" t="n"/>
-      <c r="F44" s="59" t="n"/>
-      <c r="G44" s="59" t="n"/>
-      <c r="H44" s="59" t="n"/>
-      <c r="I44" s="60" t="n"/>
+      <c r="B44" s="139" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C44" s="140" t="n"/>
+      <c r="D44" s="140" t="n"/>
+      <c r="E44" s="140" t="n"/>
+      <c r="F44" s="140" t="n"/>
+      <c r="G44" s="140" t="n"/>
+      <c r="H44" s="140" t="n"/>
+      <c r="I44" s="140" t="n"/>
       <c r="J44" s="60" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
@@ -3626,12 +3755,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B38:I38"/>
     <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B43:I43"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G36">
+  <conditionalFormatting sqref="G8:G41">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4572,7 +4701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4612,7 +4741,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46317.65719571945</v>
+        <v>46318.66168135779</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4745,7 +4874,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.034</v>
+        <v>1.009</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>14054.04</v>
@@ -4786,7 +4915,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>16701.36</v>
@@ -4827,7 +4956,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.767</v>
+        <v>0.778</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>45398.38</v>
@@ -4868,7 +4997,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>142623.33</v>
@@ -4881,7 +5010,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4890,39 +5019,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>42172.99</v>
+        <v>17904.45</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4931,33 +5060,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>17904.45</v>
+        <v>42172.99</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4991,7 +5120,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.66</v>
+        <v>0.634</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>32165.5</v>
@@ -5013,33 +5142,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.571</v>
+        <v>0.499</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>104249.82</v>
+        <v>42201.2</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -5073,7 +5202,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.516</v>
+        <v>0.483</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>9701.92</v>
@@ -5095,12 +5224,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -5110,18 +5239,18 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.516</v>
+        <v>0.481</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>1054668.83</v>
+        <v>47137.94</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -5136,12 +5265,12 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -5151,18 +5280,18 @@
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.515</v>
+        <v>0.48</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>47137.94</v>
+        <v>1054668.83</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5177,39 +5306,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.51</v>
+        <v>0.402</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>42201.2</v>
+        <v>12471.61</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>The J</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -5218,33 +5347,33 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.351</v>
+        <v>0.345</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>28342.5</v>
+        <v>12451.88</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
@@ -5259,39 +5388,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.349</v>
+        <v>0.321</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>12451.88</v>
+        <v>224207.66</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="126" t="inlineStr">
         <is>
@@ -5300,33 +5429,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.338</v>
+        <v>0.316</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>224207.66</v>
+        <v>61019.13</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5341,33 +5470,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.332</v>
+        <v>0.269</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>61019.13</v>
+        <v>60523.16</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -5382,12 +5511,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -5401,14 +5530,14 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.271</v>
+        <v>0.259</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>371563.85</v>
+        <v>41984.2</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5442,7 +5571,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.27</v>
+        <v>0.253</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>87408.73</v>
@@ -5464,33 +5593,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.269</v>
+        <v>0.252</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>41984.2</v>
+        <v>12857.61</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5505,39 +5634,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Roper Technologies Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.266</v>
+        <v>0.239</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>15537.74</v>
+        <v>35615.09</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="126" t="inlineStr">
         <is>
@@ -5546,39 +5675,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.266</v>
+        <v>0.236</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>20324.32</v>
+        <v>16850.47</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5587,39 +5716,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.243</v>
+        <v>0.218</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>12857.61</v>
+        <v>12320.13</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="126" t="inlineStr">
         <is>
@@ -5628,39 +5757,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.229</v>
+        <v>0.199</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>47993.25</v>
+        <v>23268.86</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>eBay Inc together with its subsidiaries operates marketplace platforms that connect buyers and sellers in the United States the United Kingdom China Germany and internationally</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5669,39 +5798,39 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Broadridge Financial Solutions Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.215</v>
+        <v>0.189</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>16850.47</v>
+        <v>17905.95</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
+          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="126" t="inlineStr">
         <is>
@@ -5710,33 +5839,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.205</v>
+        <v>0.175</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>17905.95</v>
+        <v>15869.76</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
+          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5751,39 +5880,39 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.202</v>
+        <v>0.166</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>156513.85</v>
+        <v>57901.58</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="52" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="126" t="inlineStr">
         <is>
@@ -5792,39 +5921,39 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Tyler Technologies Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.192</v>
+        <v>0.151</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>23268.86</v>
+        <v>13525.55</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="126" t="inlineStr">
         <is>
@@ -5833,39 +5962,39 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>EOG Resources Inc.</t>
+          <t>Nasdaq Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.187</v>
+        <v>0.149</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>75763.52</v>
+        <v>51024.57</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="52" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="126" t="inlineStr">
         <is>
@@ -5874,39 +6003,39 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>Avery Dennison Corporation</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Containers and Packaging</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.185</v>
+        <v>0.119</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>12320.13</v>
+        <v>12719.07</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="70" customHeight="1">
+    <row r="37" ht="52" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="126" t="inlineStr">
         <is>
@@ -5915,39 +6044,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Dollar General Corporation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.178</v>
+        <v>0.107</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>27315.89</v>
+        <v>73585.95</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
+          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="88" customHeight="1">
+    <row r="38" ht="52" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -5956,156 +6085,156 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.175</v>
+        <v>0.094</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>15869.76</v>
+        <v>345602.03</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="52" customHeight="1">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Republic Services Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.17</v>
+        <v>0.743</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>66372.58</v>
+        <v>17950.14</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="70" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B40" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc.</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.165</v>
+        <v>0.569</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>13525.55</v>
+        <v>104249.82</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="70" customHeight="1">
+    <row r="41" ht="88" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B41" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.164</v>
+        <v>0.548</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>57901.58</v>
+        <v>11772.74</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -6113,81 +6242,81 @@
     </row>
     <row r="42" ht="70" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B42" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Nasdaq Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.145</v>
+        <v>0.463</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>51024.57</v>
+        <v>480788.44</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="52" customHeight="1">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B43" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.143</v>
+        <v>0.425</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>22965.61</v>
+        <v>116683.09</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
@@ -6195,40 +6324,40 @@
     </row>
     <row r="44" ht="52" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B44" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.131</v>
+        <v>0.422</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>345602.03</v>
+        <v>21029.38</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6236,87 +6365,87 @@
     </row>
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B45" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.119</v>
+        <v>0.416</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>73585.95</v>
+        <v>33875.2</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="52" customHeight="1">
+    <row r="46" ht="70" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B46" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.114</v>
+        <v>0.391</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>178216.54</v>
+        <v>33430.82</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>The Walt Disney Company operates as an entertainment company in Americas Europe and the Asia Pacific</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="52" customHeight="1" thickBot="1">
+    <row r="47" ht="70" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6325,39 +6454,39 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>3.619</v>
+        <v>0.377</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>74971.71000000001</v>
+        <v>15537.74</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
-    <row r="48" ht="70" customHeight="1">
+    <row r="48" ht="106" customHeight="1">
       <c r="A48" s="43" t="n"/>
       <c r="B48" s="127" t="inlineStr">
         <is>
@@ -6366,12 +6495,12 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
@@ -6381,24 +6510,24 @@
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>1.017</v>
+        <v>0.342</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>45576.53</v>
+        <v>48910.32</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="1">
+    <row r="49" ht="88" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6407,39 +6536,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.716</v>
+        <v>0.337</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>17950.14</v>
+        <v>21455.05</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="88" customHeight="1">
+    <row r="50" ht="70" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6447,33 +6576,33 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F50" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G50" s="118" t="n">
-        <v>0.539</v>
+        <v>0.327</v>
       </c>
       <c r="H50" s="119" t="n">
-        <v>11772.74</v>
+        <v>24969.64</v>
       </c>
       <c r="I50" s="120" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
     </row>
@@ -6485,37 +6614,37 @@
       </c>
       <c r="C51" s="121" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D51" s="122" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E51" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F51" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.461</v>
+        <v>0.325</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>241617.28</v>
+        <v>28342.5</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="70" customHeight="1">
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1">
       <c r="B52" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6523,33 +6652,33 @@
       </c>
       <c r="C52" s="115" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D52" s="116" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E52" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F52" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G52" s="118" t="n">
-        <v>0.457</v>
+        <v>0.324</v>
       </c>
       <c r="H52" s="119" t="n">
-        <v>480788.44</v>
+        <v>682021.24</v>
       </c>
       <c r="I52" s="120" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -6561,185 +6690,185 @@
       </c>
       <c r="C53" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D53" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E53" s="123" t="inlineStr">
         <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F53" s="123" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G53" s="118" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="H53" s="124" t="n">
+        <v>30639.57</v>
+      </c>
+      <c r="I53" s="125" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="70" customHeight="1">
+      <c r="B54" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C54" s="115" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D54" s="116" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E54" s="117" t="inlineStr">
+        <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F53" s="123" t="inlineStr">
+      <c r="F54" s="117" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="G53" s="118" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="H53" s="124" t="n">
-        <v>116683.09</v>
-      </c>
-      <c r="I53" s="125" t="inlineStr">
-        <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="52" customHeight="1">
-      <c r="B54" s="127" t="inlineStr">
+      <c r="G54" s="118" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="H54" s="119" t="n">
+        <v>25579.38</v>
+      </c>
+      <c r="I54" s="120" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="B55" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C54" s="115" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="D54" s="116" t="inlineStr">
-        <is>
-          <t>PTC Inc.</t>
-        </is>
-      </c>
-      <c r="E54" s="117" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F54" s="117" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G54" s="118" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="H54" s="119" t="n">
-        <v>21029.38</v>
-      </c>
-      <c r="I54" s="120" t="inlineStr">
-        <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="52" customHeight="1">
-      <c r="B55" s="127" t="inlineStr">
+      <c r="C55" s="121" t="inlineStr">
+        <is>
+          <t>WST</t>
+        </is>
+      </c>
+      <c r="D55" s="122" t="inlineStr">
+        <is>
+          <t>West Pharmaceutical Services Inc.</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F55" s="123" t="inlineStr">
+        <is>
+          <t>Life Sciences Tools and Services</t>
+        </is>
+      </c>
+      <c r="G55" s="118" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H55" s="124" t="n">
+        <v>26039.81</v>
+      </c>
+      <c r="I55" s="125" t="inlineStr">
+        <is>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="52" customHeight="1">
+      <c r="B56" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C55" s="121" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="D55" s="122" t="inlineStr">
-        <is>
-          <t>The Estée Lauder Companies Inc.</t>
-        </is>
-      </c>
-      <c r="E55" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F55" s="123" t="inlineStr">
-        <is>
-          <t>Personal Care Products</t>
-        </is>
-      </c>
-      <c r="G55" s="118" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="H55" s="124" t="n">
-        <v>33875.2</v>
-      </c>
-      <c r="I55" s="125" t="inlineStr">
-        <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="70" customHeight="1">
-      <c r="B56" s="127" t="inlineStr">
+      <c r="C56" s="115" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="D56" s="116" t="inlineStr">
+        <is>
+          <t>Chevron Corporation</t>
+        </is>
+      </c>
+      <c r="E56" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F56" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="H56" s="119" t="n">
+        <v>404759.18</v>
+      </c>
+      <c r="I56" s="120" t="inlineStr">
+        <is>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="B57" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C56" s="115" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
-      </c>
-      <c r="D56" s="116" t="inlineStr">
-        <is>
-          <t>Biogen Inc.</t>
-        </is>
-      </c>
-      <c r="E56" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F56" s="117" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="G56" s="118" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="H56" s="119" t="n">
-        <v>33430.82</v>
-      </c>
-      <c r="I56" s="120" t="inlineStr">
-        <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="106" customHeight="1">
-      <c r="B57" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
       <c r="C57" s="121" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D57" s="122" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E57" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F57" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G57" s="118" t="n">
-        <v>0.343</v>
+        <v>0.27</v>
       </c>
       <c r="H57" s="124" t="n">
-        <v>48910.32</v>
+        <v>156513.85</v>
       </c>
       <c r="I57" s="125" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
     </row>
@@ -6751,33 +6880,33 @@
       </c>
       <c r="C58" s="115" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D58" s="116" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E58" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G58" s="118" t="n">
-        <v>0.34</v>
+        <v>0.259</v>
       </c>
       <c r="H58" s="119" t="n">
-        <v>25579.38</v>
+        <v>151241.83</v>
       </c>
       <c r="I58" s="120" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
     </row>
@@ -6789,37 +6918,37 @@
       </c>
       <c r="C59" s="121" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D59" s="122" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E59" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F59" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G59" s="118" t="n">
-        <v>0.336</v>
+        <v>0.255</v>
       </c>
       <c r="H59" s="124" t="n">
-        <v>682021.24</v>
+        <v>54537.32</v>
       </c>
       <c r="I59" s="125" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="70" customHeight="1">
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="88" customHeight="1">
       <c r="B60" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6827,33 +6956,33 @@
       </c>
       <c r="C60" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D60" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E60" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F60" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G60" s="118" t="n">
-        <v>0.332</v>
+        <v>0.254</v>
       </c>
       <c r="H60" s="119" t="n">
-        <v>24969.64</v>
+        <v>75763.52</v>
       </c>
       <c r="I60" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
         </is>
       </c>
     </row>
@@ -6865,109 +6994,109 @@
       </c>
       <c r="C61" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D61" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E61" s="123" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F61" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G61" s="118" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="H61" s="124" t="n">
+        <v>677009.86</v>
+      </c>
+      <c r="I61" s="125" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="70" customHeight="1">
+      <c r="B62" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C62" s="115" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="D62" s="116" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="E62" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F62" s="117" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G62" s="118" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H62" s="119" t="n">
+        <v>371563.85</v>
+      </c>
+      <c r="I62" s="120" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="70" customHeight="1">
+      <c r="B63" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C63" s="121" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D63" s="122" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc.</t>
+        </is>
+      </c>
+      <c r="E63" s="123" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F61" s="123" t="inlineStr">
-        <is>
-          <t>Life Sciences Tools and Services</t>
-        </is>
-      </c>
-      <c r="G61" s="118" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H61" s="124" t="n">
-        <v>30639.57</v>
-      </c>
-      <c r="I61" s="125" t="inlineStr">
-        <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="88" customHeight="1">
-      <c r="B62" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C62" s="115" t="inlineStr">
-        <is>
-          <t>IFF</t>
-        </is>
-      </c>
-      <c r="D62" s="116" t="inlineStr">
-        <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
-        </is>
-      </c>
-      <c r="E62" s="117" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F62" s="117" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="G62" s="118" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="H62" s="119" t="n">
-        <v>21455.05</v>
-      </c>
-      <c r="I62" s="120" t="inlineStr">
-        <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="88" customHeight="1">
-      <c r="B63" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C63" s="121" t="inlineStr">
-        <is>
-          <t>WST</t>
-        </is>
-      </c>
-      <c r="D63" s="122" t="inlineStr">
-        <is>
-          <t>West Pharmaceutical Services Inc.</t>
-        </is>
-      </c>
-      <c r="E63" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F63" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G63" s="118" t="n">
-        <v>0.296</v>
+        <v>0.243</v>
       </c>
       <c r="H63" s="124" t="n">
-        <v>26039.81</v>
+        <v>183538.16</v>
       </c>
       <c r="I63" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
     </row>
@@ -6979,33 +7108,33 @@
       </c>
       <c r="C64" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D64" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E64" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F64" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G64" s="118" t="n">
-        <v>0.293</v>
+        <v>0.23</v>
       </c>
       <c r="H64" s="119" t="n">
-        <v>151241.83</v>
+        <v>498865.76</v>
       </c>
       <c r="I64" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7017,12 +7146,12 @@
       </c>
       <c r="C65" s="121" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="D65" s="122" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E65" s="123" t="inlineStr">
@@ -7036,14 +7165,14 @@
         </is>
       </c>
       <c r="G65" s="118" t="n">
-        <v>0.28</v>
+        <v>0.222</v>
       </c>
       <c r="H65" s="124" t="n">
-        <v>54537.32</v>
+        <v>108638.32</v>
       </c>
       <c r="I65" s="125" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7055,33 +7184,33 @@
       </c>
       <c r="C66" s="115" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D66" s="116" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E66" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F66" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G66" s="118" t="n">
-        <v>0.248</v>
+        <v>0.177</v>
       </c>
       <c r="H66" s="119" t="n">
-        <v>498865.76</v>
+        <v>111058.59</v>
       </c>
       <c r="I66" s="120" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
     </row>
@@ -7093,33 +7222,33 @@
       </c>
       <c r="C67" s="121" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D67" s="122" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E67" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F67" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G67" s="118" t="n">
-        <v>0.235</v>
+        <v>0.17</v>
       </c>
       <c r="H67" s="124" t="n">
-        <v>404759.18</v>
+        <v>66372.58</v>
       </c>
       <c r="I67" s="125" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7260,12 @@
       </c>
       <c r="C68" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D68" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E68" s="117" t="inlineStr">
@@ -7146,18 +7275,18 @@
       </c>
       <c r="F68" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G68" s="118" t="n">
-        <v>0.233</v>
+        <v>0.161</v>
       </c>
       <c r="H68" s="119" t="n">
-        <v>183538.16</v>
+        <v>159089.29</v>
       </c>
       <c r="I68" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7169,33 +7298,33 @@
       </c>
       <c r="C69" s="121" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="D69" s="122" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Ulta Beauty Inc.</t>
         </is>
       </c>
       <c r="E69" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F69" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G69" s="118" t="n">
-        <v>0.224</v>
+        <v>0.155</v>
       </c>
       <c r="H69" s="124" t="n">
-        <v>108638.32</v>
+        <v>23628.33</v>
       </c>
       <c r="I69" s="125" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
         </is>
       </c>
     </row>
@@ -7207,33 +7336,33 @@
       </c>
       <c r="C70" s="115" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D70" s="116" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E70" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F70" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G70" s="118" t="n">
-        <v>0.201</v>
+        <v>0.152</v>
       </c>
       <c r="H70" s="119" t="n">
-        <v>677009.86</v>
+        <v>31594.32</v>
       </c>
       <c r="I70" s="120" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7245,33 +7374,33 @@
       </c>
       <c r="C71" s="121" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D71" s="122" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E71" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F71" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G71" s="118" t="n">
-        <v>0.177</v>
+        <v>0.137</v>
       </c>
       <c r="H71" s="124" t="n">
-        <v>111058.59</v>
+        <v>27315.89</v>
       </c>
       <c r="I71" s="125" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
     </row>
@@ -7283,50 +7412,50 @@
       </c>
       <c r="C72" s="115" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D72" s="116" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc.</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E72" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F72" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G72" s="118" t="n">
-        <v>0.17</v>
+        <v>0.112</v>
       </c>
       <c r="H72" s="119" t="n">
-        <v>23628.33</v>
+        <v>22965.61</v>
       </c>
       <c r="I72" s="120" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="70" customHeight="1">
-      <c r="B73" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+          <t>Church &amp; Dwight Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="52" customHeight="1">
+      <c r="B73" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C73" s="121" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D73" s="122" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E73" s="123" t="inlineStr">
@@ -7336,144 +7465,106 @@
       </c>
       <c r="F73" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G73" s="118" t="n">
-        <v>0.169</v>
+        <v>3.227</v>
       </c>
       <c r="H73" s="124" t="n">
-        <v>159089.29</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I73" s="125" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
     </row>
     <row r="74" ht="70" customHeight="1">
-      <c r="B74" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C74" s="115" t="inlineStr">
-        <is>
-          <t>RMD</t>
-        </is>
-      </c>
-      <c r="D74" s="116" t="inlineStr">
-        <is>
-          <t>ResMed Inc.</t>
-        </is>
-      </c>
-      <c r="E74" s="117" t="inlineStr">
+      <c r="B74" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C74" s="141" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D74" s="142" t="inlineStr">
+        <is>
+          <t>Veeva Systems Inc.</t>
+        </is>
+      </c>
+      <c r="E74" s="143" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F74" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G74" s="118" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H74" s="119" t="n">
-        <v>31594.32</v>
-      </c>
-      <c r="I74" s="120" t="inlineStr">
-        <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="52" customHeight="1">
-      <c r="B75" s="147" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C75" s="148" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="D75" s="149" t="inlineStr">
-        <is>
-          <t>Cencora Inc.</t>
-        </is>
-      </c>
-      <c r="E75" s="150" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F75" s="150" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G75" s="133" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="H75" s="151" t="n">
-        <v>61416.01</v>
-      </c>
-      <c r="I75" s="152" t="inlineStr">
-        <is>
-          <t>Cencora Inc sources and distributes pharmaceutical products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1">
-      <c r="B76" s="153" t="n"/>
-      <c r="C76" s="153" t="n"/>
-      <c r="D76" s="153" t="n"/>
-      <c r="E76" s="153" t="n"/>
-      <c r="F76" s="153" t="n"/>
-      <c r="G76" s="153" t="n"/>
-      <c r="H76" s="153" t="n"/>
-      <c r="I76" s="153" t="n"/>
-    </row>
-    <row r="77" ht="34" customHeight="1">
-      <c r="B77" s="143" t="inlineStr">
+      <c r="F74" s="143" t="inlineStr">
+        <is>
+          <t>Health Care Technology</t>
+        </is>
+      </c>
+      <c r="G74" s="133" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="H74" s="144" t="n">
+        <v>45576.53</v>
+      </c>
+      <c r="I74" s="145" t="inlineStr">
+        <is>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1">
+      <c r="B75" s="136" t="n"/>
+      <c r="C75" s="136" t="n"/>
+      <c r="D75" s="136" t="n"/>
+      <c r="E75" s="136" t="n"/>
+      <c r="F75" s="136" t="n"/>
+      <c r="G75" s="136" t="n"/>
+      <c r="H75" s="136" t="n"/>
+      <c r="I75" s="136" t="n"/>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="B76" s="137" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C77" s="144" t="n"/>
-      <c r="D77" s="144" t="n"/>
-      <c r="E77" s="144" t="n"/>
-      <c r="F77" s="144" t="n"/>
-      <c r="G77" s="144" t="n"/>
-      <c r="H77" s="144" t="n"/>
-      <c r="I77" s="144" t="n"/>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="B78" s="145" t="inlineStr">
+      <c r="C76" s="138" t="n"/>
+      <c r="D76" s="138" t="n"/>
+      <c r="E76" s="138" t="n"/>
+      <c r="F76" s="138" t="n"/>
+      <c r="G76" s="138" t="n"/>
+      <c r="H76" s="138" t="n"/>
+      <c r="I76" s="138" t="n"/>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="B77" s="139" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C78" s="146" t="n"/>
-      <c r="D78" s="146" t="n"/>
-      <c r="E78" s="146" t="n"/>
-      <c r="F78" s="146" t="n"/>
-      <c r="G78" s="146" t="n"/>
-      <c r="H78" s="146" t="n"/>
-      <c r="I78" s="146" t="n"/>
+      <c r="C77" s="140" t="n"/>
+      <c r="D77" s="140" t="n"/>
+      <c r="E77" s="140" t="n"/>
+      <c r="F77" s="140" t="n"/>
+      <c r="G77" s="140" t="n"/>
+      <c r="H77" s="140" t="n"/>
+      <c r="I77" s="140" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B78:I78"/>
     <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B76:I76"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G75">
+  <conditionalFormatting sqref="G8:G74">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$80</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -575,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -941,21 +941,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2079,7 +2064,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46318.66168135779</v>
+        <v>46321.71272094517</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2141,7 +2126,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46318.66168135779</v>
+        <v>46321.71272094517</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2246,7 +2231,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2255,39 +2240,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>HLF</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>High Liner Foods Incorporated</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.662</v>
+        <v>1.017</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>884.7</v>
+        <v>284.17</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>High Liner Foods Incorporated processes and markets prepared and packaged frozen seafood products in North America</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2296,39 +2281,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.548</v>
+        <v>0.487</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>732.01</v>
+        <v>1836.63</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2337,33 +2322,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Constellation Software Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.53</v>
+        <v>0.367</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1836.63</v>
+        <v>43632.38</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2397,7 +2382,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.451</v>
+        <v>0.361</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>43014.26</v>
@@ -2410,7 +2395,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2419,12 +2404,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>CFW</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Calfrac Well Services Ltd.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2434,24 +2419,24 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.409</v>
+        <v>0.317</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>804.05</v>
+        <v>478.75</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2460,12 +2445,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Constellation Software Inc.</t>
+          <t>Open Text Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -2479,14 +2464,14 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.393</v>
+        <v>0.29</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>43632.38</v>
+        <v>5405.28</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
+          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2501,39 +2486,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.383</v>
+        <v>0.219</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>373.79</v>
+        <v>69914.25999999999</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2542,39 +2527,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>WCN</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Open Text Corporation</t>
+          <t>Waste Connections Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.295</v>
+        <v>0.172</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>5405.28</v>
+        <v>39435.42</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
+          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2583,39 +2568,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>TNZ</t>
+          <t>XTC</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Tenaz Energy Corp.</t>
+          <t>Exco Technologies Limited</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Automobile Components</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.239</v>
+        <v>0.171</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>1570.2</v>
+        <v>220.37</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Tenaz Energy Corp an energy company engages in the acquisition and development of oil and gas assets in Canada and the Netherlands</t>
+          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2624,39 +2609,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>ENGH</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Enghouse Systems Limited</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.22</v>
+        <v>0.157</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>4428.98</v>
+        <v>634.6900000000001</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="106" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2665,238 +2650,238 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Loblaw Companies Limited</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.205</v>
+        <v>0.105</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>69914.25999999999</v>
+        <v>50539.87</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>WCN</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Waste Connections Inc.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.19</v>
+        <v>0.696</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>39435.42</v>
+        <v>884.7</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="88" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>VET</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.182</v>
+        <v>0.668</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>1789.16</v>
+        <v>600.1</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="52" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B21" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Algoma Central Corporation</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Marine Transportation</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.168</v>
+        <v>0.474</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>2245.27</v>
+        <v>743.0700000000001</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B22" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>ENGH</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.158</v>
+        <v>0.4</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>634.6900000000001</v>
+        <v>925.72</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="88" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>XTC</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Automobile Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.155</v>
+        <v>0.348</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>220.37</v>
+        <v>804.05</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2904,19 +2889,19 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B24" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>GFR</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Greenfire Resources Ltd.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -2930,55 +2915,55 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.152</v>
+        <v>0.314</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>1476.14</v>
+        <v>15597.29</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Greenfire Resources Ltd together with its subsidiaries engages in the exploration development and operation of oil and gas properties in the Athabasca oil sands region of Alberta Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="106" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B25" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>50539.87</v>
+        <v>373.79</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2986,40 +2971,40 @@
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>NWC</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>The North West Company Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.119</v>
+        <v>0.249</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>1823.99</v>
+        <v>336.54</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3034,39 +3019,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.709</v>
+        <v>0.248</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>600.1</v>
+        <v>389.1</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3075,12 +3060,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3094,20 +3079,20 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.519</v>
+        <v>0.234</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>925.72</v>
+        <v>80962.39</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="106" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3116,39 +3101,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.464</v>
+        <v>0.219</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>99672.56</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -3157,33 +3142,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.376</v>
+        <v>0.214</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>15597.29</v>
+        <v>35208.26</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -3198,12 +3183,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -3217,20 +3202,20 @@
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.294</v>
+        <v>0.198</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>336.54</v>
+        <v>3837.96</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="106" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -3239,12 +3224,12 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
@@ -3258,20 +3243,20 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.287</v>
+        <v>0.194</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>99672.56</v>
+        <v>1545.36</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="52" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="127" t="inlineStr">
         <is>
@@ -3280,12 +3265,12 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -3299,14 +3284,14 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.284</v>
+        <v>0.176</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>80962.39</v>
+        <v>4428.98</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -3321,33 +3306,33 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>E-L Financial Corporation Limited</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.234</v>
+        <v>0.171</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>35208.26</v>
+        <v>4283.74</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -3362,33 +3347,33 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>DTOL</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>D2L Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Diversified Consumer Services</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.225</v>
+        <v>0.16</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>1545.36</v>
+        <v>382.43</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
@@ -3403,12 +3388,12 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
@@ -3422,20 +3407,20 @@
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.222</v>
+        <v>0.148</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>3837.96</v>
+        <v>2245.27</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="52" customHeight="1">
+    <row r="37" ht="106" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="127" t="inlineStr">
         <is>
@@ -3444,115 +3429,115 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.196</v>
+        <v>0.101</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>389.1</v>
+        <v>398.33</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B38" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.161</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>4283.74</v>
+        <v>732.01</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="88" customHeight="1">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B39" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.126</v>
+        <v>0.429</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>382.43</v>
+        <v>3333.46</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
@@ -3567,12 +3552,12 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
@@ -3586,14 +3571,14 @@
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.426</v>
+        <v>0.322</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>3333.46</v>
+        <v>6794.59</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
@@ -3608,33 +3593,33 @@
       </c>
       <c r="C41" s="130" t="inlineStr">
         <is>
-          <t>DSG</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D41" s="131" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E41" s="132" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F41" s="132" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G41" s="133" t="n">
-        <v>0.351</v>
+        <v>0.136</v>
       </c>
       <c r="H41" s="134" t="n">
-        <v>6794.59</v>
+        <v>1823.99</v>
       </c>
       <c r="I41" s="135" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J41" s="74" t="n"/>
@@ -4701,7 +4686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4741,7 +4726,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46318.66168135779</v>
+        <v>46321.71272094517</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4874,7 +4859,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.009</v>
+        <v>1.167</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>14054.04</v>
@@ -4915,7 +4900,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.819</v>
+        <v>0.948</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>16701.36</v>
@@ -4928,7 +4913,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4937,12 +4922,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Workday Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -4952,24 +4937,24 @@
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.778</v>
+        <v>0.802</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>45398.38</v>
+        <v>17950.14</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4978,39 +4963,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>ServiceNow Inc.</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.736</v>
+        <v>0.761</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>142623.33</v>
+        <v>42172.99</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
+          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -5019,39 +5004,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>ServiceNow Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.72</v>
+        <v>0.753</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>17904.45</v>
+        <v>142623.33</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -5060,39 +5045,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>42172.99</v>
+        <v>17904.45</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5101,39 +5086,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Workday Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.634</v>
+        <v>0.694</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>32165.5</v>
+        <v>45398.38</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
+          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -5142,12 +5127,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -5161,20 +5146,20 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.499</v>
+        <v>0.582</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>42201.2</v>
+        <v>47137.94</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -5183,33 +5168,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.483</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>9701.92</v>
+        <v>42201.2</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
@@ -5224,12 +5209,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -5239,18 +5224,18 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.481</v>
+        <v>0.507</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>47137.94</v>
+        <v>1054668.83</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -5265,33 +5250,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.48</v>
+        <v>0.398</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>1054668.83</v>
+        <v>9701.92</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5325,7 +5310,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.402</v>
+        <v>0.36</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>12471.61</v>
@@ -5347,33 +5332,33 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.345</v>
+        <v>0.32</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>12451.88</v>
+        <v>224207.66</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
@@ -5388,33 +5373,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.321</v>
+        <v>0.306</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>224207.66</v>
+        <v>12320.13</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
@@ -5448,7 +5433,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.316</v>
+        <v>0.282</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>61019.13</v>
@@ -5461,7 +5446,7 @@
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="126" t="inlineStr">
         <is>
@@ -5470,33 +5455,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.269</v>
+        <v>0.274</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>60523.16</v>
+        <v>12451.88</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -5511,39 +5496,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.259</v>
+        <v>0.264</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>41984.2</v>
+        <v>12857.61</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="126" t="inlineStr">
         <is>
@@ -5552,12 +5537,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Elevance Health Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -5571,20 +5556,20 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.253</v>
+        <v>0.261</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>87408.73</v>
+        <v>32165.5</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
+          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="106" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="126" t="inlineStr">
         <is>
@@ -5593,33 +5578,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Aerospace and Defense</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.252</v>
+        <v>0.249</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>12857.61</v>
+        <v>116283.92</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5653,7 +5638,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.239</v>
+        <v>0.237</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>35615.09</v>
@@ -5666,7 +5651,7 @@
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="126" t="inlineStr">
         <is>
@@ -5675,33 +5660,33 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.236</v>
+        <v>0.233</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>16850.47</v>
+        <v>60523.16</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
@@ -5716,39 +5701,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.218</v>
+        <v>0.223</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>12320.13</v>
+        <v>16850.47</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="126" t="inlineStr">
         <is>
@@ -5757,33 +5742,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.199</v>
+        <v>0.216</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>23268.86</v>
+        <v>41984.2</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
+          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -5798,12 +5783,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5813,18 +5798,18 @@
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.189</v>
+        <v>0.206</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>17905.95</v>
+        <v>57901.58</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -5858,7 +5843,7 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.175</v>
+        <v>0.166</v>
       </c>
       <c r="H32" s="119" t="n">
         <v>15869.76</v>
@@ -5871,7 +5856,7 @@
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="52" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="126" t="inlineStr">
         <is>
@@ -5880,12 +5865,12 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -5895,24 +5880,24 @@
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.166</v>
+        <v>0.159</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>57901.58</v>
+        <v>23268.86</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="52" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="126" t="inlineStr">
         <is>
@@ -5921,33 +5906,33 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc.</t>
+          <t>Elevance Health Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.151</v>
+        <v>0.154</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>13525.55</v>
+        <v>87408.73</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -5981,7 +5966,7 @@
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.149</v>
+        <v>0.145</v>
       </c>
       <c r="H35" s="124" t="n">
         <v>51024.57</v>
@@ -6003,39 +5988,39 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation</t>
+          <t>Broadridge Financial Solutions Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Containers and Packaging</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.119</v>
+        <v>0.143</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>12719.07</v>
+        <v>17905.95</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
+          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="52" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="126" t="inlineStr">
         <is>
@@ -6044,39 +6029,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Avery Dennison Corporation</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Containers and Packaging</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.107</v>
+        <v>0.135</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>73585.95</v>
+        <v>12719.07</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
+          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -6085,80 +6070,80 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Tyler Technologies Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.094</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>345602.03</v>
+        <v>13525.55</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row r="39" ht="52" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B39" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.743</v>
+        <v>0.056</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>17950.14</v>
+        <v>73585.95</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="52" customHeight="1">
+    <row r="40" ht="88" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="127" t="inlineStr">
         <is>
@@ -6167,39 +6152,39 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.569</v>
+        <v>0.531</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>104249.82</v>
+        <v>11772.74</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="88" customHeight="1">
+    <row r="41" ht="52" customHeight="1">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="127" t="inlineStr">
         <is>
@@ -6208,33 +6193,33 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.548</v>
+        <v>0.448</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>11772.74</v>
+        <v>33875.2</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -6268,7 +6253,7 @@
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.463</v>
+        <v>0.421</v>
       </c>
       <c r="H42" s="119" t="n">
         <v>480788.44</v>
@@ -6281,7 +6266,7 @@
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="70" customHeight="1">
+    <row r="43" ht="52" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6290,39 +6275,39 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.425</v>
+        <v>0.416</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>116683.09</v>
+        <v>104249.82</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="52" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
       <c r="B44" s="127" t="inlineStr">
         <is>
@@ -6331,12 +6316,12 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
@@ -6346,24 +6331,24 @@
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.422</v>
+        <v>0.386</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>21029.38</v>
+        <v>116683.09</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="52" customHeight="1">
+    <row r="45" ht="70" customHeight="1">
       <c r="A45" s="43" t="n"/>
       <c r="B45" s="127" t="inlineStr">
         <is>
@@ -6372,39 +6357,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.416</v>
+        <v>0.382</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>33875.2</v>
+        <v>28342.5</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row r="46" ht="88" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6413,39 +6398,39 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.391</v>
+        <v>0.376</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>33430.82</v>
+        <v>21455.05</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="70" customHeight="1" thickBot="1">
+    <row r="47" ht="106" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6454,39 +6439,39 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>15537.74</v>
+        <v>48910.32</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
-    <row r="48" ht="106" customHeight="1">
+    <row r="48" ht="70" customHeight="1">
       <c r="A48" s="43" t="n"/>
       <c r="B48" s="127" t="inlineStr">
         <is>
@@ -6495,12 +6480,12 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
@@ -6510,24 +6495,24 @@
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>48910.32</v>
+        <v>30639.57</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="88" customHeight="1">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6536,39 +6521,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.337</v>
+        <v>0.329</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>21455.05</v>
+        <v>24969.64</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="70" customHeight="1">
+    <row r="50" ht="88" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6576,33 +6561,33 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F50" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G50" s="118" t="n">
-        <v>0.327</v>
+        <v>0.322</v>
       </c>
       <c r="H50" s="119" t="n">
-        <v>24969.64</v>
+        <v>26039.81</v>
       </c>
       <c r="I50" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
     </row>
@@ -6614,37 +6599,37 @@
       </c>
       <c r="C51" s="121" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D51" s="122" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E51" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F51" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.325</v>
+        <v>0.303</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>28342.5</v>
+        <v>151241.83</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="52" customHeight="1">
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1">
       <c r="B52" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6652,33 +6637,33 @@
       </c>
       <c r="C52" s="115" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D52" s="116" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E52" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F52" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G52" s="118" t="n">
-        <v>0.324</v>
+        <v>0.296</v>
       </c>
       <c r="H52" s="119" t="n">
-        <v>682021.24</v>
+        <v>15537.74</v>
       </c>
       <c r="I52" s="120" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6675,12 @@
       </c>
       <c r="C53" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D53" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E53" s="123" t="inlineStr">
@@ -6705,18 +6690,18 @@
       </c>
       <c r="F53" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G53" s="118" t="n">
-        <v>0.306</v>
+        <v>0.284</v>
       </c>
       <c r="H53" s="124" t="n">
-        <v>30639.57</v>
+        <v>33430.82</v>
       </c>
       <c r="I53" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6732,7 @@
         </is>
       </c>
       <c r="G54" s="118" t="n">
-        <v>0.305</v>
+        <v>0.265</v>
       </c>
       <c r="H54" s="119" t="n">
         <v>25579.38</v>
@@ -6758,7 +6743,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="88" customHeight="1">
+    <row r="55" ht="52" customHeight="1">
       <c r="B55" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6766,12 +6751,12 @@
       </c>
       <c r="C55" s="121" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D55" s="122" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E55" s="123" t="inlineStr">
@@ -6781,22 +6766,22 @@
       </c>
       <c r="F55" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G55" s="118" t="n">
-        <v>0.299</v>
+        <v>0.247</v>
       </c>
       <c r="H55" s="124" t="n">
-        <v>26039.81</v>
+        <v>54537.32</v>
       </c>
       <c r="I55" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="52" customHeight="1">
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
       <c r="B56" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6804,109 +6789,109 @@
       </c>
       <c r="C56" s="115" t="inlineStr">
         <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D56" s="116" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F56" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="H56" s="119" t="n">
+        <v>183538.16</v>
+      </c>
+      <c r="I56" s="120" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="B57" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C57" s="121" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="D56" s="116" t="inlineStr">
+      <c r="D57" s="122" t="inlineStr">
         <is>
           <t>Chevron Corporation</t>
         </is>
       </c>
-      <c r="E56" s="117" t="inlineStr">
+      <c r="E57" s="123" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F56" s="117" t="inlineStr">
+      <c r="F57" s="123" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G56" s="118" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="H56" s="119" t="n">
+      <c r="G57" s="118" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="H57" s="124" t="n">
         <v>404759.18</v>
       </c>
-      <c r="I56" s="120" t="inlineStr">
+      <c r="I57" s="125" t="inlineStr">
         <is>
           <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="70" customHeight="1">
-      <c r="B57" s="127" t="inlineStr">
+    <row r="58" ht="52" customHeight="1">
+      <c r="B58" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C57" s="121" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="D57" s="122" t="inlineStr">
-        <is>
-          <t>ConocoPhillips</t>
-        </is>
-      </c>
-      <c r="E57" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F57" s="123" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G57" s="118" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H57" s="124" t="n">
-        <v>156513.85</v>
-      </c>
-      <c r="I57" s="125" t="inlineStr">
-        <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="70" customHeight="1">
-      <c r="B58" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
       <c r="C58" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D58" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E58" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F58" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G58" s="118" t="n">
-        <v>0.259</v>
+        <v>0.211</v>
       </c>
       <c r="H58" s="119" t="n">
-        <v>151241.83</v>
+        <v>682021.24</v>
       </c>
       <c r="I58" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -6918,12 +6903,12 @@
       </c>
       <c r="C59" s="121" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="D59" s="122" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E59" s="123" t="inlineStr">
@@ -6937,18 +6922,18 @@
         </is>
       </c>
       <c r="G59" s="118" t="n">
-        <v>0.255</v>
+        <v>0.208</v>
       </c>
       <c r="H59" s="124" t="n">
-        <v>54537.32</v>
+        <v>108638.32</v>
       </c>
       <c r="I59" s="125" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="88" customHeight="1">
+          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
       <c r="B60" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6956,33 +6941,33 @@
       </c>
       <c r="C60" s="115" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D60" s="116" t="inlineStr">
         <is>
-          <t>EOG Resources Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E60" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F60" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G60" s="118" t="n">
-        <v>0.254</v>
+        <v>0.207</v>
       </c>
       <c r="H60" s="119" t="n">
-        <v>75763.52</v>
+        <v>111058.59</v>
       </c>
       <c r="I60" s="120" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
     </row>
@@ -7013,7 +6998,7 @@
         </is>
       </c>
       <c r="G61" s="118" t="n">
-        <v>0.253</v>
+        <v>0.206</v>
       </c>
       <c r="H61" s="124" t="n">
         <v>677009.86</v>
@@ -7032,33 +7017,33 @@
       </c>
       <c r="C62" s="115" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D62" s="116" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E62" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F62" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G62" s="118" t="n">
-        <v>0.252</v>
+        <v>0.199</v>
       </c>
       <c r="H62" s="119" t="n">
-        <v>371563.85</v>
+        <v>156513.85</v>
       </c>
       <c r="I62" s="120" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7055,12 @@
       </c>
       <c r="C63" s="121" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D63" s="122" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E63" s="123" t="inlineStr">
@@ -7085,22 +7070,22 @@
       </c>
       <c r="F63" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G63" s="118" t="n">
-        <v>0.243</v>
+        <v>0.195</v>
       </c>
       <c r="H63" s="124" t="n">
-        <v>183538.16</v>
+        <v>31594.32</v>
       </c>
       <c r="I63" s="125" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="70" customHeight="1">
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="88" customHeight="1">
       <c r="B64" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7108,37 +7093,37 @@
       </c>
       <c r="C64" s="115" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D64" s="116" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E64" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F64" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G64" s="118" t="n">
-        <v>0.23</v>
+        <v>0.191</v>
       </c>
       <c r="H64" s="119" t="n">
-        <v>498865.76</v>
+        <v>75763.52</v>
       </c>
       <c r="I64" s="120" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="52" customHeight="1">
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="70" customHeight="1">
       <c r="B65" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7146,33 +7131,33 @@
       </c>
       <c r="C65" s="121" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D65" s="122" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E65" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F65" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G65" s="118" t="n">
-        <v>0.222</v>
+        <v>0.189</v>
       </c>
       <c r="H65" s="124" t="n">
-        <v>108638.32</v>
+        <v>371563.85</v>
       </c>
       <c r="I65" s="125" t="inlineStr">
         <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7184,12 +7169,12 @@
       </c>
       <c r="C66" s="115" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D66" s="116" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E66" s="117" t="inlineStr">
@@ -7199,22 +7184,22 @@
       </c>
       <c r="F66" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G66" s="118" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="H66" s="119" t="n">
-        <v>111058.59</v>
+        <v>159089.29</v>
       </c>
       <c r="I66" s="120" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="52" customHeight="1">
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="70" customHeight="1">
       <c r="B67" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7222,37 +7207,37 @@
       </c>
       <c r="C67" s="121" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D67" s="122" t="inlineStr">
         <is>
-          <t>Republic Services Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E67" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F67" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G67" s="118" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="H67" s="124" t="n">
-        <v>66372.58</v>
+        <v>498865.76</v>
       </c>
       <c r="I67" s="125" t="inlineStr">
         <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="70" customHeight="1">
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
       <c r="B68" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7260,33 +7245,33 @@
       </c>
       <c r="C68" s="115" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="D68" s="116" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Ulta Beauty Inc.</t>
         </is>
       </c>
       <c r="E68" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F68" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G68" s="118" t="n">
-        <v>0.161</v>
+        <v>0.168</v>
       </c>
       <c r="H68" s="119" t="n">
-        <v>159089.29</v>
+        <v>23628.33</v>
       </c>
       <c r="I68" s="120" t="inlineStr">
         <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
         </is>
       </c>
     </row>
@@ -7298,33 +7283,33 @@
       </c>
       <c r="C69" s="121" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D69" s="122" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc.</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E69" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F69" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G69" s="118" t="n">
-        <v>0.155</v>
+        <v>0.165</v>
       </c>
       <c r="H69" s="124" t="n">
-        <v>23628.33</v>
+        <v>66372.58</v>
       </c>
       <c r="I69" s="125" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
     </row>
@@ -7336,33 +7321,33 @@
       </c>
       <c r="C70" s="115" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D70" s="116" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E70" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F70" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G70" s="118" t="n">
-        <v>0.152</v>
+        <v>0.136</v>
       </c>
       <c r="H70" s="119" t="n">
-        <v>31594.32</v>
+        <v>27315.89</v>
       </c>
       <c r="I70" s="120" t="inlineStr">
         <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
     </row>
@@ -7374,33 +7359,33 @@
       </c>
       <c r="C71" s="121" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="D71" s="122" t="inlineStr">
         <is>
-          <t>Dollar General Corporation</t>
+          <t>Universal Health Services Inc.</t>
         </is>
       </c>
       <c r="E71" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F71" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G71" s="118" t="n">
-        <v>0.137</v>
+        <v>0.109</v>
       </c>
       <c r="H71" s="124" t="n">
-        <v>27315.89</v>
+        <v>10428.64</v>
       </c>
       <c r="I71" s="125" t="inlineStr">
         <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
+          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
         </is>
       </c>
     </row>
@@ -7412,159 +7397,273 @@
       </c>
       <c r="C72" s="115" t="inlineStr">
         <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="D72" s="116" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="E72" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F72" s="117" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="G72" s="118" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="H72" s="119" t="n">
+        <v>345602.03</v>
+      </c>
+      <c r="I72" s="120" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="52" customHeight="1">
+      <c r="B73" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C73" s="121" t="inlineStr">
+        <is>
           <t>CHD</t>
         </is>
       </c>
-      <c r="D72" s="116" t="inlineStr">
+      <c r="D73" s="122" t="inlineStr">
         <is>
           <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
-      <c r="E72" s="117" t="inlineStr">
+      <c r="E73" s="123" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="F72" s="117" t="inlineStr">
+      <c r="F73" s="123" t="inlineStr">
         <is>
           <t>Household Products</t>
         </is>
       </c>
-      <c r="G72" s="118" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="H72" s="119" t="n">
+      <c r="G73" s="118" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H73" s="124" t="n">
         <v>22965.61</v>
       </c>
-      <c r="I72" s="120" t="inlineStr">
+      <c r="I73" s="125" t="inlineStr">
         <is>
           <t>Church &amp; Dwight Co</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="52" customHeight="1">
-      <c r="B73" s="128" t="inlineStr">
+    <row r="74" ht="52" customHeight="1">
+      <c r="B74" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C74" s="115" t="inlineStr">
+        <is>
+          <t>HCA</t>
+        </is>
+      </c>
+      <c r="D74" s="116" t="inlineStr">
+        <is>
+          <t>HCA Healthcare Inc.</t>
+        </is>
+      </c>
+      <c r="E74" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F74" s="117" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G74" s="118" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H74" s="119" t="n">
+        <v>94806.22</v>
+      </c>
+      <c r="I74" s="120" t="inlineStr">
+        <is>
+          <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="52" customHeight="1">
+      <c r="B75" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C73" s="121" t="inlineStr">
+      <c r="C75" s="121" t="inlineStr">
         <is>
           <t>MRNA</t>
         </is>
       </c>
-      <c r="D73" s="122" t="inlineStr">
+      <c r="D75" s="122" t="inlineStr">
         <is>
           <t>Moderna Inc.</t>
         </is>
       </c>
-      <c r="E73" s="123" t="inlineStr">
+      <c r="E75" s="123" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F73" s="123" t="inlineStr">
+      <c r="F75" s="123" t="inlineStr">
         <is>
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="G73" s="118" t="n">
-        <v>3.227</v>
-      </c>
-      <c r="H73" s="124" t="n">
+      <c r="G75" s="118" t="n">
+        <v>3.315</v>
+      </c>
+      <c r="H75" s="124" t="n">
         <v>74971.71000000001</v>
       </c>
-      <c r="I73" s="125" t="inlineStr">
+      <c r="I75" s="125" t="inlineStr">
         <is>
           <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="70" customHeight="1">
-      <c r="B74" s="129" t="inlineStr">
+    <row r="76" ht="70" customHeight="1">
+      <c r="B76" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C74" s="141" t="inlineStr">
+      <c r="C76" s="115" t="inlineStr">
         <is>
           <t>VEEV</t>
         </is>
       </c>
-      <c r="D74" s="142" t="inlineStr">
+      <c r="D76" s="116" t="inlineStr">
         <is>
           <t>Veeva Systems Inc.</t>
         </is>
       </c>
-      <c r="E74" s="143" t="inlineStr">
+      <c r="E76" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F74" s="143" t="inlineStr">
+      <c r="F76" s="117" t="inlineStr">
         <is>
           <t>Health Care Technology</t>
         </is>
       </c>
-      <c r="G74" s="133" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="H74" s="144" t="n">
+      <c r="G76" s="118" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="H76" s="119" t="n">
         <v>45576.53</v>
       </c>
-      <c r="I74" s="145" t="inlineStr">
+      <c r="I76" s="120" t="inlineStr">
         <is>
           <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="8" customHeight="1">
-      <c r="B75" s="136" t="n"/>
-      <c r="C75" s="136" t="n"/>
-      <c r="D75" s="136" t="n"/>
-      <c r="E75" s="136" t="n"/>
-      <c r="F75" s="136" t="n"/>
-      <c r="G75" s="136" t="n"/>
-      <c r="H75" s="136" t="n"/>
-      <c r="I75" s="136" t="n"/>
-    </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="B76" s="137" t="inlineStr">
+    <row r="77" ht="52" customHeight="1">
+      <c r="B77" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C77" s="130" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D77" s="131" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="E77" s="132" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F77" s="132" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G77" s="133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H77" s="134" t="n">
+        <v>21029.38</v>
+      </c>
+      <c r="I77" s="135" t="inlineStr">
+        <is>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1">
+      <c r="B78" s="136" t="n"/>
+      <c r="C78" s="136" t="n"/>
+      <c r="D78" s="136" t="n"/>
+      <c r="E78" s="136" t="n"/>
+      <c r="F78" s="136" t="n"/>
+      <c r="G78" s="136" t="n"/>
+      <c r="H78" s="136" t="n"/>
+      <c r="I78" s="136" t="n"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="B79" s="137" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C76" s="138" t="n"/>
-      <c r="D76" s="138" t="n"/>
-      <c r="E76" s="138" t="n"/>
-      <c r="F76" s="138" t="n"/>
-      <c r="G76" s="138" t="n"/>
-      <c r="H76" s="138" t="n"/>
-      <c r="I76" s="138" t="n"/>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="B77" s="139" t="inlineStr">
+      <c r="C79" s="138" t="n"/>
+      <c r="D79" s="138" t="n"/>
+      <c r="E79" s="138" t="n"/>
+      <c r="F79" s="138" t="n"/>
+      <c r="G79" s="138" t="n"/>
+      <c r="H79" s="138" t="n"/>
+      <c r="I79" s="138" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="B80" s="139" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C77" s="140" t="n"/>
-      <c r="D77" s="140" t="n"/>
-      <c r="E77" s="140" t="n"/>
-      <c r="F77" s="140" t="n"/>
-      <c r="G77" s="140" t="n"/>
-      <c r="H77" s="140" t="n"/>
-      <c r="I77" s="140" t="n"/>
+      <c r="C80" s="140" t="n"/>
+      <c r="D80" s="140" t="n"/>
+      <c r="E80" s="140" t="n"/>
+      <c r="F80" s="140" t="n"/>
+      <c r="G80" s="140" t="n"/>
+      <c r="H80" s="140" t="n"/>
+      <c r="I80" s="140" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B79:I79"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G74">
+  <conditionalFormatting sqref="G8:G77">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$79</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -545,6 +545,15 @@
     </border>
     <border/>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1DCE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFC67A29"/>
       </left>
@@ -558,24 +567,11 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color theme="2"/>
-      </left>
-      <right style="medium">
-        <color theme="2"/>
-      </right>
-      <top style="medium">
-        <color theme="2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -932,15 +928,51 @@
     <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2064,7 +2096,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46321.71272094517</v>
+        <v>46322.672666175</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2126,7 +2158,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46321.71272094517</v>
+        <v>46322.672666175</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2259,7 +2291,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.017</v>
+        <v>0.991</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>284.17</v>
@@ -2272,7 +2304,7 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2281,39 +2313,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>CFW</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Calfrac Well Services Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.487</v>
+        <v>0.479</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>1836.63</v>
+        <v>478.75</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="88" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2322,39 +2354,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Constellation Software Inc.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.367</v>
+        <v>0.47</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>43632.38</v>
+        <v>1836.63</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2363,33 +2395,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>Constellation Software Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.361</v>
+        <v>0.339</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>43014.26</v>
+        <v>43632.38</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2404,39 +2436,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>CFW</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.317</v>
+        <v>0.203</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>478.75</v>
+        <v>69914.25999999999</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2445,39 +2477,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>WCN</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Open Text Corporation</t>
+          <t>Waste Connections Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.29</v>
+        <v>0.155</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>5405.28</v>
+        <v>39435.42</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
+          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2486,39 +2518,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>ENGH</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Enghouse Systems Limited</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.219</v>
+        <v>0.154</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>69914.25999999999</v>
+        <v>634.6900000000001</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="106" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2527,33 +2559,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>WCN</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Waste Connections Inc.</t>
+          <t>Loblaw Companies Limited</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.172</v>
+        <v>0.096</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>39435.42</v>
+        <v>50539.87</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
+          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2568,39 +2600,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>XTC</t>
+          <t>VET</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited</t>
+          <t>Vermilion Energy Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Automobile Components</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.171</v>
+        <v>0.062</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>220.37</v>
+        <v>1789.16</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Exco Technologies Limited together with its subsidiaries designs develops manufactures and sells dies molds components and assemblies and consumable equipment for the die-cast extrusion and automotive industries</t>
+          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2609,80 +2641,80 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>ENGH</t>
+          <t>GFR</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited</t>
+          <t>Greenfire Resources Ltd.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.157</v>
+        <v>0.043</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>634.6900000000001</v>
+        <v>1476.14</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
+          <t>Greenfire Resources Ltd together with its subsidiaries engages in the exploration development and operation of oil and gas properties in the Athabasca oil sands region of Alberta Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="106" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.105</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>50539.87</v>
+        <v>884.7</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -2691,39 +2723,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.696</v>
+        <v>0.625</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>884.7</v>
+        <v>600.1</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="127" t="inlineStr">
         <is>
@@ -2732,33 +2764,33 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.668</v>
+        <v>0.411</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>600.1</v>
+        <v>925.72</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
@@ -2773,33 +2805,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Marine Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.474</v>
+        <v>0.339</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>743.0700000000001</v>
+        <v>804.05</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Algoma Central Corporation owns and operates a fleet of dry and liquid bulk carriers activities in Canada</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2814,39 +2846,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.4</v>
+        <v>0.299</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>925.72</v>
+        <v>43014.26</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -2855,12 +2887,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -2874,14 +2906,14 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.348</v>
+        <v>0.289</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>804.05</v>
+        <v>15597.29</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2896,12 +2928,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -2915,14 +2947,14 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.314</v>
+        <v>0.282</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>15597.29</v>
+        <v>373.79</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2937,39 +2969,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Open Text Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.275</v>
+        <v>0.271</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>373.79</v>
+        <v>5405.28</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2978,39 +3010,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.249</v>
+        <v>0.254</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>336.54</v>
+        <v>389.1</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="106" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3019,39 +3051,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.248</v>
+        <v>0.198</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>389.1</v>
+        <v>99672.56</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3060,12 +3092,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3079,20 +3111,20 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.234</v>
+        <v>0.196</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>80962.39</v>
+        <v>336.54</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="106" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -3101,12 +3133,12 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
@@ -3120,14 +3152,14 @@
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>99672.56</v>
+        <v>80962.39</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
@@ -3161,7 +3193,7 @@
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.214</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="119" t="n">
         <v>35208.26</v>
@@ -3174,7 +3206,7 @@
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="88" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3183,12 +3215,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -3202,20 +3234,20 @@
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.198</v>
+        <v>0.169</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>3837.96</v>
+        <v>1545.36</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="88" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -3224,12 +3256,12 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
@@ -3243,14 +3275,14 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.194</v>
+        <v>0.163</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>1545.36</v>
+        <v>4428.98</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -3265,12 +3297,12 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -3284,20 +3316,20 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.176</v>
+        <v>0.156</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>4428.98</v>
+        <v>3837.96</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="52" customHeight="1">
+    <row r="34" ht="106" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="127" t="inlineStr">
         <is>
@@ -3306,39 +3338,39 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.171</v>
+        <v>0.131</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>4283.74</v>
+        <v>398.33</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>E-L Financial Corporation Limited operates as an investment and insurance holding company in Canada</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="127" t="inlineStr">
         <is>
@@ -3347,33 +3379,33 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>DTOL</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>D2L Inc.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Diversified Consumer Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.16</v>
+        <v>0.127</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>382.43</v>
+        <v>2245.27</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>D2L Inc provides cloud-based learning software for higher education institutions kindergarten to grade 12 schools and districts and private sector enterprises in Canada the United States and internationally</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
@@ -3381,81 +3413,81 @@
     </row>
     <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B36" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>GUD</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Knight Therapeutics Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.148</v>
+        <v>0.532</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>2245.27</v>
+        <v>732.01</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="106" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B37" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.101</v>
+        <v>0.391</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>398.33</v>
+        <v>3333.46</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
@@ -3470,33 +3502,33 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>GUD</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.332</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>732.01</v>
+        <v>6794.59</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
@@ -3504,171 +3536,115 @@
     </row>
     <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="128" t="inlineStr">
+      <c r="B39" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C39" s="121" t="inlineStr">
-        <is>
-          <t>KXS</t>
-        </is>
-      </c>
-      <c r="D39" s="122" t="inlineStr">
-        <is>
-          <t>Kinaxis Inc.</t>
-        </is>
-      </c>
-      <c r="E39" s="123" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F39" s="123" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G39" s="118" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="H39" s="124" t="n">
-        <v>3333.46</v>
-      </c>
-      <c r="I39" s="125" t="inlineStr">
-        <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+      <c r="C39" s="130" t="inlineStr">
+        <is>
+          <t>NWC</t>
+        </is>
+      </c>
+      <c r="D39" s="131" t="inlineStr">
+        <is>
+          <t>The North West Company Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="132" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F39" s="132" t="inlineStr">
+        <is>
+          <t>Consumer Staples Distribution and Retail</t>
+        </is>
+      </c>
+      <c r="G39" s="133" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="H39" s="134" t="n">
+        <v>1823.99</v>
+      </c>
+      <c r="I39" s="135" t="inlineStr">
+        <is>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="70" customHeight="1">
+    <row r="40" ht="8" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C40" s="115" t="inlineStr">
-        <is>
-          <t>DSG</t>
-        </is>
-      </c>
-      <c r="D40" s="116" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc.</t>
-        </is>
-      </c>
-      <c r="E40" s="117" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F40" s="117" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G40" s="118" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="H40" s="119" t="n">
-        <v>6794.59</v>
-      </c>
-      <c r="I40" s="120" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
-        </is>
-      </c>
+      <c r="B40" s="136" t="n"/>
+      <c r="C40" s="137" t="n"/>
+      <c r="D40" s="138" t="n"/>
+      <c r="E40" s="139" t="n"/>
+      <c r="F40" s="139" t="n"/>
+      <c r="G40" s="140" t="n"/>
+      <c r="H40" s="141" t="n"/>
+      <c r="I40" s="142" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="70" customHeight="1" thickBot="1">
+    <row r="41" ht="34" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C41" s="130" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D41" s="131" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E41" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F41" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G41" s="133" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="H41" s="134" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I41" s="135" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
-        </is>
-      </c>
+      <c r="B41" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C41" s="144" t="n"/>
+      <c r="D41" s="144" t="n"/>
+      <c r="E41" s="144" t="n"/>
+      <c r="F41" s="144" t="n"/>
+      <c r="G41" s="144" t="n"/>
+      <c r="H41" s="144" t="n"/>
+      <c r="I41" s="144" t="n"/>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
-    <row r="42" ht="8" customHeight="1">
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="136" t="n"/>
-      <c r="C42" s="136" t="n"/>
-      <c r="D42" s="136" t="n"/>
-      <c r="E42" s="136" t="n"/>
-      <c r="F42" s="136" t="n"/>
-      <c r="G42" s="136" t="n"/>
-      <c r="H42" s="136" t="n"/>
-      <c r="I42" s="136" t="n"/>
+      <c r="B42" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C42" s="146" t="n"/>
+      <c r="D42" s="146" t="n"/>
+      <c r="E42" s="146" t="n"/>
+      <c r="F42" s="146" t="n"/>
+      <c r="G42" s="146" t="n"/>
+      <c r="H42" s="146" t="n"/>
+      <c r="I42" s="146" t="n"/>
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
-    <row r="43" ht="34" customHeight="1" thickBot="1">
+    <row r="43" ht="15.6" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="137" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C43" s="138" t="n"/>
-      <c r="D43" s="138" t="n"/>
-      <c r="E43" s="138" t="n"/>
-      <c r="F43" s="138" t="n"/>
-      <c r="G43" s="138" t="n"/>
-      <c r="H43" s="138" t="n"/>
-      <c r="I43" s="138" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="43" t="n"/>
+      <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="28" customHeight="1">
+    <row r="44" ht="12" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="139" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C44" s="140" t="n"/>
-      <c r="D44" s="140" t="n"/>
-      <c r="E44" s="140" t="n"/>
-      <c r="F44" s="140" t="n"/>
-      <c r="G44" s="140" t="n"/>
-      <c r="H44" s="140" t="n"/>
-      <c r="I44" s="140" t="n"/>
+      <c r="B44" s="58" t="n"/>
+      <c r="C44" s="59" t="n"/>
+      <c r="D44" s="59" t="n"/>
+      <c r="E44" s="59" t="n"/>
+      <c r="F44" s="59" t="n"/>
+      <c r="G44" s="59" t="n"/>
+      <c r="H44" s="59" t="n"/>
+      <c r="I44" s="60" t="n"/>
       <c r="J44" s="60" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
@@ -3740,12 +3716,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B44:I44"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B41:I41"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B43:I43"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G41">
+  <conditionalFormatting sqref="G8:G39">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4686,7 +4662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4726,7 +4702,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46321.71272094517</v>
+        <v>46322.672666175</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4831,7 +4807,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="88" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -4840,12 +4816,12 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc.</t>
+          <t>Revvity Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
@@ -4859,20 +4835,20 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.167</v>
+        <v>0.862</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>14054.04</v>
+        <v>16701.36</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
+          <t>Revvity Inc provides health sciences solutions technologies and services</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -4881,12 +4857,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Revvity Inc.</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -4900,20 +4876,20 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.948</v>
+        <v>0.732</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>16701.36</v>
+        <v>42172.99</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Revvity Inc provides health sciences solutions technologies and services</t>
+          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4922,12 +4898,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Workday Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -4937,24 +4913,24 @@
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.802</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>17950.14</v>
+        <v>45398.38</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4963,33 +4939,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.761</v>
+        <v>0.653</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>42172.99</v>
+        <v>17904.45</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -5004,39 +4980,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>ServiceNow Inc.</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.753</v>
+        <v>0.541</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>142623.33</v>
+        <v>47137.94</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -5045,39 +5021,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.703</v>
+        <v>0.497</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>17904.45</v>
+        <v>42201.2</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5086,39 +5062,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Workday Inc.</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.694</v>
+        <v>0.378</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>45398.38</v>
+        <v>9701.92</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
+          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -5127,33 +5103,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.582</v>
+        <v>0.33</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>47137.94</v>
+        <v>12471.61</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>The J</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -5168,12 +5144,12 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
@@ -5183,24 +5159,24 @@
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.309</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>42201.2</v>
+        <v>224207.66</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5209,33 +5185,33 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.507</v>
+        <v>0.307</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>1054668.83</v>
+        <v>12320.13</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -5250,12 +5226,12 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -5265,24 +5241,24 @@
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.398</v>
+        <v>0.267</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>9701.92</v>
+        <v>61019.13</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="106" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5291,39 +5267,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Aerospace and Defense</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.36</v>
+        <v>0.228</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>12471.61</v>
+        <v>116283.92</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>The J</t>
+          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -5332,33 +5308,33 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Roper Technologies Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.32</v>
+        <v>0.227</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>224207.66</v>
+        <v>35615.09</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
@@ -5373,33 +5349,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.306</v>
+        <v>0.211</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>12320.13</v>
+        <v>12451.88</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
@@ -5414,33 +5390,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.282</v>
+        <v>0.204</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>61019.13</v>
+        <v>41984.2</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5455,12 +5431,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -5470,24 +5446,24 @@
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.274</v>
+        <v>0.186</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>12451.88</v>
+        <v>16850.47</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5496,33 +5472,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.264</v>
+        <v>0.181</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>12857.61</v>
+        <v>88425.8</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>Emerson Electric Co</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5537,39 +5513,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Broadridge Financial Solutions Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.261</v>
+        <v>0.177</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>32165.5</v>
+        <v>17905.95</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
+          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="106" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="126" t="inlineStr">
         <is>
@@ -5578,39 +5554,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Aerospace and Defense</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.249</v>
+        <v>0.17</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>116283.92</v>
+        <v>60523.16</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="126" t="inlineStr">
         <is>
@@ -5619,33 +5595,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc.</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.237</v>
+        <v>0.168</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>35615.09</v>
+        <v>23268.86</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5660,39 +5636,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.233</v>
+        <v>0.151</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>60523.16</v>
+        <v>57901.58</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5701,33 +5677,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.223</v>
+        <v>0.146</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>16850.47</v>
+        <v>15869.76</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
+          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5742,39 +5718,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Nasdaq Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.216</v>
+        <v>0.145</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>41984.2</v>
+        <v>51024.57</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5783,39 +5759,39 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Elevance Health Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.206</v>
+        <v>0.135</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>57901.58</v>
+        <v>87408.73</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="88" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="126" t="inlineStr">
         <is>
@@ -5824,39 +5800,39 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Avery Dennison Corporation</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Containers and Packaging</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.166</v>
+        <v>0.121</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>15869.76</v>
+        <v>12719.07</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
+          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="52" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="126" t="inlineStr">
         <is>
@@ -5865,33 +5841,33 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Tyler Technologies Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.159</v>
+        <v>0.112</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>23268.86</v>
+        <v>13525.55</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -5906,12 +5882,12 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Elevance Health Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
@@ -5925,14 +5901,14 @@
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.154</v>
+        <v>0.051</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>87408.73</v>
+        <v>73585.95</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
+          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -5947,115 +5923,115 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Nasdaq Inc.</t>
+          <t>Occidental Petroleum Corporation</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.145</v>
+        <v>0.05</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>51024.57</v>
+        <v>58304.85</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row r="36" ht="52" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B36" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc.</t>
+          <t>Moderna Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.143</v>
+        <v>3.278</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>17905.95</v>
+        <v>74971.71000000001</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
+          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="70" customHeight="1">
+    <row r="37" ht="88" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation</t>
+          <t>Charles River Laboratories International Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Containers and Packaging</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.135</v>
+        <v>1.139</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>12719.07</v>
+        <v>14054.04</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
+          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
@@ -6063,19 +6039,19 @@
     </row>
     <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc.</t>
+          <t>ServiceNow Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
@@ -6089,55 +6065,55 @@
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>13525.55</v>
+        <v>142623.33</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="52" customHeight="1">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.056</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>73585.95</v>
+        <v>17950.14</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
@@ -6171,7 +6147,7 @@
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.531</v>
+        <v>0.513</v>
       </c>
       <c r="H40" s="119" t="n">
         <v>11772.74</v>
@@ -6212,7 +6188,7 @@
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.448</v>
+        <v>0.417</v>
       </c>
       <c r="H41" s="124" t="n">
         <v>33875.2</v>
@@ -6225,7 +6201,7 @@
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="70" customHeight="1" thickBot="1">
+    <row r="42" ht="52" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
       <c r="B42" s="127" t="inlineStr">
         <is>
@@ -6234,39 +6210,39 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.421</v>
+        <v>0.401</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>480788.44</v>
+        <v>104249.82</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="52" customHeight="1">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6275,33 +6251,33 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Williams-Sonoma Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.416</v>
+        <v>0.396</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>104249.82</v>
+        <v>28342.5</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
@@ -6316,33 +6292,33 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.386</v>
+        <v>0.378</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>116683.09</v>
+        <v>1054668.83</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6357,39 +6333,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.382</v>
+        <v>0.349</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>28342.5</v>
+        <v>116683.09</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="88" customHeight="1">
+    <row r="46" ht="70" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6398,39 +6374,39 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.376</v>
+        <v>0.345</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>21455.05</v>
+        <v>24969.64</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="106" customHeight="1" thickBot="1">
+    <row r="47" ht="88" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6439,12 +6415,12 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
@@ -6454,18 +6430,18 @@
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.359</v>
+        <v>0.335</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>48910.32</v>
+        <v>26039.81</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6480,12 +6456,12 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
@@ -6495,24 +6471,24 @@
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.345</v>
+        <v>0.329</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>30639.57</v>
+        <v>33430.82</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="1">
+    <row r="49" ht="88" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6521,39 +6497,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>24969.64</v>
+        <v>21455.05</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="88" customHeight="1">
+    <row r="50" ht="106" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6561,12 +6537,12 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
@@ -6576,18 +6552,18 @@
       </c>
       <c r="F50" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G50" s="118" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="H50" s="119" t="n">
-        <v>26039.81</v>
+        <v>48910.32</v>
       </c>
       <c r="I50" s="120" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
     </row>
@@ -6599,12 +6575,12 @@
       </c>
       <c r="C51" s="121" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D51" s="122" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E51" s="123" t="inlineStr">
@@ -6618,14 +6594,14 @@
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.303</v>
+        <v>0.317</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>151241.83</v>
+        <v>30639.57</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
     </row>
@@ -6637,33 +6613,33 @@
       </c>
       <c r="C52" s="115" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D52" s="116" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E52" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F52" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G52" s="118" t="n">
-        <v>0.296</v>
+        <v>0.303</v>
       </c>
       <c r="H52" s="119" t="n">
-        <v>15537.74</v>
+        <v>151241.83</v>
       </c>
       <c r="I52" s="120" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6651,12 @@
       </c>
       <c r="C53" s="121" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D53" s="122" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E53" s="123" t="inlineStr">
@@ -6690,18 +6666,18 @@
       </c>
       <c r="F53" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G53" s="118" t="n">
-        <v>0.284</v>
+        <v>0.297</v>
       </c>
       <c r="H53" s="124" t="n">
-        <v>33430.82</v>
+        <v>32165.5</v>
       </c>
       <c r="I53" s="125" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
         </is>
       </c>
     </row>
@@ -6713,71 +6689,71 @@
       </c>
       <c r="C54" s="115" t="inlineStr">
         <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D54" s="116" t="inlineStr">
+        <is>
+          <t>APA Corporation</t>
+        </is>
+      </c>
+      <c r="E54" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F54" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G54" s="118" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="H54" s="119" t="n">
+        <v>15537.74</v>
+      </c>
+      <c r="I54" s="120" t="inlineStr">
+        <is>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="70" customHeight="1">
+      <c r="B55" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C55" s="121" t="inlineStr">
+        <is>
           <t>CTSH</t>
         </is>
       </c>
-      <c r="D54" s="116" t="inlineStr">
+      <c r="D55" s="122" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
-      <c r="E54" s="117" t="inlineStr">
+      <c r="E55" s="123" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F54" s="117" t="inlineStr">
+      <c r="F55" s="123" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="G54" s="118" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H54" s="119" t="n">
+      <c r="G55" s="118" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H55" s="124" t="n">
         <v>25579.38</v>
       </c>
-      <c r="I54" s="120" t="inlineStr">
+      <c r="I55" s="125" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="52" customHeight="1">
-      <c r="B55" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C55" s="121" t="inlineStr">
-        <is>
-          <t>CAH</t>
-        </is>
-      </c>
-      <c r="D55" s="122" t="inlineStr">
-        <is>
-          <t>Cardinal Health Inc.</t>
-        </is>
-      </c>
-      <c r="E55" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F55" s="123" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G55" s="118" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="H55" s="124" t="n">
-        <v>54537.32</v>
-      </c>
-      <c r="I55" s="125" t="inlineStr">
-        <is>
-          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -6789,33 +6765,33 @@
       </c>
       <c r="C56" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D56" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E56" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F56" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G56" s="118" t="n">
-        <v>0.244</v>
+        <v>0.256</v>
       </c>
       <c r="H56" s="119" t="n">
-        <v>183538.16</v>
+        <v>12857.61</v>
       </c>
       <c r="I56" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
     </row>
@@ -6827,147 +6803,147 @@
       </c>
       <c r="C57" s="121" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D57" s="122" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F57" s="123" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G57" s="118" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="H57" s="124" t="n">
+        <v>682021.24</v>
+      </c>
+      <c r="I57" s="125" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="70" customHeight="1">
+      <c r="B58" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C58" s="115" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D58" s="116" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="E58" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F58" s="117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G58" s="118" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H58" s="119" t="n">
+        <v>498865.76</v>
+      </c>
+      <c r="I58" s="120" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="70" customHeight="1">
+      <c r="B59" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C59" s="121" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D59" s="122" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc.</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F59" s="123" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G59" s="118" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="H59" s="124" t="n">
+        <v>183538.16</v>
+      </c>
+      <c r="I59" s="125" t="inlineStr">
+        <is>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
+      <c r="B60" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C60" s="115" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="D57" s="122" t="inlineStr">
+      <c r="D60" s="116" t="inlineStr">
         <is>
           <t>Chevron Corporation</t>
         </is>
       </c>
-      <c r="E57" s="123" t="inlineStr">
+      <c r="E60" s="117" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F57" s="123" t="inlineStr">
+      <c r="F60" s="117" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G57" s="118" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="H57" s="124" t="n">
+      <c r="G60" s="118" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="H60" s="119" t="n">
         <v>404759.18</v>
       </c>
-      <c r="I57" s="125" t="inlineStr">
+      <c r="I60" s="120" t="inlineStr">
         <is>
           <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="52" customHeight="1">
-      <c r="B58" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C58" s="115" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D58" s="116" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E58" s="117" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F58" s="117" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G58" s="118" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="H58" s="119" t="n">
-        <v>682021.24</v>
-      </c>
-      <c r="I58" s="120" t="inlineStr">
-        <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="52" customHeight="1">
-      <c r="B59" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C59" s="121" t="inlineStr">
-        <is>
-          <t>MCK</t>
-        </is>
-      </c>
-      <c r="D59" s="122" t="inlineStr">
-        <is>
-          <t>McKesson Corporation</t>
-        </is>
-      </c>
-      <c r="E59" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F59" s="123" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G59" s="118" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="H59" s="124" t="n">
-        <v>108638.32</v>
-      </c>
-      <c r="I59" s="125" t="inlineStr">
-        <is>
-          <t>McKesson Corporation provides healthcare services in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="70" customHeight="1">
-      <c r="B60" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C60" s="115" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="D60" s="116" t="inlineStr">
-        <is>
-          <t>Medtronic plc</t>
-        </is>
-      </c>
-      <c r="E60" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F60" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G60" s="118" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="H60" s="119" t="n">
-        <v>111058.59</v>
-      </c>
-      <c r="I60" s="120" t="inlineStr">
-        <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
     </row>
@@ -6979,12 +6955,12 @@
       </c>
       <c r="C61" s="121" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D61" s="122" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E61" s="123" t="inlineStr">
@@ -6998,14 +6974,14 @@
         </is>
       </c>
       <c r="G61" s="118" t="n">
-        <v>0.206</v>
+        <v>0.198</v>
       </c>
       <c r="H61" s="124" t="n">
-        <v>677009.86</v>
+        <v>156513.85</v>
       </c>
       <c r="I61" s="125" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
     </row>
@@ -7017,12 +6993,12 @@
       </c>
       <c r="C62" s="115" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D62" s="116" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E62" s="117" t="inlineStr">
@@ -7036,14 +7012,14 @@
         </is>
       </c>
       <c r="G62" s="118" t="n">
-        <v>0.199</v>
+        <v>0.19</v>
       </c>
       <c r="H62" s="119" t="n">
-        <v>156513.85</v>
+        <v>677009.86</v>
       </c>
       <c r="I62" s="120" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
     </row>
@@ -7055,71 +7031,71 @@
       </c>
       <c r="C63" s="121" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D63" s="122" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E63" s="123" t="inlineStr">
         <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F63" s="123" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G63" s="118" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="H63" s="124" t="n">
+        <v>371563.85</v>
+      </c>
+      <c r="I63" s="125" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="70" customHeight="1">
+      <c r="B64" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C64" s="115" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="D64" s="116" t="inlineStr">
+        <is>
+          <t>Medtronic plc</t>
+        </is>
+      </c>
+      <c r="E64" s="117" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F63" s="123" t="inlineStr">
+      <c r="F64" s="117" t="inlineStr">
         <is>
           <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
-      <c r="G63" s="118" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H63" s="124" t="n">
-        <v>31594.32</v>
-      </c>
-      <c r="I63" s="125" t="inlineStr">
-        <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="88" customHeight="1">
-      <c r="B64" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C64" s="115" t="inlineStr">
-        <is>
-          <t>EOG</t>
-        </is>
-      </c>
-      <c r="D64" s="116" t="inlineStr">
-        <is>
-          <t>EOG Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E64" s="117" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F64" s="117" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
       <c r="G64" s="118" t="n">
-        <v>0.191</v>
+        <v>0.179</v>
       </c>
       <c r="H64" s="119" t="n">
-        <v>75763.52</v>
+        <v>111058.59</v>
       </c>
       <c r="I64" s="120" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
     </row>
@@ -7131,37 +7107,37 @@
       </c>
       <c r="C65" s="121" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D65" s="122" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E65" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F65" s="123" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G65" s="118" t="n">
-        <v>0.189</v>
+        <v>0.179</v>
       </c>
       <c r="H65" s="124" t="n">
-        <v>371563.85</v>
+        <v>31594.32</v>
       </c>
       <c r="I65" s="125" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="70" customHeight="1">
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="88" customHeight="1">
       <c r="B66" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7169,109 +7145,109 @@
       </c>
       <c r="C66" s="115" t="inlineStr">
         <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D66" s="116" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E66" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F66" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G66" s="118" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H66" s="119" t="n">
+        <v>75763.52</v>
+      </c>
+      <c r="I66" s="120" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="B67" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C67" s="121" t="inlineStr">
+        <is>
+          <t>ULTA</t>
+        </is>
+      </c>
+      <c r="D67" s="122" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc.</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F67" s="123" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G67" s="118" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H67" s="124" t="n">
+        <v>23628.33</v>
+      </c>
+      <c r="I67" s="125" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="70" customHeight="1">
+      <c r="B68" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C68" s="115" t="inlineStr">
+        <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="D66" s="116" t="inlineStr">
+      <c r="D68" s="116" t="inlineStr">
         <is>
           <t>Pfizer Inc.</t>
         </is>
       </c>
-      <c r="E66" s="117" t="inlineStr">
+      <c r="E68" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F66" s="117" t="inlineStr">
+      <c r="F68" s="117" t="inlineStr">
         <is>
           <t>Pharmaceuticals</t>
         </is>
       </c>
-      <c r="G66" s="118" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="H66" s="119" t="n">
+      <c r="G68" s="118" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="H68" s="119" t="n">
         <v>159089.29</v>
       </c>
-      <c r="I66" s="120" t="inlineStr">
+      <c r="I68" s="120" t="inlineStr">
         <is>
           <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="70" customHeight="1">
-      <c r="B67" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C67" s="121" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D67" s="122" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated</t>
-        </is>
-      </c>
-      <c r="E67" s="123" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F67" s="123" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G67" s="118" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="H67" s="124" t="n">
-        <v>498865.76</v>
-      </c>
-      <c r="I67" s="125" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="52" customHeight="1">
-      <c r="B68" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C68" s="115" t="inlineStr">
-        <is>
-          <t>ULTA</t>
-        </is>
-      </c>
-      <c r="D68" s="116" t="inlineStr">
-        <is>
-          <t>Ulta Beauty Inc.</t>
-        </is>
-      </c>
-      <c r="E68" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F68" s="117" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G68" s="118" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="H68" s="119" t="n">
-        <v>23628.33</v>
-      </c>
-      <c r="I68" s="120" t="inlineStr">
-        <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7278,7 @@
         </is>
       </c>
       <c r="G69" s="118" t="n">
-        <v>0.165</v>
+        <v>0.132</v>
       </c>
       <c r="H69" s="124" t="n">
         <v>66372.58</v>
@@ -7340,7 +7316,7 @@
         </is>
       </c>
       <c r="G70" s="118" t="n">
-        <v>0.136</v>
+        <v>0.112</v>
       </c>
       <c r="H70" s="119" t="n">
         <v>27315.89</v>
@@ -7351,7 +7327,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="70" customHeight="1">
+    <row r="71" ht="52" customHeight="1">
       <c r="B71" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7359,33 +7335,33 @@
       </c>
       <c r="C71" s="121" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D71" s="122" t="inlineStr">
         <is>
-          <t>Universal Health Services Inc.</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E71" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F71" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="G71" s="118" t="n">
-        <v>0.109</v>
+        <v>0.094</v>
       </c>
       <c r="H71" s="124" t="n">
-        <v>10428.64</v>
+        <v>345602.03</v>
       </c>
       <c r="I71" s="125" t="inlineStr">
         <is>
-          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
         </is>
       </c>
     </row>
@@ -7397,12 +7373,12 @@
       </c>
       <c r="C72" s="115" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D72" s="116" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E72" s="117" t="inlineStr">
@@ -7416,18 +7392,18 @@
         </is>
       </c>
       <c r="G72" s="118" t="n">
-        <v>0.106</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H72" s="119" t="n">
-        <v>345602.03</v>
+        <v>22965.61</v>
       </c>
       <c r="I72" s="120" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="52" customHeight="1">
+          <t>Church &amp; Dwight Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="70" customHeight="1">
       <c r="B73" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7435,33 +7411,33 @@
       </c>
       <c r="C73" s="121" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="D73" s="122" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
+          <t>Universal Health Services Inc.</t>
         </is>
       </c>
       <c r="E73" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F73" s="123" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G73" s="118" t="n">
-        <v>0.099</v>
+        <v>0.048</v>
       </c>
       <c r="H73" s="124" t="n">
-        <v>22965.61</v>
+        <v>10428.64</v>
       </c>
       <c r="I73" s="125" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co</t>
+          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7468,7 @@
         </is>
       </c>
       <c r="G74" s="118" t="n">
-        <v>0.073</v>
+        <v>0.022</v>
       </c>
       <c r="H74" s="119" t="n">
         <v>94806.22</v>
@@ -7503,7 +7479,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="52" customHeight="1">
+    <row r="75" ht="70" customHeight="1">
       <c r="B75" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
@@ -7511,12 +7487,12 @@
       </c>
       <c r="C75" s="121" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D75" s="122" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E75" s="123" t="inlineStr">
@@ -7526,144 +7502,106 @@
       </c>
       <c r="F75" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G75" s="118" t="n">
-        <v>3.315</v>
+        <v>1.019</v>
       </c>
       <c r="H75" s="124" t="n">
-        <v>74971.71000000001</v>
+        <v>45576.53</v>
       </c>
       <c r="I75" s="125" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="70" customHeight="1">
-      <c r="B76" s="128" t="inlineStr">
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="52" customHeight="1">
+      <c r="B76" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C76" s="115" t="inlineStr">
-        <is>
-          <t>VEEV</t>
-        </is>
-      </c>
-      <c r="D76" s="116" t="inlineStr">
-        <is>
-          <t>Veeva Systems Inc.</t>
-        </is>
-      </c>
-      <c r="E76" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F76" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Technology</t>
-        </is>
-      </c>
-      <c r="G76" s="118" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="H76" s="119" t="n">
-        <v>45576.53</v>
-      </c>
-      <c r="I76" s="120" t="inlineStr">
-        <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="52" customHeight="1">
-      <c r="B77" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C77" s="130" t="inlineStr">
+      <c r="C76" s="147" t="inlineStr">
         <is>
           <t>PTC</t>
         </is>
       </c>
-      <c r="D77" s="131" t="inlineStr">
+      <c r="D76" s="148" t="inlineStr">
         <is>
           <t>PTC Inc.</t>
         </is>
       </c>
-      <c r="E77" s="132" t="inlineStr">
+      <c r="E76" s="149" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F77" s="132" t="inlineStr">
+      <c r="F76" s="149" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G77" s="133" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H77" s="134" t="n">
+      <c r="G76" s="133" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="H76" s="150" t="n">
         <v>21029.38</v>
       </c>
-      <c r="I77" s="135" t="inlineStr">
+      <c r="I76" s="151" t="inlineStr">
         <is>
           <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="8" customHeight="1">
-      <c r="B78" s="136" t="n"/>
-      <c r="C78" s="136" t="n"/>
-      <c r="D78" s="136" t="n"/>
-      <c r="E78" s="136" t="n"/>
-      <c r="F78" s="136" t="n"/>
-      <c r="G78" s="136" t="n"/>
-      <c r="H78" s="136" t="n"/>
-      <c r="I78" s="136" t="n"/>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="B79" s="137" t="inlineStr">
+    <row r="77" ht="8" customHeight="1">
+      <c r="B77" s="152" t="n"/>
+      <c r="C77" s="152" t="n"/>
+      <c r="D77" s="152" t="n"/>
+      <c r="E77" s="152" t="n"/>
+      <c r="F77" s="152" t="n"/>
+      <c r="G77" s="152" t="n"/>
+      <c r="H77" s="152" t="n"/>
+      <c r="I77" s="152" t="n"/>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="B78" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C79" s="138" t="n"/>
-      <c r="D79" s="138" t="n"/>
-      <c r="E79" s="138" t="n"/>
-      <c r="F79" s="138" t="n"/>
-      <c r="G79" s="138" t="n"/>
-      <c r="H79" s="138" t="n"/>
-      <c r="I79" s="138" t="n"/>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="B80" s="139" t="inlineStr">
+      <c r="C78" s="144" t="n"/>
+      <c r="D78" s="144" t="n"/>
+      <c r="E78" s="144" t="n"/>
+      <c r="F78" s="144" t="n"/>
+      <c r="G78" s="144" t="n"/>
+      <c r="H78" s="144" t="n"/>
+      <c r="I78" s="144" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="B79" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C80" s="140" t="n"/>
-      <c r="D80" s="140" t="n"/>
-      <c r="E80" s="140" t="n"/>
-      <c r="F80" s="140" t="n"/>
-      <c r="G80" s="140" t="n"/>
-      <c r="H80" s="140" t="n"/>
-      <c r="I80" s="140" t="n"/>
+      <c r="C79" s="146" t="n"/>
+      <c r="D79" s="146" t="n"/>
+      <c r="E79" s="146" t="n"/>
+      <c r="F79" s="146" t="n"/>
+      <c r="G79" s="146" t="n"/>
+      <c r="H79" s="146" t="n"/>
+      <c r="I79" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G77">
+  <conditionalFormatting sqref="G8:G76">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$81</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -545,15 +545,6 @@
     </border>
     <border/>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD1DCE8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFC67A29"/>
       </left>
@@ -567,11 +558,20 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1DCE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -910,22 +910,22 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -949,29 +949,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2096,7 +2081,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46322.672666175</v>
+        <v>46323.70689792356</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2158,7 +2143,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46322.672666175</v>
+        <v>46323.70689792356</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2291,7 +2276,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.991</v>
+        <v>0.964</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>284.17</v>
@@ -2304,7 +2289,7 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2313,39 +2298,39 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>CFW</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.479</v>
+        <v>0.465</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>478.75</v>
+        <v>1836.63</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -2354,33 +2339,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>CFW</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Calfrac Well Services Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.47</v>
+        <v>0.458</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1836.63</v>
+        <v>478.75</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2414,7 +2399,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.339</v>
+        <v>0.383</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>43632.38</v>
@@ -2455,7 +2440,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.203</v>
+        <v>0.194</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>69914.25999999999</v>
@@ -2468,7 +2453,7 @@
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2477,39 +2462,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>WCN</t>
+          <t>FFH</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Waste Connections Inc.</t>
+          <t>Fairfax Financial Holdings Limited</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.155</v>
+        <v>0.135</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>39435.42</v>
+        <v>31304.08</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Waste Connections Inc provides non-hazardous waste collection transfer and disposal services in the United States and Canada</t>
+          <t>Fairfax Financial Holdings Limited through its subsidiaries provides property and casualty insurance and reinsurance and investment management services in Canada the United States the Middle East and Asia and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="106" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2518,39 +2503,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>ENGH</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.154</v>
+        <v>0.123</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>634.6900000000001</v>
+        <v>398.33</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="106" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2559,33 +2544,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>ENGH</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited</t>
+          <t>Enghouse Systems Limited</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.096</v>
+        <v>0.113</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>50539.87</v>
+        <v>634.6900000000001</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
+          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2619,7 +2604,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.062</v>
+        <v>0.099</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>1789.16</v>
@@ -2632,7 +2617,7 @@
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2641,12 +2626,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>GFR</t>
+          <t>CEU</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Greenfire Resources Ltd.</t>
+          <t>CES Energy Solutions Corp.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -2656,65 +2641,65 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.043</v>
+        <v>0.096</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>1476.14</v>
+        <v>2712.63</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Greenfire Resources Ltd together with its subsidiaries engages in the exploration development and operation of oil and gas properties in the Athabasca oil sands region of Alberta Canada</t>
+          <t>CES Energy Solutions Corp together with its subsidiaries engages in the design implementation and manufacture of advanced consumable fluids and specialty chemicals in the United States and Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="106" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Loblaw Companies Limited</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>884.7</v>
+        <v>50539.87</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -2723,39 +2708,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>600.1</v>
+        <v>884.7</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="127" t="inlineStr">
         <is>
@@ -2764,39 +2749,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.411</v>
+        <v>0.496</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>925.72</v>
+        <v>600.1</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="52" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="127" t="inlineStr">
         <is>
@@ -2805,12 +2790,12 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -2824,20 +2809,20 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.339</v>
+        <v>0.423</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>804.05</v>
+        <v>925.72</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2846,33 +2831,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.299</v>
+        <v>0.353</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>43014.26</v>
+        <v>804.05</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
@@ -2887,33 +2872,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.289</v>
+        <v>0.335</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>15597.29</v>
+        <v>3333.46</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2928,12 +2913,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -2947,14 +2932,14 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.282</v>
+        <v>0.313</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>373.79</v>
+        <v>15597.29</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2969,39 +2954,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Open Text Corporation</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.271</v>
+        <v>0.309</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>5405.28</v>
+        <v>43014.26</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Open Text Corporation provides data management solutions for enterprise AI in North Central and South America Europe the Middle East Africa Australia Japan Singapore India and China</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="52" customHeight="1">
+    <row r="26" ht="106" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -3010,39 +2995,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.254</v>
+        <v>0.236</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>389.1</v>
+        <v>99672.56</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="106" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -3051,12 +3036,12 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
@@ -3070,20 +3055,20 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.198</v>
+        <v>0.213</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>99672.56</v>
+        <v>336.54</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3092,12 +3077,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3111,14 +3096,14 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>336.54</v>
+        <v>80962.39</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
@@ -3133,39 +3118,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.183</v>
+        <v>0.197</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>80962.39</v>
+        <v>389.1</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -3174,39 +3159,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>35208.26</v>
+        <v>1545.36</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="88" customHeight="1">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -3215,33 +3200,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>DOL</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Dollarama Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Broadline Retail</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
         <v>0.169</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>1545.36</v>
+        <v>35208.26</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -3256,12 +3241,12 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>GEI</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>Gibson Energy Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
@@ -3275,14 +3260,14 @@
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>4428.98</v>
+        <v>3837.96</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -3297,12 +3282,12 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -3316,20 +3301,20 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.156</v>
+        <v>0.151</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>3837.96</v>
+        <v>4428.98</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="106" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="127" t="inlineStr">
         <is>
@@ -3338,33 +3323,33 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.131</v>
+        <v>0.12</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>398.33</v>
+        <v>1823.99</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -3398,7 +3383,7 @@
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="H35" s="124" t="n">
         <v>2245.27</v>
@@ -3439,7 +3424,7 @@
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.532</v>
+        <v>0.499</v>
       </c>
       <c r="H36" s="119" t="n">
         <v>732.01</v>
@@ -3452,7 +3437,7 @@
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="70" customHeight="1">
+    <row r="37" ht="88" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="128" t="inlineStr">
         <is>
@@ -3461,33 +3446,33 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>ACT Energy Technologies Ltd.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.391</v>
+        <v>0.378</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>3333.46</v>
+        <v>211.92</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>ACT Energy Technologies Ltd together with its subsidiaries provides directional drilling services and related downhole technologies to oil and natural gas companies in Canada and the United States</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
@@ -3495,38 +3480,38 @@
     </row>
     <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="128" t="inlineStr">
+      <c r="B38" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C38" s="115" t="inlineStr">
+      <c r="C38" s="130" t="inlineStr">
         <is>
           <t>DSG</t>
         </is>
       </c>
-      <c r="D38" s="116" t="inlineStr">
+      <c r="D38" s="131" t="inlineStr">
         <is>
           <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
-      <c r="E38" s="117" t="inlineStr">
+      <c r="E38" s="132" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F38" s="117" t="inlineStr">
+      <c r="F38" s="132" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G38" s="118" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="H38" s="119" t="n">
+      <c r="G38" s="133" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="H38" s="134" t="n">
         <v>6794.59</v>
       </c>
-      <c r="I38" s="120" t="inlineStr">
+      <c r="I38" s="135" t="inlineStr">
         <is>
           <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
@@ -3534,91 +3519,63 @@
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row r="39" ht="8" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C39" s="130" t="inlineStr">
-        <is>
-          <t>NWC</t>
-        </is>
-      </c>
-      <c r="D39" s="131" t="inlineStr">
-        <is>
-          <t>The North West Company Inc.</t>
-        </is>
-      </c>
-      <c r="E39" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F39" s="132" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G39" s="133" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="H39" s="134" t="n">
-        <v>1823.99</v>
-      </c>
-      <c r="I39" s="135" t="inlineStr">
-        <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
-        </is>
-      </c>
+      <c r="B39" s="136" t="n"/>
+      <c r="C39" s="137" t="n"/>
+      <c r="D39" s="138" t="n"/>
+      <c r="E39" s="139" t="n"/>
+      <c r="F39" s="139" t="n"/>
+      <c r="G39" s="140" t="n"/>
+      <c r="H39" s="141" t="n"/>
+      <c r="I39" s="142" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="8" customHeight="1">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="136" t="n"/>
-      <c r="C40" s="137" t="n"/>
-      <c r="D40" s="138" t="n"/>
-      <c r="E40" s="139" t="n"/>
-      <c r="F40" s="139" t="n"/>
-      <c r="G40" s="140" t="n"/>
-      <c r="H40" s="141" t="n"/>
-      <c r="I40" s="142" t="n"/>
+      <c r="B40" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C40" s="144" t="n"/>
+      <c r="D40" s="144" t="n"/>
+      <c r="E40" s="144" t="n"/>
+      <c r="F40" s="144" t="n"/>
+      <c r="G40" s="144" t="n"/>
+      <c r="H40" s="144" t="n"/>
+      <c r="I40" s="144" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="34" customHeight="1" thickBot="1">
+    <row r="41" ht="28" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C41" s="144" t="n"/>
-      <c r="D41" s="144" t="n"/>
-      <c r="E41" s="144" t="n"/>
-      <c r="F41" s="144" t="n"/>
-      <c r="G41" s="144" t="n"/>
-      <c r="H41" s="144" t="n"/>
-      <c r="I41" s="144" t="n"/>
+      <c r="B41" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C41" s="146" t="n"/>
+      <c r="D41" s="146" t="n"/>
+      <c r="E41" s="146" t="n"/>
+      <c r="F41" s="146" t="n"/>
+      <c r="G41" s="146" t="n"/>
+      <c r="H41" s="146" t="n"/>
+      <c r="I41" s="146" t="n"/>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
-    <row r="42" ht="28" customHeight="1">
+    <row r="42">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C42" s="146" t="n"/>
-      <c r="D42" s="146" t="n"/>
-      <c r="E42" s="146" t="n"/>
-      <c r="F42" s="146" t="n"/>
-      <c r="G42" s="146" t="n"/>
-      <c r="H42" s="146" t="n"/>
-      <c r="I42" s="146" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="43" t="n"/>
+      <c r="E42" s="43" t="n"/>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="43" t="n"/>
+      <c r="I42" s="43" t="n"/>
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
@@ -3717,11 +3674,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B6:G6"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G39">
+  <conditionalFormatting sqref="G8:G38">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4662,7 +4619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4702,7 +4659,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46322.672666175</v>
+        <v>46323.70689792356</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4835,7 +4792,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.862</v>
+        <v>0.911</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>16701.36</v>
@@ -4876,7 +4833,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.732</v>
+        <v>0.749</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>42172.99</v>
@@ -4889,7 +4846,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="52" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4898,39 +4855,39 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Workday Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>45398.38</v>
+        <v>17904.45</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -4939,39 +4896,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Workday Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.653</v>
+        <v>0.613</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>17904.45</v>
+        <v>45398.38</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4980,12 +4937,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>Labcorp Holdings Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -4995,18 +4952,18 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.541</v>
+        <v>0.431</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>47137.94</v>
+        <v>25388.92</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>Labcorp Holdings Inc provides laboratory services</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -5021,12 +4978,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -5036,24 +4993,24 @@
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.497</v>
+        <v>0.382</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>42201.2</v>
+        <v>224207.66</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5062,33 +5019,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.378</v>
+        <v>0.343</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>9701.92</v>
+        <v>12320.13</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -5122,7 +5079,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.33</v>
+        <v>0.316</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>12471.61</v>
@@ -5135,7 +5092,7 @@
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -5144,39 +5101,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.309</v>
+        <v>0.26</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>224207.66</v>
+        <v>61019.13</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="106" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5185,12 +5142,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -5200,24 +5157,24 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Aerospace and Defense</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.307</v>
+        <v>0.249</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>12320.13</v>
+        <v>116283.92</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -5226,39 +5183,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.267</v>
+        <v>0.226</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>61019.13</v>
+        <v>88425.8</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Emerson Electric Co</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="106" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5267,33 +5224,33 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Aerospace and Defense</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.228</v>
+        <v>0.224</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>116283.92</v>
+        <v>12451.88</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
+          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5327,7 +5284,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.227</v>
+        <v>0.221</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>35615.09</v>
@@ -5340,7 +5297,7 @@
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="52" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5349,33 +5306,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>12451.88</v>
+        <v>60523.16</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
@@ -5409,7 +5366,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.204</v>
+        <v>0.209</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>41984.2</v>
@@ -5431,39 +5388,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.186</v>
+        <v>0.175</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>16850.47</v>
+        <v>23268.86</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="52" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="126" t="inlineStr">
         <is>
@@ -5472,33 +5429,33 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Emerson Electric Co.</t>
+          <t>Nasdaq Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.181</v>
+        <v>0.158</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>88425.8</v>
+        <v>51024.57</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Emerson Electric Co</t>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -5532,7 +5489,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.177</v>
+        <v>0.154</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>17905.95</v>
@@ -5554,33 +5511,33 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.17</v>
+        <v>0.148</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>60523.16</v>
+        <v>57901.58</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5595,33 +5552,33 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Elevance Health Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.168</v>
+        <v>0.13</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>23268.86</v>
+        <v>87408.73</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
+          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -5636,39 +5593,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Avery Dennison Corporation</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Containers and Packaging</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.151</v>
+        <v>0.127</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>57901.58</v>
+        <v>12719.07</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="126" t="inlineStr">
         <is>
@@ -5677,39 +5634,39 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Tyler Technologies Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.146</v>
+        <v>0.115</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>15869.76</v>
+        <v>13525.55</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="126" t="inlineStr">
         <is>
@@ -5718,39 +5675,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Nasdaq Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.145</v>
+        <v>0.111</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>51024.57</v>
+        <v>15869.76</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="88" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="126" t="inlineStr">
         <is>
@@ -5759,33 +5716,33 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Elevance Health Inc.</t>
+          <t>Johnson Controls International plc</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.135</v>
+        <v>0.096</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>87408.73</v>
+        <v>93531.92999999999</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
+          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -5800,39 +5757,39 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation</t>
+          <t>Occidental Petroleum Corporation</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Containers and Packaging</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.121</v>
+        <v>0.09</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>12719.07</v>
+        <v>58304.85</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
+          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="52" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="126" t="inlineStr">
         <is>
@@ -5841,33 +5798,33 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc.</t>
+          <t>HCA Healthcare Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.112</v>
+        <v>0.068</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>13525.55</v>
+        <v>94806.22</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+          <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
@@ -5901,7 +5858,7 @@
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.051</v>
+        <v>0.058</v>
       </c>
       <c r="H34" s="119" t="n">
         <v>73585.95</v>
@@ -5914,48 +5871,48 @@
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="70" customHeight="1">
+    <row r="35" ht="88" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B35" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation</t>
+          <t>Charles River Laboratories International Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.05</v>
+        <v>1.251</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>58304.85</v>
+        <v>14054.04</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
+          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="52" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="127" t="inlineStr">
         <is>
@@ -5964,12 +5921,12 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Moderna Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
@@ -5979,24 +5936,24 @@
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>3.278</v>
+        <v>0.838</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>74971.71000000001</v>
+        <v>45576.53</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Moderna Inc a biotechnology company provides messenger RNA medicines in the United States Europe and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="88" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="127" t="inlineStr">
         <is>
@@ -6005,33 +5962,33 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>1.139</v>
+        <v>0.678</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>14054.04</v>
+        <v>17950.14</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
@@ -6065,7 +6022,7 @@
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.767</v>
+        <v>0.649</v>
       </c>
       <c r="H38" s="119" t="n">
         <v>142623.33</v>
@@ -6087,39 +6044,39 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.587</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>17950.14</v>
+        <v>47137.94</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="88" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="127" t="inlineStr">
         <is>
@@ -6128,39 +6085,39 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.513</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>11772.74</v>
+        <v>42201.2</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="52" customHeight="1">
+    <row r="41" ht="88" customHeight="1">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="127" t="inlineStr">
         <is>
@@ -6169,39 +6126,39 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Gartner Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.417</v>
+        <v>0.503</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>33875.2</v>
+        <v>11772.74</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="52" customHeight="1" thickBot="1">
+    <row r="42" ht="70" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
       <c r="B42" s="127" t="inlineStr">
         <is>
@@ -6210,33 +6167,33 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.401</v>
+        <v>0.499</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>104249.82</v>
+        <v>241617.28</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
@@ -6270,7 +6227,7 @@
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.396</v>
+        <v>0.403</v>
       </c>
       <c r="H43" s="124" t="n">
         <v>28342.5</v>
@@ -6283,7 +6240,7 @@
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="70" customHeight="1" thickBot="1">
+    <row r="44" ht="52" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
       <c r="B44" s="127" t="inlineStr">
         <is>
@@ -6292,33 +6249,33 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>1054668.83</v>
+        <v>33875.2</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6333,39 +6290,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.349</v>
+        <v>0.376</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>116683.09</v>
+        <v>9701.92</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row r="46" ht="52" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6374,12 +6331,12 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Automatic Data Processing Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
@@ -6389,24 +6346,24 @@
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>24969.64</v>
+        <v>104249.82</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="88" customHeight="1" thickBot="1">
+    <row r="47" ht="70" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6415,12 +6372,12 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
@@ -6434,14 +6391,14 @@
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.335</v>
+        <v>0.346</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>26039.81</v>
+        <v>30639.57</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6456,39 +6413,39 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.329</v>
+        <v>0.344</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>33430.82</v>
+        <v>24969.64</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="88" customHeight="1">
+    <row r="49" ht="70" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6497,39 +6454,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.328</v>
+        <v>0.342</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>21455.05</v>
+        <v>151241.83</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="106" customHeight="1">
+    <row r="50" ht="70" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6537,12 +6494,12 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
@@ -6552,22 +6509,22 @@
       </c>
       <c r="F50" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G50" s="118" t="n">
-        <v>0.325</v>
+        <v>0.341</v>
       </c>
       <c r="H50" s="119" t="n">
-        <v>48910.32</v>
+        <v>1054668.83</v>
       </c>
       <c r="I50" s="120" t="inlineStr">
         <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="70" customHeight="1">
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="88" customHeight="1">
       <c r="B51" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6575,12 +6532,12 @@
       </c>
       <c r="C51" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D51" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E51" s="123" t="inlineStr">
@@ -6594,14 +6551,14 @@
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.317</v>
+        <v>0.337</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>30639.57</v>
+        <v>26039.81</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6570,12 @@
       </c>
       <c r="C52" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D52" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E52" s="117" t="inlineStr">
@@ -6628,22 +6585,22 @@
       </c>
       <c r="F52" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G52" s="118" t="n">
-        <v>0.303</v>
+        <v>0.334</v>
       </c>
       <c r="H52" s="119" t="n">
-        <v>151241.83</v>
+        <v>33430.82</v>
       </c>
       <c r="I52" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="70" customHeight="1">
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="106" customHeight="1">
       <c r="B53" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6651,12 +6608,12 @@
       </c>
       <c r="C53" s="121" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="D53" s="122" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Becton Dickinson and Company</t>
         </is>
       </c>
       <c r="E53" s="123" t="inlineStr">
@@ -6666,18 +6623,18 @@
       </c>
       <c r="F53" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G53" s="118" t="n">
-        <v>0.297</v>
+        <v>0.315</v>
       </c>
       <c r="H53" s="124" t="n">
-        <v>32165.5</v>
+        <v>48910.32</v>
       </c>
       <c r="I53" s="125" t="inlineStr">
         <is>
-          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
+          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6665,7 @@
         </is>
       </c>
       <c r="G54" s="118" t="n">
-        <v>0.274</v>
+        <v>0.306</v>
       </c>
       <c r="H54" s="119" t="n">
         <v>15537.74</v>
@@ -6719,7 +6676,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="70" customHeight="1">
+    <row r="55" ht="88" customHeight="1">
       <c r="B55" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6727,33 +6684,33 @@
       </c>
       <c r="C55" s="121" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D55" s="122" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E55" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F55" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G55" s="118" t="n">
-        <v>0.262</v>
+        <v>0.292</v>
       </c>
       <c r="H55" s="124" t="n">
-        <v>25579.38</v>
+        <v>21455.05</v>
       </c>
       <c r="I55" s="125" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -6765,37 +6722,37 @@
       </c>
       <c r="C56" s="115" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D56" s="116" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E56" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F56" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G56" s="118" t="n">
-        <v>0.256</v>
+        <v>0.285</v>
       </c>
       <c r="H56" s="119" t="n">
-        <v>12857.61</v>
+        <v>25579.38</v>
       </c>
       <c r="I56" s="120" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="52" customHeight="1">
+          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="70" customHeight="1">
       <c r="B57" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6803,33 +6760,33 @@
       </c>
       <c r="C57" s="121" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D57" s="122" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E57" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F57" s="123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G57" s="118" t="n">
-        <v>0.221</v>
+        <v>0.271</v>
       </c>
       <c r="H57" s="124" t="n">
-        <v>682021.24</v>
+        <v>32165.5</v>
       </c>
       <c r="I57" s="125" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
         </is>
       </c>
     </row>
@@ -6841,33 +6798,33 @@
       </c>
       <c r="C58" s="115" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D58" s="116" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E58" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F58" s="117" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G58" s="118" t="n">
-        <v>0.218</v>
+        <v>0.266</v>
       </c>
       <c r="H58" s="119" t="n">
-        <v>498865.76</v>
+        <v>12857.61</v>
       </c>
       <c r="I58" s="120" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
     </row>
@@ -6879,37 +6836,37 @@
       </c>
       <c r="C59" s="121" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D59" s="122" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E59" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F59" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G59" s="118" t="n">
-        <v>0.217</v>
+        <v>0.241</v>
       </c>
       <c r="H59" s="124" t="n">
-        <v>183538.16</v>
+        <v>498865.76</v>
       </c>
       <c r="I59" s="125" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="52" customHeight="1">
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
       <c r="B60" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6917,71 +6874,71 @@
       </c>
       <c r="C60" s="115" t="inlineStr">
         <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D60" s="116" t="inlineStr">
+        <is>
+          <t>ConocoPhillips</t>
+        </is>
+      </c>
+      <c r="E60" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F60" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G60" s="118" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="H60" s="119" t="n">
+        <v>156513.85</v>
+      </c>
+      <c r="I60" s="120" t="inlineStr">
+        <is>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="52" customHeight="1">
+      <c r="B61" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C61" s="121" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="D60" s="116" t="inlineStr">
+      <c r="D61" s="122" t="inlineStr">
         <is>
           <t>Chevron Corporation</t>
         </is>
       </c>
-      <c r="E60" s="117" t="inlineStr">
+      <c r="E61" s="123" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F60" s="117" t="inlineStr">
+      <c r="F61" s="123" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G60" s="118" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="H60" s="119" t="n">
+      <c r="G61" s="118" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="H61" s="124" t="n">
         <v>404759.18</v>
       </c>
-      <c r="I60" s="120" t="inlineStr">
+      <c r="I61" s="125" t="inlineStr">
         <is>
           <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="70" customHeight="1">
-      <c r="B61" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C61" s="121" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="D61" s="122" t="inlineStr">
-        <is>
-          <t>ConocoPhillips</t>
-        </is>
-      </c>
-      <c r="E61" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F61" s="123" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G61" s="118" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="H61" s="124" t="n">
-        <v>156513.85</v>
-      </c>
-      <c r="I61" s="125" t="inlineStr">
-        <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
     </row>
@@ -6993,37 +6950,37 @@
       </c>
       <c r="C62" s="115" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D62" s="116" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E62" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F62" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G62" s="118" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H62" s="119" t="n">
-        <v>677009.86</v>
+        <v>31594.32</v>
       </c>
       <c r="I62" s="120" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="70" customHeight="1">
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="52" customHeight="1">
       <c r="B63" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -7031,33 +6988,33 @@
       </c>
       <c r="C63" s="121" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D63" s="122" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E63" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F63" s="123" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G63" s="118" t="n">
-        <v>0.186</v>
+        <v>0.229</v>
       </c>
       <c r="H63" s="124" t="n">
-        <v>371563.85</v>
+        <v>682021.24</v>
       </c>
       <c r="I63" s="125" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7026,12 @@
       </c>
       <c r="C64" s="115" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D64" s="116" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E64" s="117" t="inlineStr">
@@ -7084,18 +7041,18 @@
       </c>
       <c r="F64" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G64" s="118" t="n">
-        <v>0.179</v>
+        <v>0.225</v>
       </c>
       <c r="H64" s="119" t="n">
-        <v>111058.59</v>
+        <v>183538.16</v>
       </c>
       <c r="I64" s="120" t="inlineStr">
         <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
     </row>
@@ -7107,71 +7064,71 @@
       </c>
       <c r="C65" s="121" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D65" s="122" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E65" s="123" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F65" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G65" s="118" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H65" s="124" t="n">
+        <v>677009.86</v>
+      </c>
+      <c r="I65" s="125" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="70" customHeight="1">
+      <c r="B66" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C66" s="115" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="D66" s="116" t="inlineStr">
+        <is>
+          <t>Medtronic plc</t>
+        </is>
+      </c>
+      <c r="E66" s="117" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F65" s="123" t="inlineStr">
+      <c r="F66" s="117" t="inlineStr">
         <is>
           <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
-      <c r="G65" s="118" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="H65" s="124" t="n">
-        <v>31594.32</v>
-      </c>
-      <c r="I65" s="125" t="inlineStr">
-        <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="88" customHeight="1">
-      <c r="B66" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C66" s="115" t="inlineStr">
-        <is>
-          <t>EOG</t>
-        </is>
-      </c>
-      <c r="D66" s="116" t="inlineStr">
-        <is>
-          <t>EOG Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E66" s="117" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F66" s="117" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
       <c r="G66" s="118" t="n">
-        <v>0.168</v>
+        <v>0.207</v>
       </c>
       <c r="H66" s="119" t="n">
-        <v>75763.52</v>
+        <v>111058.59</v>
       </c>
       <c r="I66" s="120" t="inlineStr">
         <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
         </is>
       </c>
     </row>
@@ -7183,33 +7140,33 @@
       </c>
       <c r="C67" s="121" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D67" s="122" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E67" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F67" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G67" s="118" t="n">
-        <v>0.161</v>
+        <v>0.204</v>
       </c>
       <c r="H67" s="124" t="n">
-        <v>23628.33</v>
+        <v>16850.47</v>
       </c>
       <c r="I67" s="125" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
     </row>
@@ -7221,147 +7178,147 @@
       </c>
       <c r="C68" s="115" t="inlineStr">
         <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="D68" s="116" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="E68" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F68" s="117" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G68" s="118" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="H68" s="119" t="n">
+        <v>371563.85</v>
+      </c>
+      <c r="I68" s="120" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="88" customHeight="1">
+      <c r="B69" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C69" s="121" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D69" s="122" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E69" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F69" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G69" s="118" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H69" s="124" t="n">
+        <v>75763.52</v>
+      </c>
+      <c r="I69" s="125" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="52" customHeight="1">
+      <c r="B70" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C70" s="115" t="inlineStr">
+        <is>
+          <t>ULTA</t>
+        </is>
+      </c>
+      <c r="D70" s="116" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc.</t>
+        </is>
+      </c>
+      <c r="E70" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F70" s="117" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G70" s="118" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H70" s="119" t="n">
+        <v>23628.33</v>
+      </c>
+      <c r="I70" s="120" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="70" customHeight="1">
+      <c r="B71" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C71" s="121" t="inlineStr">
+        <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="D68" s="116" t="inlineStr">
+      <c r="D71" s="122" t="inlineStr">
         <is>
           <t>Pfizer Inc.</t>
         </is>
       </c>
-      <c r="E68" s="117" t="inlineStr">
+      <c r="E71" s="123" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F68" s="117" t="inlineStr">
+      <c r="F71" s="123" t="inlineStr">
         <is>
           <t>Pharmaceuticals</t>
         </is>
       </c>
-      <c r="G68" s="118" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="H68" s="119" t="n">
+      <c r="G71" s="118" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H71" s="124" t="n">
         <v>159089.29</v>
       </c>
-      <c r="I68" s="120" t="inlineStr">
+      <c r="I71" s="125" t="inlineStr">
         <is>
           <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="52" customHeight="1">
-      <c r="B69" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C69" s="121" t="inlineStr">
-        <is>
-          <t>RSG</t>
-        </is>
-      </c>
-      <c r="D69" s="122" t="inlineStr">
-        <is>
-          <t>Republic Services Inc.</t>
-        </is>
-      </c>
-      <c r="E69" s="123" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F69" s="123" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G69" s="118" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="H69" s="124" t="n">
-        <v>66372.58</v>
-      </c>
-      <c r="I69" s="125" t="inlineStr">
-        <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="70" customHeight="1">
-      <c r="B70" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C70" s="115" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
-      </c>
-      <c r="D70" s="116" t="inlineStr">
-        <is>
-          <t>Dollar General Corporation</t>
-        </is>
-      </c>
-      <c r="E70" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F70" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G70" s="118" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="H70" s="119" t="n">
-        <v>27315.89</v>
-      </c>
-      <c r="I70" s="120" t="inlineStr">
-        <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="52" customHeight="1">
-      <c r="B71" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C71" s="121" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="D71" s="122" t="inlineStr">
-        <is>
-          <t>The Procter &amp; Gamble Company</t>
-        </is>
-      </c>
-      <c r="E71" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F71" s="123" t="inlineStr">
-        <is>
-          <t>Household Products</t>
-        </is>
-      </c>
-      <c r="G71" s="118" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="H71" s="124" t="n">
-        <v>345602.03</v>
-      </c>
-      <c r="I71" s="125" t="inlineStr">
-        <is>
-          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
         </is>
       </c>
     </row>
@@ -7373,33 +7330,33 @@
       </c>
       <c r="C72" s="115" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D72" s="116" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
+          <t>Republic Services Inc.</t>
         </is>
       </c>
       <c r="E72" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F72" s="117" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G72" s="118" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="H72" s="119" t="n">
-        <v>22965.61</v>
+        <v>66372.58</v>
       </c>
       <c r="I72" s="120" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co</t>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
         </is>
       </c>
     </row>
@@ -7411,33 +7368,33 @@
       </c>
       <c r="C73" s="121" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="D73" s="122" t="inlineStr">
         <is>
-          <t>Universal Health Services Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="E73" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F73" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G73" s="118" t="n">
-        <v>0.048</v>
+        <v>0.113</v>
       </c>
       <c r="H73" s="124" t="n">
-        <v>10428.64</v>
+        <v>27315.89</v>
       </c>
       <c r="I73" s="125" t="inlineStr">
         <is>
-          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
+          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
         </is>
       </c>
     </row>
@@ -7449,159 +7406,235 @@
       </c>
       <c r="C74" s="115" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D74" s="116" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc.</t>
+          <t>Church &amp; Dwight Co. Inc.</t>
         </is>
       </c>
       <c r="E74" s="117" t="inlineStr">
         <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F74" s="117" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="G74" s="118" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H74" s="119" t="n">
+        <v>22965.61</v>
+      </c>
+      <c r="I74" s="120" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="52" customHeight="1">
+      <c r="B75" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C75" s="121" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="D75" s="122" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="E75" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F75" s="123" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="G75" s="118" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H75" s="124" t="n">
+        <v>345602.03</v>
+      </c>
+      <c r="I75" s="125" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="70" customHeight="1">
+      <c r="B76" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C76" s="115" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="D76" s="116" t="inlineStr">
+        <is>
+          <t>Universal Health Services Inc.</t>
+        </is>
+      </c>
+      <c r="E76" s="117" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F74" s="117" t="inlineStr">
+      <c r="F76" s="117" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
       </c>
-      <c r="G74" s="118" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="H74" s="119" t="n">
-        <v>94806.22</v>
-      </c>
-      <c r="I74" s="120" t="inlineStr">
-        <is>
-          <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="70" customHeight="1">
-      <c r="B75" s="128" t="inlineStr">
+      <c r="G76" s="118" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H76" s="119" t="n">
+        <v>10428.64</v>
+      </c>
+      <c r="I76" s="120" t="inlineStr">
+        <is>
+          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="52" customHeight="1">
+      <c r="B77" s="128" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C75" s="121" t="inlineStr">
-        <is>
-          <t>VEEV</t>
-        </is>
-      </c>
-      <c r="D75" s="122" t="inlineStr">
-        <is>
-          <t>Veeva Systems Inc.</t>
-        </is>
-      </c>
-      <c r="E75" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F75" s="123" t="inlineStr">
-        <is>
-          <t>Health Care Technology</t>
-        </is>
-      </c>
-      <c r="G75" s="118" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="H75" s="124" t="n">
-        <v>45576.53</v>
-      </c>
-      <c r="I75" s="125" t="inlineStr">
-        <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="52" customHeight="1">
-      <c r="B76" s="129" t="inlineStr">
+      <c r="C77" s="121" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D77" s="122" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="E77" s="123" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F77" s="123" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G77" s="118" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="H77" s="124" t="n">
+        <v>21029.38</v>
+      </c>
+      <c r="I77" s="125" t="inlineStr">
+        <is>
+          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="70" customHeight="1">
+      <c r="B78" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C76" s="147" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="D76" s="148" t="inlineStr">
-        <is>
-          <t>PTC Inc.</t>
-        </is>
-      </c>
-      <c r="E76" s="149" t="inlineStr">
+      <c r="C78" s="130" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D78" s="131" t="inlineStr">
+        <is>
+          <t>Accenture plc</t>
+        </is>
+      </c>
+      <c r="E78" s="132" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F76" s="149" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G76" s="133" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H76" s="150" t="n">
-        <v>21029.38</v>
-      </c>
-      <c r="I76" s="151" t="inlineStr">
-        <is>
-          <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="8" customHeight="1">
-      <c r="B77" s="152" t="n"/>
-      <c r="C77" s="152" t="n"/>
-      <c r="D77" s="152" t="n"/>
-      <c r="E77" s="152" t="n"/>
-      <c r="F77" s="152" t="n"/>
-      <c r="G77" s="152" t="n"/>
-      <c r="H77" s="152" t="n"/>
-      <c r="I77" s="152" t="n"/>
-    </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="B78" s="143" t="inlineStr">
+      <c r="F78" s="132" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="G78" s="133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H78" s="134" t="n">
+        <v>116683.09</v>
+      </c>
+      <c r="I78" s="135" t="inlineStr">
+        <is>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1">
+      <c r="B79" s="147" t="n"/>
+      <c r="C79" s="147" t="n"/>
+      <c r="D79" s="147" t="n"/>
+      <c r="E79" s="147" t="n"/>
+      <c r="F79" s="147" t="n"/>
+      <c r="G79" s="147" t="n"/>
+      <c r="H79" s="147" t="n"/>
+      <c r="I79" s="147" t="n"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="B80" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C78" s="144" t="n"/>
-      <c r="D78" s="144" t="n"/>
-      <c r="E78" s="144" t="n"/>
-      <c r="F78" s="144" t="n"/>
-      <c r="G78" s="144" t="n"/>
-      <c r="H78" s="144" t="n"/>
-      <c r="I78" s="144" t="n"/>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="B79" s="145" t="inlineStr">
+      <c r="C80" s="144" t="n"/>
+      <c r="D80" s="144" t="n"/>
+      <c r="E80" s="144" t="n"/>
+      <c r="F80" s="144" t="n"/>
+      <c r="G80" s="144" t="n"/>
+      <c r="H80" s="144" t="n"/>
+      <c r="I80" s="144" t="n"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="B81" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C79" s="146" t="n"/>
-      <c r="D79" s="146" t="n"/>
-      <c r="E79" s="146" t="n"/>
-      <c r="F79" s="146" t="n"/>
-      <c r="G79" s="146" t="n"/>
-      <c r="H79" s="146" t="n"/>
-      <c r="I79" s="146" t="n"/>
+      <c r="C81" s="146" t="n"/>
+      <c r="D81" s="146" t="n"/>
+      <c r="E81" s="146" t="n"/>
+      <c r="F81" s="146" t="n"/>
+      <c r="G81" s="146" t="n"/>
+      <c r="H81" s="146" t="n"/>
+      <c r="I81" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B80:I80"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G76">
+  <conditionalFormatting sqref="G8:G78">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$38</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -383,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -558,20 +558,11 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD1DCE8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -910,22 +901,22 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -957,6 +948,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2081,7 +2087,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46323.70689792356</v>
+        <v>46324.71790944901</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2143,7 +2149,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46323.70689792356</v>
+        <v>46324.71790944901</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2276,7 +2282,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.964</v>
+        <v>0.987</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>284.17</v>
@@ -2289,7 +2295,7 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2298,33 +2304,33 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>FTG</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Firan Technology Group Corporation</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.465</v>
+        <v>0.773</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>1836.63</v>
+        <v>443.56</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Firan Technology Group Corporation manufactures and sells aerospace and defense electronic products and subsystems in Canada the United States Asia Europe China internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2358,7 +2364,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.458</v>
+        <v>0.441</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>478.75</v>
@@ -2371,7 +2377,7 @@
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2380,39 +2386,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Constellation Software Inc.</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.383</v>
+        <v>0.306</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>43632.38</v>
+        <v>107611.83</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2421,39 +2427,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Precision Drilling Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.194</v>
+        <v>0.16</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>69914.25999999999</v>
+        <v>1097.13</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Precision Drilling Corporation a drilling company provides onshore drilling services to exploration and production companies in the oil and natural gas and geothermal industries in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2462,33 +2468,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>FFH</t>
+          <t>TNZ</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Fairfax Financial Holdings Limited</t>
+          <t>Tenaz Energy Corp.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.135</v>
+        <v>0.151</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>31304.08</v>
+        <v>1570.2</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Fairfax Financial Holdings Limited through its subsidiaries provides property and casualty insurance and reinsurance and investment management services in Canada the United States the Middle East and Asia and internationally</t>
+          <t>Tenaz Energy Corp an energy company engages in the acquisition and development of oil and gas assets in Canada and the Netherlands</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2522,7 +2528,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.123</v>
+        <v>0.126</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>398.33</v>
@@ -2535,7 +2541,7 @@
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2544,39 +2550,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ENGH</t>
+          <t>CEU</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited</t>
+          <t>CES Energy Solutions Corp.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.113</v>
+        <v>0.105</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>634.6900000000001</v>
+        <v>2712.63</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
+          <t>CES Energy Solutions Corp together with its subsidiaries engages in the design implementation and manufacture of advanced consumable fluids and specialty chemicals in the United States and Canada</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2585,33 +2591,33 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>VET</t>
+          <t>ENGH</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc.</t>
+          <t>Enghouse Systems Limited</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.099</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>1789.16</v>
+        <v>634.6900000000001</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
+          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -2626,12 +2632,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>CEU</t>
+          <t>VET</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>CES Energy Solutions Corp.</t>
+          <t>Vermilion Energy Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -2641,65 +2647,65 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.096</v>
+        <v>0.038</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>2712.63</v>
+        <v>1789.16</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>CES Energy Solutions Corp together with its subsidiaries engages in the design implementation and manufacture of advanced consumable fluids and specialty chemicals in the United States and Canada</t>
+          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="106" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.096</v>
+        <v>0.675</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>50539.87</v>
+        <v>884.7</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Loblaw Companies Limited a food and pharmacy company provides grocery pharmacy and healthcare services health and beauty products apparel general merchandise financial services and wireless mobile products and services in Canada and the United States</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -2708,39 +2714,39 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Docebo Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.676</v>
+        <v>0.421</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>884.7</v>
+        <v>600.1</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="88" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="127" t="inlineStr">
         <is>
@@ -2749,12 +2755,12 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>Constellation Software Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
@@ -2768,20 +2774,20 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.496</v>
+        <v>0.344</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>600.1</v>
+        <v>43632.38</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="52" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="127" t="inlineStr">
         <is>
@@ -2790,12 +2796,12 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>SGY</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>Surge Energy Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -2809,20 +2815,20 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.423</v>
+        <v>0.305</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>925.72</v>
+        <v>804.05</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="52" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -2831,33 +2837,33 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.353</v>
+        <v>0.252</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>804.05</v>
+        <v>43014.26</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
@@ -2872,39 +2878,39 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.335</v>
+        <v>0.247</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>3333.46</v>
+        <v>15597.29</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="106" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2913,12 +2919,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -2932,14 +2938,14 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.313</v>
+        <v>0.21</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>15597.29</v>
+        <v>99672.56</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2954,39 +2960,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>IPO</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>InPlay Oil Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.309</v>
+        <v>0.169</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>43014.26</v>
+        <v>336.54</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="106" customHeight="1">
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -2995,12 +3001,12 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
@@ -3014,14 +3020,14 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.236</v>
+        <v>0.152</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>99672.56</v>
+        <v>1545.36</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -3036,12 +3042,12 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Tamarack Valley Energy Ltd.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
@@ -3055,20 +3061,20 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.213</v>
+        <v>0.121</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>336.54</v>
+        <v>4428.98</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3077,12 +3083,12 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
@@ -3096,178 +3102,178 @@
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.198</v>
+        <v>0.108</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>80962.39</v>
+        <v>2245.27</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B29" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>ACQ</t>
+          <t>ACX</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>AutoCanada Inc.</t>
+          <t>ACT Energy Technologies Ltd.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.197</v>
+        <v>0.39</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>389.1</v>
+        <v>211.92</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+          <t>ACT Energy Technologies Ltd together with its subsidiaries provides directional drilling services and related downhole technologies to oil and natural gas companies in Canada and the United States</t>
         </is>
       </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="88" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B30" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.19</v>
+        <v>0.316</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>1545.36</v>
+        <v>3333.46</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B31" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>DOL</t>
+          <t>SOIL</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Dollarama Inc.</t>
+          <t>Saturn Oil &amp; Gas Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Broadline Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.169</v>
+        <v>0.299</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>35208.26</v>
+        <v>925.72</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Dollarama Inc operates a chain of stores and provides related logistical and administrative support activities</t>
+          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>GEI</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.165</v>
+        <v>0.277</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>3837.96</v>
+        <v>389.1</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -3275,81 +3281,81 @@
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B33" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.151</v>
+        <v>0.267</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>4428.98</v>
+        <v>6794.59</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="52" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B34" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>NWC</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>The North West Company Inc.</t>
+          <t>Suncor Energy Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples Distribution and Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.12</v>
+        <v>0.175</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>1823.99</v>
+        <v>80962.39</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
+          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
@@ -3357,212 +3363,128 @@
     </row>
     <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C35" s="121" t="inlineStr">
-        <is>
-          <t>HWX</t>
-        </is>
-      </c>
-      <c r="D35" s="122" t="inlineStr">
-        <is>
-          <t>Headwater Exploration Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="123" t="inlineStr">
+      <c r="B35" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C35" s="130" t="inlineStr">
+        <is>
+          <t>GEI</t>
+        </is>
+      </c>
+      <c r="D35" s="131" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="132" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F35" s="123" t="inlineStr">
+      <c r="F35" s="132" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G35" s="118" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="H35" s="124" t="n">
-        <v>2245.27</v>
-      </c>
-      <c r="I35" s="125" t="inlineStr">
-        <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+      <c r="G35" s="133" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="H35" s="134" t="n">
+        <v>3837.96</v>
+      </c>
+      <c r="I35" s="135" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row r="36" ht="8" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C36" s="115" t="inlineStr">
-        <is>
-          <t>GUD</t>
-        </is>
-      </c>
-      <c r="D36" s="116" t="inlineStr">
-        <is>
-          <t>Knight Therapeutics Inc.</t>
-        </is>
-      </c>
-      <c r="E36" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F36" s="117" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G36" s="118" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="H36" s="119" t="n">
-        <v>732.01</v>
-      </c>
-      <c r="I36" s="120" t="inlineStr">
-        <is>
-          <t>Knight Therapeutics Inc focuses on acquiring in-licensing out-licensing marketing and commercializing prescription pharmaceutical products in Canada and Latin America</t>
-        </is>
-      </c>
+      <c r="B36" s="136" t="n"/>
+      <c r="C36" s="137" t="n"/>
+      <c r="D36" s="138" t="n"/>
+      <c r="E36" s="139" t="n"/>
+      <c r="F36" s="139" t="n"/>
+      <c r="G36" s="140" t="n"/>
+      <c r="H36" s="141" t="n"/>
+      <c r="I36" s="142" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="88" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C37" s="121" t="inlineStr">
-        <is>
-          <t>ACX</t>
-        </is>
-      </c>
-      <c r="D37" s="122" t="inlineStr">
-        <is>
-          <t>ACT Energy Technologies Ltd.</t>
-        </is>
-      </c>
-      <c r="E37" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F37" s="123" t="inlineStr">
-        <is>
-          <t>Energy Equipment and Services</t>
-        </is>
-      </c>
-      <c r="G37" s="118" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="H37" s="124" t="n">
-        <v>211.92</v>
-      </c>
-      <c r="I37" s="125" t="inlineStr">
-        <is>
-          <t>ACT Energy Technologies Ltd together with its subsidiaries provides directional drilling services and related downhole technologies to oil and natural gas companies in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B37" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C37" s="144" t="n"/>
+      <c r="D37" s="144" t="n"/>
+      <c r="E37" s="144" t="n"/>
+      <c r="F37" s="144" t="n"/>
+      <c r="G37" s="144" t="n"/>
+      <c r="H37" s="144" t="n"/>
+      <c r="I37" s="144" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C38" s="130" t="inlineStr">
-        <is>
-          <t>DSG</t>
-        </is>
-      </c>
-      <c r="D38" s="131" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="132" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F38" s="132" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G38" s="133" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="H38" s="134" t="n">
-        <v>6794.59</v>
-      </c>
-      <c r="I38" s="135" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
-        </is>
-      </c>
+      <c r="B38" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C38" s="146" t="n"/>
+      <c r="D38" s="146" t="n"/>
+      <c r="E38" s="146" t="n"/>
+      <c r="F38" s="146" t="n"/>
+      <c r="G38" s="146" t="n"/>
+      <c r="H38" s="146" t="n"/>
+      <c r="I38" s="146" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="8" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="136" t="n"/>
-      <c r="C39" s="137" t="n"/>
-      <c r="D39" s="138" t="n"/>
-      <c r="E39" s="139" t="n"/>
-      <c r="F39" s="139" t="n"/>
-      <c r="G39" s="140" t="n"/>
-      <c r="H39" s="141" t="n"/>
-      <c r="I39" s="142" t="n"/>
+      <c r="B39" s="49" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="89" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="54" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="20.4" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C40" s="144" t="n"/>
-      <c r="D40" s="144" t="n"/>
-      <c r="E40" s="144" t="n"/>
-      <c r="F40" s="144" t="n"/>
-      <c r="G40" s="144" t="n"/>
-      <c r="H40" s="144" t="n"/>
-      <c r="I40" s="144" t="n"/>
+      <c r="B40" s="48" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="89" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="28" customHeight="1" thickBot="1">
+    <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C41" s="146" t="n"/>
-      <c r="D41" s="146" t="n"/>
-      <c r="E41" s="146" t="n"/>
-      <c r="F41" s="146" t="n"/>
-      <c r="G41" s="146" t="n"/>
-      <c r="H41" s="146" t="n"/>
-      <c r="I41" s="146" t="n"/>
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="96" t="n"/>
+      <c r="I41" s="74" t="n"/>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
@@ -3674,11 +3596,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B40:I40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G38">
+  <conditionalFormatting sqref="G8:G35">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4619,7 +4541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4659,7 +4581,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46323.70689792356</v>
+        <v>46324.71790944901</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4764,7 +4686,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -4773,12 +4695,12 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Revvity Inc.</t>
+          <t>Illumina Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
@@ -4792,20 +4714,20 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.911</v>
+        <v>1.092</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>16701.36</v>
+        <v>39661.06</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Revvity Inc provides health sciences solutions technologies and services</t>
+          <t>Illumina Inc provides sequencing- and array-based solutions for genetic and genomic analysis in the Americas Europe Greater China the Asia Pacific the Middle East and Africa</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="88" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -4814,12 +4736,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Labcorp Holdings Inc.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -4829,24 +4751,24 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.749</v>
+        <v>0.435</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>42172.99</v>
+        <v>25388.92</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
+          <t>Labcorp Holdings Inc provides laboratory services</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4855,33 +4777,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>United Rentals Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.65</v>
+        <v>0.298</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>17904.45</v>
+        <v>64935.97</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>United Rentals Inc through its subsidiaries operates as an equipment rental company in the United States Canada Europe Australia and New Zealand</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4896,39 +4818,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Workday Inc.</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.613</v>
+        <v>0.267</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>45398.38</v>
+        <v>88425.8</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
+          <t>Emerson Electric Co</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="52" customHeight="1">
+    <row r="12" ht="106" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4937,39 +4859,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Labcorp Holdings Inc.</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Aerospace and Defense</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.431</v>
+        <v>0.264</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>25388.92</v>
+        <v>116283.92</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Labcorp Holdings Inc provides laboratory services</t>
+          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4978,12 +4900,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4993,24 +4915,24 @@
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.382</v>
+        <v>0.263</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>224207.66</v>
+        <v>28944.51</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>GE HealthCare Technologies Inc engages in the development manufacture and marketing of products services and complementary digital solutions used in the diagnosis treatment and monitoring of patients in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5019,39 +4941,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.343</v>
+        <v>0.198</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>12320.13</v>
+        <v>60523.16</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -5060,39 +4982,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>J</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>Jacobs Solutions Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.316</v>
+        <v>0.178</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>12471.61</v>
+        <v>16016.73</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>The J</t>
+          <t>Jacobs Solutions Inc engages in the infrastructure and advanced facilities and consulting businesses in the United States Europe Canada India Asia Australia New Zealand the Middle East and Africa</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -5101,39 +5023,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Johnson Controls International plc</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.26</v>
+        <v>0.093</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>61019.13</v>
+        <v>93531.92999999999</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="106" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5142,74 +5064,74 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Occidental Petroleum Corporation</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Aerospace and Defense</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.249</v>
+        <v>0.047</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>116283.92</v>
+        <v>58304.85</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
+          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Emerson Electric Co.</t>
+          <t>Charles River Laboratories International Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.226</v>
+        <v>1.197</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>88425.8</v>
+        <v>14054.04</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Emerson Electric Co</t>
+          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5217,40 +5139,40 @@
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Revvity Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.224</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>12451.88</v>
+        <v>16701.36</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>GoDaddy Inc engages in the design and development of cloud-based products in the United States and internationally</t>
+          <t>Revvity Inc provides health sciences solutions technologies and services</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -5258,163 +5180,163 @@
     </row>
     <row r="20" ht="70" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Technology</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.221</v>
+        <v>0.838</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>35615.09</v>
+        <v>45576.53</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
+          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B21" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.212</v>
+        <v>0.765</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>60523.16</v>
+        <v>17904.45</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B22" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.209</v>
+        <v>0.707</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>41984.2</v>
+        <v>42172.99</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
+          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.175</v>
+        <v>0.679</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>23268.86</v>
+        <v>17950.14</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
+          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -5422,81 +5344,81 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B24" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Nasdaq Inc.</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.158</v>
+        <v>0.624</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>51024.57</v>
+        <v>47137.94</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B25" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.154</v>
+        <v>0.592</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>17905.95</v>
+        <v>42201.2</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions Inc provides investor communications and technology-driven solutions for the financial services industry in the United States and internationally</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -5504,40 +5426,40 @@
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.148</v>
+        <v>0.536</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>57901.58</v>
+        <v>241617.28</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
@@ -5545,265 +5467,265 @@
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B27" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Elevance Health Inc.</t>
+          <t>Workday Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.13</v>
+        <v>0.513</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>87408.73</v>
+        <v>45398.38</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Elevance Health Inc together with its subsidiaries operates as a health benefits company in the United States</t>
+          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B28" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Containers and Packaging</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.127</v>
+        <v>0.443</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>12719.07</v>
+        <v>26039.81</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation operates as a materials science and digital identification solutions company in the North America Europe the Middle East North Africa Asia and Latin America</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B29" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.115</v>
+        <v>0.435</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>13525.55</v>
+        <v>224207.66</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="88" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B30" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.111</v>
+        <v>0.423</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>15869.76</v>
+        <v>24969.64</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>News Corporation a media and information services company creates and distributes authoritative and engaging content and other products and services for consumers and businesses in the United States Canada Europe Australasia and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="88" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B31" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.096</v>
+        <v>0.422</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>93531.92999999999</v>
+        <v>1054668.83</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B32" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.09</v>
+        <v>0.412</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>58304.85</v>
+        <v>12320.13</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="52" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc.</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -5813,38 +5735,38 @@
       </c>
       <c r="F33" s="123" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.068</v>
+        <v>0.369</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>94806.22</v>
+        <v>30639.57</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="52" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
@@ -5854,24 +5776,24 @@
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.058</v>
+        <v>0.367</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>73585.95</v>
+        <v>151241.83</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>The Cigna Group together with its subsidiaries provides insurance and related products and services in the United States</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="52" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="127" t="inlineStr">
         <is>
@@ -5880,39 +5802,39 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>1.251</v>
+        <v>0.353</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>14054.04</v>
+        <v>33875.2</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
+          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="70" customHeight="1">
+    <row r="36" ht="88" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="127" t="inlineStr">
         <is>
@@ -5921,33 +5843,33 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.838</v>
+        <v>0.31</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>45576.53</v>
+        <v>21455.05</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
@@ -5962,39 +5884,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.678</v>
+        <v>0.285</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>17950.14</v>
+        <v>12857.61</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="70" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="127" t="inlineStr">
         <is>
@@ -6003,33 +5925,33 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>ServiceNow Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.649</v>
+        <v>0.274</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>142623.33</v>
+        <v>20324.32</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
@@ -6044,33 +5966,33 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>Roper Technologies Inc.</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.587</v>
+        <v>0.249</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>47137.94</v>
+        <v>35615.09</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
@@ -6085,39 +6007,39 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Ulta Beauty Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.242</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>42201.2</v>
+        <v>23628.33</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="88" customHeight="1">
+    <row r="41" ht="70" customHeight="1">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="127" t="inlineStr">
         <is>
@@ -6126,33 +6048,33 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>Gartner Inc.</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.503</v>
+        <v>0.229</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>11772.74</v>
+        <v>15537.74</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>Gartner Inc provides business and technology insights to support decision-making and performance on an organization’s mission-critical priorities in the United States Canada Europe the Middle East Africa and internationally</t>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -6167,12 +6089,12 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
@@ -6182,24 +6104,24 @@
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.499</v>
+        <v>0.229</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>241617.28</v>
+        <v>183538.16</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="70" customHeight="1">
+    <row r="43" ht="52" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6208,33 +6130,33 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Electronic Equipment Instruments and Components</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.403</v>
+        <v>0.228</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>28342.5</v>
+        <v>16850.47</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>Williams-Sonoma Inc operates as an omni-channel specialty retailer of various products for home the United States and internationally</t>
+          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
@@ -6249,33 +6171,33 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.389</v>
+        <v>0.218</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>33875.2</v>
+        <v>404759.18</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6290,39 +6212,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.376</v>
+        <v>0.21</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>9701.92</v>
+        <v>156513.85</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc together with its subsidiaries operates as a financial digital platform and enterprise solutions provider for the investment community</t>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="52" customHeight="1">
+    <row r="46" ht="70" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6331,33 +6253,33 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.347</v>
+        <v>0.21</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>104249.82</v>
+        <v>31594.32</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc provides cloud-based human capital management (HCM) solutions worldwide</t>
+          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
@@ -6372,33 +6294,33 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>ServiceNow Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.346</v>
+        <v>0.202</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>30639.57</v>
+        <v>142623.33</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6413,33 +6335,33 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>ExxonMobil Holdings Corporation</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.344</v>
+        <v>0.2</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>24969.64</v>
+        <v>677009.86</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
@@ -6454,39 +6376,39 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Nasdaq Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.342</v>
+        <v>0.165</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>151241.83</v>
+        <v>51024.57</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="70" customHeight="1">
+    <row r="50" ht="88" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6494,1147 +6416,159 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D50" s="116" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>EOG Resources Inc.</t>
         </is>
       </c>
       <c r="E50" s="117" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F50" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G50" s="118" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="H50" s="119" t="n">
+        <v>75763.52</v>
+      </c>
+      <c r="I50" s="120" t="inlineStr">
+        <is>
+          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="B51" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C51" s="121" t="inlineStr">
+        <is>
+          <t>HCA</t>
+        </is>
+      </c>
+      <c r="D51" s="122" t="inlineStr">
+        <is>
+          <t>HCA Healthcare Inc.</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="inlineStr">
+        <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F50" s="117" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G50" s="118" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H50" s="119" t="n">
-        <v>1054668.83</v>
-      </c>
-      <c r="I50" s="120" t="inlineStr">
-        <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="88" customHeight="1">
-      <c r="B51" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C51" s="121" t="inlineStr">
-        <is>
-          <t>WST</t>
-        </is>
-      </c>
-      <c r="D51" s="122" t="inlineStr">
-        <is>
-          <t>West Pharmaceutical Services Inc.</t>
-        </is>
-      </c>
-      <c r="E51" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
       <c r="F51" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G51" s="118" t="n">
-        <v>0.337</v>
+        <v>0.119</v>
       </c>
       <c r="H51" s="124" t="n">
-        <v>26039.81</v>
+        <v>94806.22</v>
       </c>
       <c r="I51" s="125" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="70" customHeight="1">
-      <c r="B52" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C52" s="115" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
-      </c>
-      <c r="D52" s="116" t="inlineStr">
-        <is>
-          <t>Biogen Inc.</t>
-        </is>
-      </c>
-      <c r="E52" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F52" s="117" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="G52" s="118" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="H52" s="119" t="n">
-        <v>33430.82</v>
-      </c>
-      <c r="I52" s="120" t="inlineStr">
-        <is>
-          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="106" customHeight="1">
-      <c r="B53" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C53" s="121" t="inlineStr">
-        <is>
-          <t>BDX</t>
-        </is>
-      </c>
-      <c r="D53" s="122" t="inlineStr">
-        <is>
-          <t>Becton Dickinson and Company</t>
-        </is>
-      </c>
-      <c r="E53" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F53" s="123" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G53" s="118" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="H53" s="124" t="n">
-        <v>48910.32</v>
-      </c>
-      <c r="I53" s="125" t="inlineStr">
-        <is>
-          <t>Becton Dickinson and Company develops manufactures and sells medical supplies devices laboratory equipment and diagnostic products for healthcare institutions physicians life science researchers clinical laboratories pharmaceutical industry and the general public worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="70" customHeight="1">
-      <c r="B54" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C54" s="115" t="inlineStr">
-        <is>
-          <t>APA</t>
-        </is>
-      </c>
-      <c r="D54" s="116" t="inlineStr">
-        <is>
-          <t>APA Corporation</t>
-        </is>
-      </c>
-      <c r="E54" s="117" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F54" s="117" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G54" s="118" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="H54" s="119" t="n">
-        <v>15537.74</v>
-      </c>
-      <c r="I54" s="120" t="inlineStr">
-        <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="88" customHeight="1">
-      <c r="B55" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C55" s="121" t="inlineStr">
-        <is>
-          <t>IFF</t>
-        </is>
-      </c>
-      <c r="D55" s="122" t="inlineStr">
-        <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
-        </is>
-      </c>
-      <c r="E55" s="123" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F55" s="123" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="G55" s="118" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H55" s="124" t="n">
-        <v>21455.05</v>
-      </c>
-      <c r="I55" s="125" t="inlineStr">
-        <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="70" customHeight="1">
-      <c r="B56" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C56" s="115" t="inlineStr">
-        <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="D56" s="116" t="inlineStr">
-        <is>
-          <t>Cognizant Technology Solutions Corporation</t>
-        </is>
-      </c>
-      <c r="E56" s="117" t="inlineStr">
+          <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1">
+      <c r="B52" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C52" s="147" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D52" s="148" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="E52" s="149" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F56" s="117" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="G56" s="118" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="H56" s="119" t="n">
-        <v>25579.38</v>
-      </c>
-      <c r="I56" s="120" t="inlineStr">
-        <is>
-          <t>Cognizant Technology Solutions Corporation a professional services company provides consulting and technology and outsourcing services in North America Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="70" customHeight="1">
-      <c r="B57" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C57" s="121" t="inlineStr">
-        <is>
-          <t>CNC</t>
-        </is>
-      </c>
-      <c r="D57" s="122" t="inlineStr">
-        <is>
-          <t>Centene Corporation</t>
-        </is>
-      </c>
-      <c r="E57" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F57" s="123" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G57" s="118" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="H57" s="124" t="n">
-        <v>32165.5</v>
-      </c>
-      <c r="I57" s="125" t="inlineStr">
-        <is>
-          <t>Centene Corporation operates as a managed care company that provides programs and services to under-insured families and commercial organizations in the United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="70" customHeight="1">
-      <c r="B58" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C58" s="115" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="D58" s="116" t="inlineStr">
-        <is>
-          <t>Hasbro Inc.</t>
-        </is>
-      </c>
-      <c r="E58" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F58" s="117" t="inlineStr">
-        <is>
-          <t>Leisure Products</t>
-        </is>
-      </c>
-      <c r="G58" s="118" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="H58" s="119" t="n">
-        <v>12857.61</v>
-      </c>
-      <c r="I58" s="120" t="inlineStr">
-        <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="70" customHeight="1">
-      <c r="B59" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C59" s="121" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D59" s="122" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated</t>
-        </is>
-      </c>
-      <c r="E59" s="123" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F59" s="123" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G59" s="118" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="H59" s="124" t="n">
-        <v>498865.76</v>
-      </c>
-      <c r="I59" s="125" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="70" customHeight="1">
-      <c r="B60" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C60" s="115" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="D60" s="116" t="inlineStr">
-        <is>
-          <t>ConocoPhillips</t>
-        </is>
-      </c>
-      <c r="E60" s="117" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F60" s="117" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G60" s="118" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="H60" s="119" t="n">
-        <v>156513.85</v>
-      </c>
-      <c r="I60" s="120" t="inlineStr">
-        <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="52" customHeight="1">
-      <c r="B61" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C61" s="121" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="D61" s="122" t="inlineStr">
-        <is>
-          <t>Chevron Corporation</t>
-        </is>
-      </c>
-      <c r="E61" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F61" s="123" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G61" s="118" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="H61" s="124" t="n">
-        <v>404759.18</v>
-      </c>
-      <c r="I61" s="125" t="inlineStr">
-        <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="70" customHeight="1">
-      <c r="B62" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C62" s="115" t="inlineStr">
-        <is>
-          <t>RMD</t>
-        </is>
-      </c>
-      <c r="D62" s="116" t="inlineStr">
-        <is>
-          <t>ResMed Inc.</t>
-        </is>
-      </c>
-      <c r="E62" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F62" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G62" s="118" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H62" s="119" t="n">
-        <v>31594.32</v>
-      </c>
-      <c r="I62" s="120" t="inlineStr">
-        <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="52" customHeight="1">
-      <c r="B63" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C63" s="121" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D63" s="122" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E63" s="123" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F63" s="123" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G63" s="118" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="H63" s="124" t="n">
-        <v>682021.24</v>
-      </c>
-      <c r="I63" s="125" t="inlineStr">
-        <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="70" customHeight="1">
-      <c r="B64" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C64" s="115" t="inlineStr">
-        <is>
-          <t>GILD</t>
-        </is>
-      </c>
-      <c r="D64" s="116" t="inlineStr">
-        <is>
-          <t>Gilead Sciences Inc.</t>
-        </is>
-      </c>
-      <c r="E64" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F64" s="117" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="G64" s="118" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="H64" s="119" t="n">
-        <v>183538.16</v>
-      </c>
-      <c r="I64" s="120" t="inlineStr">
-        <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="70" customHeight="1">
-      <c r="B65" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C65" s="121" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D65" s="122" t="inlineStr">
-        <is>
-          <t>ExxonMobil Holdings Corporation</t>
-        </is>
-      </c>
-      <c r="E65" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F65" s="123" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G65" s="118" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H65" s="124" t="n">
-        <v>677009.86</v>
-      </c>
-      <c r="I65" s="125" t="inlineStr">
-        <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="70" customHeight="1">
-      <c r="B66" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C66" s="115" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="D66" s="116" t="inlineStr">
-        <is>
-          <t>Medtronic plc</t>
-        </is>
-      </c>
-      <c r="E66" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F66" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Equipment and Supplies</t>
-        </is>
-      </c>
-      <c r="G66" s="118" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="H66" s="119" t="n">
-        <v>111058.59</v>
-      </c>
-      <c r="I66" s="120" t="inlineStr">
-        <is>
-          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="52" customHeight="1">
-      <c r="B67" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C67" s="121" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
-      <c r="D67" s="122" t="inlineStr">
-        <is>
-          <t>CDW Corporation</t>
-        </is>
-      </c>
-      <c r="E67" s="123" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F67" s="123" t="inlineStr">
-        <is>
-          <t>Electronic Equipment Instruments and Components</t>
-        </is>
-      </c>
-      <c r="G67" s="118" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="H67" s="124" t="n">
-        <v>16850.47</v>
-      </c>
-      <c r="I67" s="125" t="inlineStr">
-        <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="70" customHeight="1">
-      <c r="B68" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C68" s="115" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="D68" s="116" t="inlineStr">
-        <is>
-          <t>The Coca-Cola Company</t>
-        </is>
-      </c>
-      <c r="E68" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F68" s="117" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="G68" s="118" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="H68" s="119" t="n">
-        <v>371563.85</v>
-      </c>
-      <c r="I68" s="120" t="inlineStr">
-        <is>
-          <t>The Coca-Cola Company a beverage company manufactures and sells various nonalcoholic beverages in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="88" customHeight="1">
-      <c r="B69" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C69" s="121" t="inlineStr">
-        <is>
-          <t>EOG</t>
-        </is>
-      </c>
-      <c r="D69" s="122" t="inlineStr">
-        <is>
-          <t>EOG Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E69" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F69" s="123" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G69" s="118" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H69" s="124" t="n">
-        <v>75763.52</v>
-      </c>
-      <c r="I69" s="125" t="inlineStr">
-        <is>
-          <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="52" customHeight="1">
-      <c r="B70" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C70" s="115" t="inlineStr">
-        <is>
-          <t>ULTA</t>
-        </is>
-      </c>
-      <c r="D70" s="116" t="inlineStr">
-        <is>
-          <t>Ulta Beauty Inc.</t>
-        </is>
-      </c>
-      <c r="E70" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F70" s="117" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G70" s="118" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="H70" s="119" t="n">
-        <v>23628.33</v>
-      </c>
-      <c r="I70" s="120" t="inlineStr">
-        <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="70" customHeight="1">
-      <c r="B71" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C71" s="121" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="D71" s="122" t="inlineStr">
-        <is>
-          <t>Pfizer Inc.</t>
-        </is>
-      </c>
-      <c r="E71" s="123" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F71" s="123" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="G71" s="118" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H71" s="124" t="n">
-        <v>159089.29</v>
-      </c>
-      <c r="I71" s="125" t="inlineStr">
-        <is>
-          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="52" customHeight="1">
-      <c r="B72" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C72" s="115" t="inlineStr">
-        <is>
-          <t>RSG</t>
-        </is>
-      </c>
-      <c r="D72" s="116" t="inlineStr">
-        <is>
-          <t>Republic Services Inc.</t>
-        </is>
-      </c>
-      <c r="E72" s="117" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F72" s="117" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G72" s="118" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="H72" s="119" t="n">
-        <v>66372.58</v>
-      </c>
-      <c r="I72" s="120" t="inlineStr">
-        <is>
-          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="70" customHeight="1">
-      <c r="B73" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C73" s="121" t="inlineStr">
-        <is>
-          <t>DG</t>
-        </is>
-      </c>
-      <c r="D73" s="122" t="inlineStr">
-        <is>
-          <t>Dollar General Corporation</t>
-        </is>
-      </c>
-      <c r="E73" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F73" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples Distribution and Retail</t>
-        </is>
-      </c>
-      <c r="G73" s="118" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="H73" s="124" t="n">
-        <v>27315.89</v>
-      </c>
-      <c r="I73" s="125" t="inlineStr">
-        <is>
-          <t>Dollar General Corporation a discount retailer provides various merchandise products in the southern southwestern midwestern and eastern United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="52" customHeight="1">
-      <c r="B74" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C74" s="115" t="inlineStr">
-        <is>
-          <t>CHD</t>
-        </is>
-      </c>
-      <c r="D74" s="116" t="inlineStr">
-        <is>
-          <t>Church &amp; Dwight Co. Inc.</t>
-        </is>
-      </c>
-      <c r="E74" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F74" s="117" t="inlineStr">
-        <is>
-          <t>Household Products</t>
-        </is>
-      </c>
-      <c r="G74" s="118" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H74" s="119" t="n">
-        <v>22965.61</v>
-      </c>
-      <c r="I74" s="120" t="inlineStr">
-        <is>
-          <t>Church &amp; Dwight Co</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="52" customHeight="1">
-      <c r="B75" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C75" s="121" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="D75" s="122" t="inlineStr">
-        <is>
-          <t>The Procter &amp; Gamble Company</t>
-        </is>
-      </c>
-      <c r="E75" s="123" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F75" s="123" t="inlineStr">
-        <is>
-          <t>Household Products</t>
-        </is>
-      </c>
-      <c r="G75" s="118" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H75" s="124" t="n">
-        <v>345602.03</v>
-      </c>
-      <c r="I75" s="125" t="inlineStr">
-        <is>
-          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="70" customHeight="1">
-      <c r="B76" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C76" s="115" t="inlineStr">
-        <is>
-          <t>UHS</t>
-        </is>
-      </c>
-      <c r="D76" s="116" t="inlineStr">
-        <is>
-          <t>Universal Health Services Inc.</t>
-        </is>
-      </c>
-      <c r="E76" s="117" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F76" s="117" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G76" s="118" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="H76" s="119" t="n">
-        <v>10428.64</v>
-      </c>
-      <c r="I76" s="120" t="inlineStr">
-        <is>
-          <t>Universal Health Services Inc through its subsidiaries owns and operates acute care hospitals and outpatient and behavioral health care facilities in the United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="52" customHeight="1">
-      <c r="B77" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C77" s="121" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="D77" s="122" t="inlineStr">
-        <is>
-          <t>PTC Inc.</t>
-        </is>
-      </c>
-      <c r="E77" s="123" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F77" s="123" t="inlineStr">
+      <c r="F52" s="149" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G77" s="118" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H77" s="124" t="n">
+      <c r="G52" s="133" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H52" s="150" t="n">
         <v>21029.38</v>
       </c>
-      <c r="I77" s="125" t="inlineStr">
+      <c r="I52" s="151" t="inlineStr">
         <is>
           <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="70" customHeight="1">
-      <c r="B78" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C78" s="130" t="inlineStr">
-        <is>
-          <t>ACN</t>
-        </is>
-      </c>
-      <c r="D78" s="131" t="inlineStr">
-        <is>
-          <t>Accenture plc</t>
-        </is>
-      </c>
-      <c r="E78" s="132" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F78" s="132" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="G78" s="133" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H78" s="134" t="n">
-        <v>116683.09</v>
-      </c>
-      <c r="I78" s="135" t="inlineStr">
-        <is>
-          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="8" customHeight="1">
-      <c r="B79" s="147" t="n"/>
-      <c r="C79" s="147" t="n"/>
-      <c r="D79" s="147" t="n"/>
-      <c r="E79" s="147" t="n"/>
-      <c r="F79" s="147" t="n"/>
-      <c r="G79" s="147" t="n"/>
-      <c r="H79" s="147" t="n"/>
-      <c r="I79" s="147" t="n"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="B80" s="143" t="inlineStr">
+    <row r="53" ht="8" customHeight="1">
+      <c r="B53" s="152" t="n"/>
+      <c r="C53" s="152" t="n"/>
+      <c r="D53" s="152" t="n"/>
+      <c r="E53" s="152" t="n"/>
+      <c r="F53" s="152" t="n"/>
+      <c r="G53" s="152" t="n"/>
+      <c r="H53" s="152" t="n"/>
+      <c r="I53" s="152" t="n"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="B54" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C80" s="144" t="n"/>
-      <c r="D80" s="144" t="n"/>
-      <c r="E80" s="144" t="n"/>
-      <c r="F80" s="144" t="n"/>
-      <c r="G80" s="144" t="n"/>
-      <c r="H80" s="144" t="n"/>
-      <c r="I80" s="144" t="n"/>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="B81" s="145" t="inlineStr">
+      <c r="C54" s="144" t="n"/>
+      <c r="D54" s="144" t="n"/>
+      <c r="E54" s="144" t="n"/>
+      <c r="F54" s="144" t="n"/>
+      <c r="G54" s="144" t="n"/>
+      <c r="H54" s="144" t="n"/>
+      <c r="I54" s="144" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="B55" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C81" s="146" t="n"/>
-      <c r="D81" s="146" t="n"/>
-      <c r="E81" s="146" t="n"/>
-      <c r="F81" s="146" t="n"/>
-      <c r="G81" s="146" t="n"/>
-      <c r="H81" s="146" t="n"/>
-      <c r="I81" s="146" t="n"/>
+      <c r="C55" s="146" t="n"/>
+      <c r="D55" s="146" t="n"/>
+      <c r="E55" s="146" t="n"/>
+      <c r="F55" s="146" t="n"/>
+      <c r="G55" s="146" t="n"/>
+      <c r="H55" s="146" t="n"/>
+      <c r="I55" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G78">
+  <conditionalFormatting sqref="G8:G52">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -901,22 +901,22 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -948,19 +948,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2087,7 +2087,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46324.71790944901</v>
+        <v>46325.70470768796</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46324.71790944901</v>
+        <v>46325.70470768796</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.773</v>
+        <v>0.606</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>443.56</v>
@@ -2345,33 +2345,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>CFW</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd.</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.441</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>478.75</v>
+        <v>777.7</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -2386,39 +2386,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CFW</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Calfrac Well Services Ltd.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.306</v>
+        <v>0.416</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>107611.83</v>
+        <v>478.75</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Calfrac Well Services Ltd together with its subsidiaries provides specialized oilfield services in Canada the United States and Argentina</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -2427,33 +2427,33 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Precision Drilling Corporation</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.16</v>
+        <v>0.338</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>1097.13</v>
+        <v>997.76</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Precision Drilling Corporation a drilling company provides onshore drilling services to exploration and production companies in the oil and natural gas and geothermal industries in the United States Canada and internationally</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.151</v>
+        <v>0.155</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>1570.2</v>
@@ -2500,7 +2500,7 @@
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="106" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>POU</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp.</t>
+          <t>Paramount Resources Ltd.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
@@ -2524,24 +2524,24 @@
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.126</v>
+        <v>0.153</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>398.33</v>
+        <v>3216.97</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
+          <t>Paramount Resources Ltd an energy company explores for and develops conventional and unconventional petroleum and natural gas reserves and resources in Canada</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2550,39 +2550,39 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CEU</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>CES Energy Solutions Corp.</t>
+          <t>Methanex Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.105</v>
+        <v>0.139</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>2712.63</v>
+        <v>4773.24</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>CES Energy Solutions Corp together with its subsidiaries engages in the design implementation and manufacture of advanced consumable fluids and specialty chemicals in the United States and Canada</t>
+          <t>Methanex Corporation engages in the production and sale of methanol and ammonia in Asia Pacific North America Europe and South America</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="52" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="28" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -2591,39 +2591,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>ENGH</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited</t>
+          <t>Precision Drilling Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.135</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>634.6900000000001</v>
+        <v>1097.13</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Enghouse Systems Limited together with its subsidiaries develops enterprise software solutions worldwide</t>
+          <t>Precision Drilling Corporation a drilling company provides onshore drilling services to exploration and production companies in the oil and natural gas and geothermal industries in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="88" customHeight="1">
+    <row r="17" ht="106" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>VET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc.</t>
+          <t>PHX Energy Services Corp.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -2647,38 +2647,38 @@
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.038</v>
+        <v>0.116</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>1789.16</v>
+        <v>398.33</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
+          <t>PHX Energy Services Corp provides horizontal and directional drilling services rents performance drilling motors and sells motor equipment and parts to oil and natural gas exploration and development companies in Canada the United States the Middle East regions and internationally</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>CEU</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>CES Energy Solutions Corp.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -2692,55 +2692,55 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.675</v>
+        <v>0.104</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>884.7</v>
+        <v>2712.63</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>CES Energy Solutions Corp together with its subsidiaries engages in the design implementation and manufacture of advanced consumable fluids and specialty chemicals in the United States and Canada</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Docebo Inc.</t>
+          <t>TMX Group Limited</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.421</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>600.1</v>
+        <v>10036.23</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Docebo Inc develops and provides learning management platform for training in Canada the United States and internationally</t>
+          <t>TMX Group Limited operates exchanges markets and clearinghouses primarily for capital markets in Canada the United States the United Kingdom Germany and internationally</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
@@ -2748,40 +2748,40 @@
     </row>
     <row r="20" ht="88" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>AAV</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Constellation Software Inc.</t>
+          <t>Advantage Energy Ltd.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.344</v>
+        <v>0.097</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>43632.38</v>
+        <v>1240.82</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Constellation Software Inc together with its subsidiaries acquires builds and manages vertical market software businesses to develop mission-critical software solutions for public and private sector markets</t>
+          <t>Advantage Energy Ltd together with its subsidiaries engages in the acquisition exploitation development and production natural gas crude oil and natural gas liquids (NGLs) in the Province of Alberta Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
@@ -2789,19 +2789,19 @@
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>SGY</t>
+          <t>PSK</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Surge Energy Inc.</t>
+          <t>PrairieSky Royalty Ltd.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -2815,55 +2815,55 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.305</v>
+        <v>0.095</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>804.05</v>
+        <v>5448.33</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+          <t>PrairieSky Royalty Ltd holds crude oil and natural gas royalty interests in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>VET</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>Vermilion Energy Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.252</v>
+        <v>0.055</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>43014.26</v>
+        <v>1789.16</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation operates as a content and technology company in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Vermilion Energy Inc engages in petroleum and natural gas focuses on the acquisition exploration development and optimization of producing properties in North America Europe and Australia</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
@@ -2893,24 +2893,24 @@
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.247</v>
+        <v>0.67</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>15597.29</v>
+        <v>884.7</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="106" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="127" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>CNQ</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
@@ -2938,20 +2938,20 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.21</v>
+        <v>0.236</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>99672.56</v>
+        <v>15597.29</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="106" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>IPO</t>
+          <t>CNQ</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp.</t>
+          <t>Canadian Natural Resources Limited</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
@@ -2979,14 +2979,14 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.169</v>
+        <v>0.23</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>336.54</v>
+        <v>99672.56</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>InPlay Oil Corp engages in the acquisition exploration development and production of petroleum and natural gas properties in Canada</t>
+          <t>Canadian Natural Resources Limited engages in the acquisition exploration development production marketing and sale of crude oil natural gas and natural gas liquids (NGLs) in Western Canada the United Kingdom sector of the North Sea and Offshore Africa</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.152</v>
+        <v>0.161</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>1545.36</v>
@@ -3042,39 +3042,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>NWC</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd.</t>
+          <t>The North West Company Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Consumer Staples Distribution and Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.121</v>
+        <v>0.155</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>4428.98</v>
+        <v>1823.99</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Tamarack Valley Energy Ltd engages in the exploration development production and sale of oil natural gas and natural gas liquids in the Western Canadian sedimentary basin</t>
+          <t>The North West Company Inc through its subsidiaries engages in the retail of food and everyday products and services in northern Canada rural Alaska the South Pacific and the Caribbean</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -3083,33 +3083,33 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>FFH</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Fairfax Financial Holdings Limited</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.108</v>
+        <v>0.129</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>2245.27</v>
+        <v>31304.08</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Fairfax Financial Holdings Limited through its subsidiaries provides property and casualty insurance and reinsurance and investment management services in Canada the United States the Middle East and Asia and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.39</v>
+        <v>0.415</v>
       </c>
       <c r="H29" s="124" t="n">
         <v>211.92</v>
@@ -3156,7 +3156,7 @@
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="128" t="inlineStr">
         <is>
@@ -3165,33 +3165,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>ACQ</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>AutoCanada Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.316</v>
+        <v>0.271</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>3333.46</v>
+        <v>389.1</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -3206,246 +3206,162 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>SOIL</t>
+          <t>DSG</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.299</v>
+        <v>0.26</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>925.72</v>
+        <v>6794.59</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Saturn Oil &amp; Gas Inc engages in the acquisition exploration and development of petroleum and natural gas resource deposits in Canada</t>
+          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="128" t="inlineStr">
+      <c r="B32" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C32" s="115" t="inlineStr">
-        <is>
-          <t>ACQ</t>
-        </is>
-      </c>
-      <c r="D32" s="116" t="inlineStr">
-        <is>
-          <t>AutoCanada Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="117" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F32" s="117" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G32" s="118" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="H32" s="119" t="n">
-        <v>389.1</v>
-      </c>
-      <c r="I32" s="120" t="inlineStr">
-        <is>
-          <t>AutoCanada Inc through its subsidiaries operates franchised automobile dealerships and related business</t>
+      <c r="C32" s="130" t="inlineStr">
+        <is>
+          <t>GEI</t>
+        </is>
+      </c>
+      <c r="D32" s="131" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="132" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F32" s="132" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G32" s="133" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H32" s="134" t="n">
+        <v>3837.96</v>
+      </c>
+      <c r="I32" s="135" t="inlineStr">
+        <is>
+          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="8" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C33" s="121" t="inlineStr">
-        <is>
-          <t>DSG</t>
-        </is>
-      </c>
-      <c r="D33" s="122" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="123" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F33" s="123" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G33" s="118" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="H33" s="124" t="n">
-        <v>6794.59</v>
-      </c>
-      <c r="I33" s="125" t="inlineStr">
-        <is>
-          <t>The Descartes Systems Group Inc provides global logistics technology solutions in the United States Europe the Middle East Africa Canada and the Asia Pacific</t>
-        </is>
-      </c>
+      <c r="B33" s="136" t="n"/>
+      <c r="C33" s="137" t="n"/>
+      <c r="D33" s="138" t="n"/>
+      <c r="E33" s="139" t="n"/>
+      <c r="F33" s="139" t="n"/>
+      <c r="G33" s="140" t="n"/>
+      <c r="H33" s="141" t="n"/>
+      <c r="I33" s="142" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="52" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C34" s="115" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="D34" s="116" t="inlineStr">
-        <is>
-          <t>Suncor Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="117" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F34" s="117" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G34" s="118" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="H34" s="119" t="n">
-        <v>80962.39</v>
-      </c>
-      <c r="I34" s="120" t="inlineStr">
-        <is>
-          <t>Suncor Energy Inc operates as an integrated energy company in Canada the United States and internationally</t>
-        </is>
-      </c>
+      <c r="B34" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C34" s="144" t="n"/>
+      <c r="D34" s="144" t="n"/>
+      <c r="E34" s="144" t="n"/>
+      <c r="F34" s="144" t="n"/>
+      <c r="G34" s="144" t="n"/>
+      <c r="H34" s="144" t="n"/>
+      <c r="I34" s="144" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="70" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C35" s="130" t="inlineStr">
-        <is>
-          <t>GEI</t>
-        </is>
-      </c>
-      <c r="D35" s="131" t="inlineStr">
-        <is>
-          <t>Gibson Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="132" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F35" s="132" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G35" s="133" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="H35" s="134" t="n">
-        <v>3837.96</v>
-      </c>
-      <c r="I35" s="135" t="inlineStr">
-        <is>
-          <t>Gibson Energy Inc together with its subsidiaries engages in the gathering storing optimizing and processing of liquids and refined products in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B35" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C35" s="146" t="n"/>
+      <c r="D35" s="146" t="n"/>
+      <c r="E35" s="146" t="n"/>
+      <c r="F35" s="146" t="n"/>
+      <c r="G35" s="146" t="n"/>
+      <c r="H35" s="146" t="n"/>
+      <c r="I35" s="146" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="8" customHeight="1">
+    <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="136" t="n"/>
-      <c r="C36" s="137" t="n"/>
-      <c r="D36" s="138" t="n"/>
-      <c r="E36" s="139" t="n"/>
-      <c r="F36" s="139" t="n"/>
-      <c r="G36" s="140" t="n"/>
-      <c r="H36" s="141" t="n"/>
-      <c r="I36" s="142" t="n"/>
+      <c r="B36" s="48" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="89" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="34" customHeight="1">
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C37" s="144" t="n"/>
-      <c r="D37" s="144" t="n"/>
-      <c r="E37" s="144" t="n"/>
-      <c r="F37" s="144" t="n"/>
-      <c r="G37" s="144" t="n"/>
-      <c r="H37" s="144" t="n"/>
-      <c r="I37" s="144" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="89" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="28" customHeight="1">
+    <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C38" s="146" t="n"/>
-      <c r="D38" s="146" t="n"/>
-      <c r="E38" s="146" t="n"/>
-      <c r="F38" s="146" t="n"/>
-      <c r="G38" s="146" t="n"/>
-      <c r="H38" s="146" t="n"/>
-      <c r="I38" s="146" t="n"/>
+      <c r="B38" s="48" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="89" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
@@ -3596,11 +3512,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G35">
+  <conditionalFormatting sqref="G8:G32">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4541,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -4581,7 +4497,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46324.71790944901</v>
+        <v>46325.70470768796</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4695,12 +4611,12 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Illumina Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
@@ -4714,14 +4630,14 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.092</v>
+        <v>0.512</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>39661.06</v>
+        <v>241617.28</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Illumina Inc provides sequencing- and array-based solutions for genetic and genomic analysis in the Americas Europe Greater China the Asia Pacific the Middle East and Africa</t>
+          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
@@ -4755,7 +4671,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.435</v>
+        <v>0.429</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>25388.92</v>
@@ -4777,12 +4693,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>United Rentals Inc.</t>
+          <t>Stanley Black &amp; Decker Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -4792,18 +4708,18 @@
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.298</v>
+        <v>0.401</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>64935.97</v>
+        <v>13144.19</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>United Rentals Inc through its subsidiaries operates as an equipment rental company in the United States Canada Europe Australia and New Zealand</t>
+          <t>Stanley Black &amp; Decker Inc provides hand tools power tools outdoor products and related accessories in the United States Canada Other Americas Europe and Asia</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4818,39 +4734,39 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Emerson Electric Co.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.267</v>
+        <v>0.326</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>88425.8</v>
+        <v>25223.73</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Emerson Electric Co</t>
+          <t>Quest Diagnostics Incorporated provides diagnostic testing and services in the United States</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="106" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4859,39 +4775,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Aerospace and Defense</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.264</v>
+        <v>0.302</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>116283.92</v>
+        <v>129046.84</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
+          <t>Vertex Pharmaceuticals Incorporated operates as a biotechnology company in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4900,12 +4816,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>Regeneron Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4915,24 +4831,24 @@
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.263</v>
+        <v>0.287</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>28944.51</v>
+        <v>74249.87</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc engages in the development manufacture and marketing of products services and complementary digital solutions used in the diagnosis treatment and monitoring of patients in the United States Canada and internationally</t>
+          <t>Regeneron Pharmaceuticals Inc discovers invents develops manufactures and commercializes medicines to treat various diseases worldwide</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4941,39 +4857,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.198</v>
+        <v>0.272</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>60523.16</v>
+        <v>20324.32</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -4982,12 +4898,12 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Jacobs Solutions Inc.</t>
+          <t>United Rentals Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
@@ -4997,18 +4913,18 @@
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.178</v>
+        <v>0.271</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>16016.73</v>
+        <v>64935.97</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Jacobs Solutions Inc engages in the infrastructure and advanced facilities and consulting businesses in the United States Europe Canada India Asia Australia New Zealand the Middle East and Africa</t>
+          <t>United Rentals Inc through its subsidiaries operates as an equipment rental company in the United States Canada Europe Australia and New Zealand</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -5023,39 +4939,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Health Care Equipment and Supplies</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.093</v>
+        <v>0.258</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>93531.92999999999</v>
+        <v>28944.51</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
+          <t>GE HealthCare Technologies Inc engages in the development manufacture and marketing of products services and complementary digital solutions used in the diagnosis treatment and monitoring of patients in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5064,53 +4980,53 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.047</v>
+        <v>0.256</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>58304.85</v>
+        <v>299111.95</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation together with its subsidiaries engages in the acquisition exploration and development of oil and gas properties in the United States and internationally</t>
+          <t>Philip Morris International Inc operates as a tobacco company</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
@@ -5120,18 +5036,18 @@
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>1.197</v>
+        <v>0.243</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>14054.04</v>
+        <v>626725.46</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
+          <t>Johnson &amp; Johnson together with its subsidiaries engages in the research and development manufacture and sale of a range of products in the healthcare field worldwide</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
@@ -5139,163 +5055,163 @@
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Revvity Inc.</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>16701.36</v>
+        <v>88425.8</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Revvity Inc provides health sciences solutions technologies and services</t>
+          <t>Emerson Electric Co</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Health Care Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.838</v>
+        <v>0.192</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>45576.53</v>
+        <v>78079.92999999999</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc provides cloud-based software for the life sciences industry in North America Europe the Asia Pacific the Middle East Africa and Latin America</t>
+          <t>Ecolab Inc provides water hygiene and infection prevention solutions and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="34" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>J</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Jacobs Solutions Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.765</v>
+        <v>0.19</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>17904.45</v>
+        <v>16016.73</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Jacobs Solutions Inc engages in the infrastructure and advanced facilities and consulting businesses in the United States Europe Canada India Asia Australia New Zealand the Middle East and Africa</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="88" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.707</v>
+        <v>0.188</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>42172.99</v>
+        <v>14020.94</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc provides clinical research services commercial insights and healthcare intelligence to the life sciences and healthcare industries in the Americas Europe Africa and the Asia-Pacific</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
@@ -5303,292 +5219,292 @@
     </row>
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.679</v>
+        <v>0.17</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>17950.14</v>
+        <v>115179.44</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation together with its subsidiaries operates in the automatic identification and data capture solutions industry worldwide</t>
+          <t>S&amp;P Global Inc together with its subsidiaries provides benchmarks data analytics and workflow solutions in the global capital energy and commodity and automotive markets</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="70" customHeight="1">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc.</t>
+          <t>American Water Works Company Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Water Utilities</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.624</v>
+        <v>0.161</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>47137.94</v>
+        <v>25463.94</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
+          <t>American Water Works Company Inc through its subsidiaries provides water and wastewater services in the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B25" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Motorola Solutions Inc.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.592</v>
+        <v>0.133</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>42201.2</v>
+        <v>74919.87</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Motorola Solutions Inc provides public safety government defense and enterprise security solutions in the United States the United Kingdom Canada and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B26" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Altria Group Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.536</v>
+        <v>0.099</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>241617.28</v>
+        <v>115290.81</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc provides life sciences solutions analytical instruments specialty diagnostics and laboratory products and biopharma services internationally</t>
+          <t>Altria Group Inc through its subsidiaries manufactures and sells smokeable and oral tobacco products in the United States</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="106" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B27" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Workday Inc.</t>
+          <t>Intercontinental Exchange Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.513</v>
+        <v>0.09</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>45398.38</v>
+        <v>85343.19</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Workday Inc provides enterprise cloud applications in the United States and internationally</t>
+          <t>Intercontinental Exchange Inc together with its subsidiaries provides technology and data to financial institutions corporations and government entities in the United States the United Kingdom the European Union Canada Asia Pacific and the Middle East</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B28" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc.</t>
+          <t>Consolidated Edison Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.443</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>26039.81</v>
+        <v>38770.61</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Consolidated Edison Inc through its subsidiaries engages in the regulated electric gas and steam delivery businesses in the United States</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="52" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B29" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Johnson Controls International plc</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.435</v>
+        <v>0.044</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>224207.66</v>
+        <v>93531.92999999999</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
+          <t>Johnson Controls International plc together with its subsidiaries engages in engineering manufacturing commissioning and retrofitting building products and systems in the Americas Europe the Middle East Africa and the Asia-Pacific</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="70" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="127" t="inlineStr">
         <is>
@@ -5597,39 +5513,39 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Charles River Laboratories International Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.423</v>
+        <v>1.063</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>24969.64</v>
+        <v>14054.04</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Charles River Laboratories International Inc provides drug discovery non-clinical development and safety testing services in the United States Europe Canada the Asia Pacific and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="52" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="127" t="inlineStr">
         <is>
@@ -5638,12 +5554,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Revvity Inc.</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5653,24 +5569,24 @@
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.422</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>1054668.83</v>
+        <v>16701.36</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
+          <t>Revvity Inc provides health sciences solutions technologies and services</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -5679,39 +5595,39 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>Agilent Technologies Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.412</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>12320.13</v>
+        <v>47137.94</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
+          <t>Agilent Technologies Inc provides application focused solutions to the life sciences diagnostics and applied chemical markets worldwide</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="52" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="127" t="inlineStr">
         <is>
@@ -5720,12 +5636,12 @@
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -5739,20 +5655,20 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.369</v>
+        <v>0.524</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>30639.57</v>
+        <v>42201.2</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="52" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="127" t="inlineStr">
         <is>
@@ -5761,12 +5677,12 @@
       </c>
       <c r="C34" s="115" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E34" s="117" t="inlineStr">
@@ -5776,24 +5692,24 @@
       </c>
       <c r="F34" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G34" s="118" t="n">
-        <v>0.367</v>
+        <v>0.474</v>
       </c>
       <c r="H34" s="119" t="n">
-        <v>151241.83</v>
+        <v>224207.66</v>
       </c>
       <c r="I34" s="120" t="inlineStr">
         <is>
-          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
+          <t>Amgen Inc discovers develops manufactures and delivers human therapeutics worldwide</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="52" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="127" t="inlineStr">
         <is>
@@ -5802,39 +5718,39 @@
       </c>
       <c r="C35" s="121" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D35" s="122" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F35" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G35" s="118" t="n">
-        <v>0.353</v>
+        <v>0.474</v>
       </c>
       <c r="H35" s="124" t="n">
-        <v>33875.2</v>
+        <v>1054668.83</v>
       </c>
       <c r="I35" s="125" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc manufactures markets and sells skin care makeup fragrance and hair care products worldwide</t>
+          <t>Eli Lilly and Company discovers develops manufactures and markets human pharmaceutical products in the United States Europe China Japan and internationally</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="88" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="127" t="inlineStr">
         <is>
@@ -5843,33 +5759,33 @@
       </c>
       <c r="C36" s="115" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="D36" s="116" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E36" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F36" s="117" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="G36" s="118" t="n">
-        <v>0.31</v>
+        <v>0.468</v>
       </c>
       <c r="H36" s="119" t="n">
-        <v>21455.05</v>
+        <v>116683.09</v>
       </c>
       <c r="I36" s="120" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc together with its subsidiaries manufactures and markets food beverage health and biosciences scent and complementary adjacent products in the United States and internationally</t>
+          <t>Accenture plc provides strategy and consulting industry X song and technology and operation services in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
@@ -5884,39 +5800,39 @@
       </c>
       <c r="C37" s="121" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D37" s="122" t="inlineStr">
         <is>
-          <t>Hasbro Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E37" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F37" s="123" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G37" s="118" t="n">
-        <v>0.285</v>
+        <v>0.44</v>
       </c>
       <c r="H37" s="124" t="n">
-        <v>12857.61</v>
+        <v>480788.44</v>
       </c>
       <c r="I37" s="125" t="inlineStr">
         <is>
-          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="88" customHeight="1">
+    <row r="38" ht="70" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="127" t="inlineStr">
         <is>
@@ -5925,39 +5841,39 @@
       </c>
       <c r="C38" s="115" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D38" s="116" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E38" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F38" s="117" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G38" s="118" t="n">
-        <v>0.274</v>
+        <v>0.432</v>
       </c>
       <c r="H38" s="119" t="n">
-        <v>20324.32</v>
+        <v>24969.64</v>
       </c>
       <c r="I38" s="120" t="inlineStr">
         <is>
-          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row r="39" ht="52" customHeight="1">
       <c r="A39" s="28" t="n"/>
       <c r="B39" s="127" t="inlineStr">
         <is>
@@ -5966,39 +5882,39 @@
       </c>
       <c r="C39" s="121" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="D39" s="122" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc.</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F39" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="G39" s="118" t="n">
-        <v>0.249</v>
+        <v>0.419</v>
       </c>
       <c r="H39" s="124" t="n">
-        <v>35615.09</v>
+        <v>12320.13</v>
       </c>
       <c r="I39" s="125" t="inlineStr">
         <is>
-          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
+          <t>Allegion plc engages in the provision of security products and solutions worldwide</t>
         </is>
       </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="52" customHeight="1">
+    <row r="40" ht="88" customHeight="1">
       <c r="A40" s="36" t="n"/>
       <c r="B40" s="127" t="inlineStr">
         <is>
@@ -6007,33 +5923,33 @@
       </c>
       <c r="C40" s="115" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="D40" s="116" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc.</t>
+          <t>West Pharmaceutical Services Inc.</t>
         </is>
       </c>
       <c r="E40" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F40" s="117" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G40" s="118" t="n">
-        <v>0.242</v>
+        <v>0.368</v>
       </c>
       <c r="H40" s="119" t="n">
-        <v>23628.33</v>
+        <v>26039.81</v>
       </c>
       <c r="I40" s="120" t="inlineStr">
         <is>
-          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+          <t>West Pharmaceutical Services Inc designs manufactures and sells containment and delivery systems for injectable drugs and healthcare products in the Americas Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J40" s="53" t="n"/>
@@ -6048,33 +5964,33 @@
       </c>
       <c r="C41" s="121" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D41" s="122" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F41" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G41" s="118" t="n">
-        <v>0.229</v>
+        <v>0.355</v>
       </c>
       <c r="H41" s="124" t="n">
-        <v>15537.74</v>
+        <v>33430.82</v>
       </c>
       <c r="I41" s="125" t="inlineStr">
         <is>
-          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+          <t>Biogen Inc discovers develops manufactures and delivers therapies in the United States Europe Germany Asia and internationally</t>
         </is>
       </c>
       <c r="J41" s="54" t="n"/>
@@ -6089,12 +6005,12 @@
       </c>
       <c r="C42" s="115" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="D42" s="116" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E42" s="117" t="inlineStr">
@@ -6104,24 +6020,24 @@
       </c>
       <c r="F42" s="117" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G42" s="118" t="n">
-        <v>0.229</v>
+        <v>0.335</v>
       </c>
       <c r="H42" s="119" t="n">
-        <v>183538.16</v>
+        <v>151241.83</v>
       </c>
       <c r="I42" s="120" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
+          <t>Danaher Corporation designs manufactures and markets professional medical research and industrial products and services in the United States China and internationally</t>
         </is>
       </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="52" customHeight="1">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
       <c r="B43" s="127" t="inlineStr">
         <is>
@@ -6130,39 +6046,39 @@
       </c>
       <c r="C43" s="121" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D43" s="122" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="E43" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F43" s="123" t="inlineStr">
         <is>
-          <t>Electronic Equipment Instruments and Components</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G43" s="118" t="n">
-        <v>0.228</v>
+        <v>0.331</v>
       </c>
       <c r="H43" s="124" t="n">
-        <v>16850.47</v>
+        <v>30639.57</v>
       </c>
       <c r="I43" s="125" t="inlineStr">
         <is>
-          <t>CDW Corporation provides information technology (IT) solutions in the United States the United Kingdom and Canada</t>
+          <t>Mettler-Toledo International Inc manufactures and supplies precision instruments and services in the Americas Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="52" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
       <c r="B44" s="127" t="inlineStr">
         <is>
@@ -6171,33 +6087,33 @@
       </c>
       <c r="C44" s="115" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D44" s="116" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Roper Technologies Inc.</t>
         </is>
       </c>
       <c r="E44" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F44" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G44" s="118" t="n">
-        <v>0.218</v>
+        <v>0.324</v>
       </c>
       <c r="H44" s="119" t="n">
-        <v>404759.18</v>
+        <v>35615.09</v>
       </c>
       <c r="I44" s="120" t="inlineStr">
         <is>
-          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+          <t>Roper Technologies Inc designs and develops vertical software and technology enabled products in the United States Canada Europe Asia and internationally</t>
         </is>
       </c>
       <c r="J44" s="43" t="n"/>
@@ -6212,39 +6128,39 @@
       </c>
       <c r="C45" s="121" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D45" s="122" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Gilead Sciences Inc.</t>
         </is>
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F45" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G45" s="118" t="n">
-        <v>0.21</v>
+        <v>0.314</v>
       </c>
       <c r="H45" s="124" t="n">
-        <v>156513.85</v>
+        <v>183538.16</v>
       </c>
       <c r="I45" s="125" t="inlineStr">
         <is>
-          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+          <t>Gilead Sciences Inc a biopharmaceutical company discovers develops and commercializes medicines in the areas of unmet medical need in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row r="46" ht="52" customHeight="1">
       <c r="A46" s="43" t="n"/>
       <c r="B46" s="127" t="inlineStr">
         <is>
@@ -6253,39 +6169,39 @@
       </c>
       <c r="C46" s="115" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D46" s="116" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="E46" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F46" s="117" t="inlineStr">
         <is>
-          <t>Health Care Equipment and Supplies</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G46" s="118" t="n">
-        <v>0.21</v>
+        <v>0.302</v>
       </c>
       <c r="H46" s="119" t="n">
-        <v>31594.32</v>
+        <v>23268.86</v>
       </c>
       <c r="I46" s="120" t="inlineStr">
         <is>
-          <t>ResMed Inc engages in the digital health and cloud-connected medical devices business in the United States and internationally</t>
+          <t>Veralto Corporation provides water analytics water treatment marking and coding and packaging and color solutions worldwide</t>
         </is>
       </c>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="70" customHeight="1" thickBot="1">
+    <row r="47" ht="52" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
       <c r="B47" s="127" t="inlineStr">
         <is>
@@ -6294,33 +6210,33 @@
       </c>
       <c r="C47" s="121" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="D47" s="122" t="inlineStr">
         <is>
-          <t>ServiceNow Inc.</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E47" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G47" s="118" t="n">
-        <v>0.202</v>
+        <v>0.297</v>
       </c>
       <c r="H47" s="124" t="n">
-        <v>142623.33</v>
+        <v>54537.32</v>
       </c>
       <c r="I47" s="125" t="inlineStr">
         <is>
-          <t>ServiceNow Inc provides cloud-based solution for digital workflows in the North America Brazil Europe the Middle East and Africa Asia Pacific and internationally</t>
+          <t>Cardinal Health Inc operates as a healthcare services and products company in the United States and internationally</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -6335,39 +6251,39 @@
       </c>
       <c r="C48" s="115" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D48" s="116" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation</t>
+          <t>Hasbro Inc.</t>
         </is>
       </c>
       <c r="E48" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F48" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G48" s="118" t="n">
-        <v>0.2</v>
+        <v>0.288</v>
       </c>
       <c r="H48" s="119" t="n">
-        <v>677009.86</v>
+        <v>12857.61</v>
       </c>
       <c r="I48" s="120" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+          <t>Hasbro Inc operates as a toy and game company in the United States Europe Canada Mexico Latin America Australia China and Hong Kong</t>
         </is>
       </c>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
     </row>
-    <row r="49" ht="70" customHeight="1">
+    <row r="49" ht="52" customHeight="1">
       <c r="A49" s="43" t="n"/>
       <c r="B49" s="127" t="inlineStr">
         <is>
@@ -6376,12 +6292,12 @@
       </c>
       <c r="C49" s="121" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D49" s="122" t="inlineStr">
         <is>
-          <t>Nasdaq Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E49" s="123" t="inlineStr">
@@ -6391,24 +6307,24 @@
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G49" s="118" t="n">
-        <v>0.165</v>
+        <v>0.273</v>
       </c>
       <c r="H49" s="124" t="n">
-        <v>51024.57</v>
+        <v>682021.24</v>
       </c>
       <c r="I49" s="125" t="inlineStr">
         <is>
-          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
-    <row r="50" ht="88" customHeight="1">
+    <row r="50" ht="70" customHeight="1">
       <c r="B50" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
@@ -6416,159 +6332,805 @@
       </c>
       <c r="C50" s="115" t="inlineStr">
         <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D50" s="116" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="E50" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F50" s="117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G50" s="118" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="H50" s="119" t="n">
+        <v>498865.76</v>
+      </c>
+      <c r="I50" s="120" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated a technology company provides transaction processing and other payment-related products and services in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="70" customHeight="1">
+      <c r="B51" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C51" s="121" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D51" s="122" t="inlineStr">
+        <is>
+          <t>APA Corporation</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F51" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G51" s="118" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="H51" s="124" t="n">
+        <v>15537.74</v>
+      </c>
+      <c r="I51" s="125" t="inlineStr">
+        <is>
+          <t>APA Corporation an independent energy company explores for develops and produces natural gas crude oil and natural gas liquids</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="70" customHeight="1">
+      <c r="B52" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C52" s="115" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="D52" s="116" t="inlineStr">
+        <is>
+          <t>Medtronic plc</t>
+        </is>
+      </c>
+      <c r="E52" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F52" s="117" t="inlineStr">
+        <is>
+          <t>Health Care Equipment and Supplies</t>
+        </is>
+      </c>
+      <c r="G52" s="118" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H52" s="119" t="n">
+        <v>111058.59</v>
+      </c>
+      <c r="I52" s="120" t="inlineStr">
+        <is>
+          <t>Medtronic plc develops manufactures and sells device-based medical therapies to healthcare systems physicians clinicians and patients in the United States Ireland and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="70" customHeight="1">
+      <c r="B53" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C53" s="121" t="inlineStr">
+        <is>
+          <t>KDP</t>
+        </is>
+      </c>
+      <c r="D53" s="122" t="inlineStr">
+        <is>
+          <t>Keurig Dr Pepper Inc.</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F53" s="123" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G53" s="118" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="H53" s="124" t="n">
+        <v>41984.2</v>
+      </c>
+      <c r="I53" s="125" t="inlineStr">
+        <is>
+          <t>Keurig Dr Pepper Inc owns manufactures and distributors beverages and single serve brewing systems in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="106" customHeight="1">
+      <c r="B54" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C54" s="115" t="inlineStr">
+        <is>
+          <t>LMT</t>
+        </is>
+      </c>
+      <c r="D54" s="116" t="inlineStr">
+        <is>
+          <t>Lockheed Martin Corporation</t>
+        </is>
+      </c>
+      <c r="E54" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F54" s="117" t="inlineStr">
+        <is>
+          <t>Aerospace and Defense</t>
+        </is>
+      </c>
+      <c r="G54" s="118" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H54" s="119" t="n">
+        <v>116283.92</v>
+      </c>
+      <c r="I54" s="120" t="inlineStr">
+        <is>
+          <t>Lockheed Martin Corporation an aerospace and defense company engages in the research design development manufacture integration and sustainment of technology systems products and services in the United States Europe Asia the Middle East and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1">
+      <c r="B55" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C55" s="121" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="D55" s="122" t="inlineStr">
+        <is>
+          <t>Chevron Corporation</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F55" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G55" s="118" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="H55" s="124" t="n">
+        <v>404759.18</v>
+      </c>
+      <c r="I55" s="125" t="inlineStr">
+        <is>
+          <t>Chevron Corporation through its subsidiaries engages in the integrated energy and chemicals operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="B56" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C56" s="115" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D56" s="116" t="inlineStr">
+        <is>
+          <t>ConocoPhillips</t>
+        </is>
+      </c>
+      <c r="E56" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F56" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="H56" s="119" t="n">
+        <v>156513.85</v>
+      </c>
+      <c r="I56" s="120" t="inlineStr">
+        <is>
+          <t>ConocoPhillips explores for produces transports and markets crude oil bitumen natural gas liquefied natural gas (LNG) and natural gas liquids</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="B57" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C57" s="121" t="inlineStr">
+        <is>
+          <t>ULTA</t>
+        </is>
+      </c>
+      <c r="D57" s="122" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc.</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F57" s="123" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G57" s="118" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="H57" s="124" t="n">
+        <v>23628.33</v>
+      </c>
+      <c r="I57" s="125" t="inlineStr">
+        <is>
+          <t>Ulta Beauty Inc operates as a specialty beauty retailer in the United States Mexico and Kuwait</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="70" customHeight="1">
+      <c r="B58" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C58" s="115" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D58" s="116" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="E58" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F58" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G58" s="118" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="H58" s="119" t="n">
+        <v>677009.86</v>
+      </c>
+      <c r="I58" s="120" t="inlineStr">
+        <is>
+          <t>ExxonMobil Holdings Corporation engages in the exploration and production of crude oil and natural gas in the United States Canada and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="70" customHeight="1">
+      <c r="B59" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C59" s="121" t="inlineStr">
+        <is>
+          <t>TRGP</t>
+        </is>
+      </c>
+      <c r="D59" s="122" t="inlineStr">
+        <is>
+          <t>Targa Resources Corp.</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F59" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G59" s="118" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H59" s="124" t="n">
+        <v>60523.16</v>
+      </c>
+      <c r="I59" s="125" t="inlineStr">
+        <is>
+          <t>Targa Resources Corp together with its subsidiaries owns operates acquires and develops a portfolio of complementary domestic infrastructure assets in North America</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
+      <c r="B60" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C60" s="115" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D60" s="116" t="inlineStr">
+        <is>
+          <t>Tyler Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="117" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F60" s="117" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G60" s="118" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H60" s="119" t="n">
+        <v>13525.55</v>
+      </c>
+      <c r="I60" s="120" t="inlineStr">
+        <is>
+          <t>Tyler Technologies Inc provides integrated software and technology management solutions for the public sector in the United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="70" customHeight="1">
+      <c r="B61" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C61" s="121" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D61" s="122" t="inlineStr">
+        <is>
+          <t>Pfizer Inc.</t>
+        </is>
+      </c>
+      <c r="E61" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F61" s="123" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="G61" s="118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H61" s="124" t="n">
+        <v>159089.29</v>
+      </c>
+      <c r="I61" s="125" t="inlineStr">
+        <is>
+          <t>Pfizer Inc discovers develops manufactures markets distributes and sells biopharmaceutical products in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="52" customHeight="1">
+      <c r="B62" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C62" s="115" t="inlineStr">
+        <is>
+          <t>RSG</t>
+        </is>
+      </c>
+      <c r="D62" s="116" t="inlineStr">
+        <is>
+          <t>Republic Services Inc.</t>
+        </is>
+      </c>
+      <c r="E62" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F62" s="117" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G62" s="118" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="H62" s="119" t="n">
+        <v>66372.58</v>
+      </c>
+      <c r="I62" s="120" t="inlineStr">
+        <is>
+          <t>Republic Services Inc together with its subsidiaries offers environmental services in the United States and Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="B63" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C63" s="121" t="inlineStr">
+        <is>
           <t>EOG</t>
         </is>
       </c>
-      <c r="D50" s="116" t="inlineStr">
+      <c r="D63" s="122" t="inlineStr">
         <is>
           <t>EOG Resources Inc.</t>
         </is>
       </c>
-      <c r="E50" s="117" t="inlineStr">
+      <c r="E63" s="123" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F50" s="117" t="inlineStr">
+      <c r="F63" s="123" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G50" s="118" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="H50" s="119" t="n">
+      <c r="G63" s="118" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="H63" s="124" t="n">
         <v>75763.52</v>
       </c>
-      <c r="I50" s="120" t="inlineStr">
+      <c r="I63" s="125" t="inlineStr">
         <is>
           <t>EOG Resources Inc together with its subsidiaries explores for develops produces and markets crude oil natural gas liquids and natural gas in producing basins in the United States the Republic of Trinidad and Tobago and internationally</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="52" customHeight="1">
-      <c r="B51" s="127" t="inlineStr">
+    <row r="64" ht="70" customHeight="1">
+      <c r="B64" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C51" s="121" t="inlineStr">
+      <c r="C64" s="115" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="D64" s="116" t="inlineStr">
+        <is>
+          <t>Fastenal Company</t>
+        </is>
+      </c>
+      <c r="E64" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F64" s="117" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G64" s="118" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H64" s="119" t="n">
+        <v>57901.58</v>
+      </c>
+      <c r="I64" s="120" t="inlineStr">
+        <is>
+          <t>Fastenal Company together with its subsidiaries engages in the wholesale distribution of industrial and construction supplies in the United States Canada Mexico and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="70" customHeight="1">
+      <c r="B65" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C65" s="121" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="D65" s="122" t="inlineStr">
+        <is>
+          <t>Nasdaq Inc.</t>
+        </is>
+      </c>
+      <c r="E65" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F65" s="123" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G65" s="118" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H65" s="124" t="n">
+        <v>51024.57</v>
+      </c>
+      <c r="I65" s="125" t="inlineStr">
+        <is>
+          <t>Nasdaq Inc operates as a technology company that serves capital markets and other industries in the United States and internationally</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="52" customHeight="1">
+      <c r="B66" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C66" s="115" t="inlineStr">
+        <is>
+          <t>CHD</t>
+        </is>
+      </c>
+      <c r="D66" s="116" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E66" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F66" s="117" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="G66" s="118" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H66" s="119" t="n">
+        <v>22965.61</v>
+      </c>
+      <c r="I66" s="120" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="B67" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C67" s="121" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="D67" s="122" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F67" s="123" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="G67" s="118" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="H67" s="124" t="n">
+        <v>345602.03</v>
+      </c>
+      <c r="I67" s="125" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
+      <c r="B68" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C68" s="115" t="inlineStr">
         <is>
           <t>HCA</t>
         </is>
       </c>
-      <c r="D51" s="122" t="inlineStr">
+      <c r="D68" s="116" t="inlineStr">
         <is>
           <t>HCA Healthcare Inc.</t>
         </is>
       </c>
-      <c r="E51" s="123" t="inlineStr">
+      <c r="E68" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F51" s="123" t="inlineStr">
+      <c r="F68" s="117" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
       </c>
-      <c r="G51" s="118" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="H51" s="124" t="n">
+      <c r="G68" s="118" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="H68" s="119" t="n">
         <v>94806.22</v>
       </c>
-      <c r="I51" s="125" t="inlineStr">
+      <c r="I68" s="120" t="inlineStr">
         <is>
           <t>HCA Healthcare Inc through its subsidiaries provides health care services in the United States</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="52" customHeight="1">
-      <c r="B52" s="129" t="inlineStr">
+    <row r="69" ht="52" customHeight="1">
+      <c r="B69" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C52" s="147" t="inlineStr">
+      <c r="C69" s="147" t="inlineStr">
         <is>
           <t>PTC</t>
         </is>
       </c>
-      <c r="D52" s="148" t="inlineStr">
+      <c r="D69" s="148" t="inlineStr">
         <is>
           <t>PTC Inc.</t>
         </is>
       </c>
-      <c r="E52" s="149" t="inlineStr">
+      <c r="E69" s="149" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F52" s="149" t="inlineStr">
+      <c r="F69" s="149" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="G52" s="133" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="H52" s="150" t="n">
+      <c r="G69" s="133" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="H69" s="150" t="n">
         <v>21029.38</v>
       </c>
-      <c r="I52" s="151" t="inlineStr">
+      <c r="I69" s="151" t="inlineStr">
         <is>
           <t>PTC Inc operates as software company in the Americas Europe and the Asia Pacific</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="8" customHeight="1">
-      <c r="B53" s="152" t="n"/>
-      <c r="C53" s="152" t="n"/>
-      <c r="D53" s="152" t="n"/>
-      <c r="E53" s="152" t="n"/>
-      <c r="F53" s="152" t="n"/>
-      <c r="G53" s="152" t="n"/>
-      <c r="H53" s="152" t="n"/>
-      <c r="I53" s="152" t="n"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="B54" s="143" t="inlineStr">
+    <row r="70" ht="8" customHeight="1">
+      <c r="B70" s="152" t="n"/>
+      <c r="C70" s="152" t="n"/>
+      <c r="D70" s="152" t="n"/>
+      <c r="E70" s="152" t="n"/>
+      <c r="F70" s="152" t="n"/>
+      <c r="G70" s="152" t="n"/>
+      <c r="H70" s="152" t="n"/>
+      <c r="I70" s="152" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="B71" s="143" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C54" s="144" t="n"/>
-      <c r="D54" s="144" t="n"/>
-      <c r="E54" s="144" t="n"/>
-      <c r="F54" s="144" t="n"/>
-      <c r="G54" s="144" t="n"/>
-      <c r="H54" s="144" t="n"/>
-      <c r="I54" s="144" t="n"/>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="B55" s="145" t="inlineStr">
+      <c r="C71" s="144" t="n"/>
+      <c r="D71" s="144" t="n"/>
+      <c r="E71" s="144" t="n"/>
+      <c r="F71" s="144" t="n"/>
+      <c r="G71" s="144" t="n"/>
+      <c r="H71" s="144" t="n"/>
+      <c r="I71" s="144" t="n"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="B72" s="145" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C55" s="146" t="n"/>
-      <c r="D55" s="146" t="n"/>
-      <c r="E55" s="146" t="n"/>
-      <c r="F55" s="146" t="n"/>
-      <c r="G55" s="146" t="n"/>
-      <c r="H55" s="146" t="n"/>
-      <c r="I55" s="146" t="n"/>
+      <c r="C72" s="146" t="n"/>
+      <c r="D72" s="146" t="n"/>
+      <c r="E72" s="146" t="n"/>
+      <c r="F72" s="146" t="n"/>
+      <c r="G72" s="146" t="n"/>
+      <c r="H72" s="146" t="n"/>
+      <c r="I72" s="146" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G52">
+  <conditionalFormatting sqref="G8:G69">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
